--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3FEA5A-86CB-4429-8A51-A12A698511B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87FED35-C8AF-4DEE-B249-5227B195F64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71340" yWindow="2940" windowWidth="33420" windowHeight="22650" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="43200" windowHeight="23985" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -151,17 +151,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -986,17 +986,29 @@
               <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
               <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
             </a:rPr>
-            <a:t>で設計データを公</a:t>
+            <a:t>で設計データを公開中です。</a:t>
           </a:r>
+        </a:p>
+        <a:p>
           <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
               <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
             </a:rPr>
-            <a:t>	OSHWLab</a:t>
+            <a:t>画像をクリックすることで</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>OSHWLab</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
@@ -1008,13 +1020,6 @@
             </a:rPr>
             <a:t>の当該のサイトに飛びます。</a:t>
           </a:r>
-          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
@@ -2508,185 +2513,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="8">
+      <c r="B1" s="10">
         <v>1</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="7">
+      <c r="C1" s="10"/>
+      <c r="D1" s="8">
         <v>2</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7">
+      <c r="E1" s="8"/>
+      <c r="F1" s="8">
         <v>3</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7">
+      <c r="G1" s="8"/>
+      <c r="H1" s="8">
         <v>4</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7">
+      <c r="I1" s="8"/>
+      <c r="J1" s="8">
         <v>5</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7">
+      <c r="K1" s="8"/>
+      <c r="L1" s="8">
         <v>6</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7">
+      <c r="M1" s="8"/>
+      <c r="N1" s="8">
         <v>7</v>
       </c>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7">
+      <c r="O1" s="8"/>
+      <c r="P1" s="8">
         <v>8</v>
       </c>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7">
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8">
         <v>9</v>
       </c>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7">
+      <c r="S1" s="8"/>
+      <c r="T1" s="8">
         <v>10</v>
       </c>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7">
+      <c r="U1" s="8"/>
+      <c r="V1" s="8">
         <v>11</v>
       </c>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7">
+      <c r="W1" s="8"/>
+      <c r="X1" s="8">
         <v>12</v>
       </c>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7">
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="8">
         <v>13</v>
       </c>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7">
+      <c r="AA1" s="8"/>
+      <c r="AB1" s="8">
         <v>14</v>
       </c>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7">
+      <c r="AC1" s="8"/>
+      <c r="AD1" s="8">
         <v>15</v>
       </c>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7">
+      <c r="AE1" s="8"/>
+      <c r="AF1" s="8">
         <v>16</v>
       </c>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7">
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="8">
         <v>17</v>
       </c>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7">
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8">
         <v>18</v>
       </c>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7">
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8">
         <v>19</v>
       </c>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7">
+      <c r="AM1" s="8"/>
+      <c r="AN1" s="8">
         <v>20</v>
       </c>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="7">
+      <c r="AO1" s="8"/>
+      <c r="AP1" s="8">
         <v>21</v>
       </c>
-      <c r="AQ1" s="7"/>
-      <c r="AR1" s="7">
+      <c r="AQ1" s="8"/>
+      <c r="AR1" s="8">
         <v>22</v>
       </c>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="7">
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8">
         <v>23</v>
       </c>
-      <c r="AU1" s="7"/>
-      <c r="AV1" s="7">
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8">
         <v>24</v>
       </c>
-      <c r="AW1" s="7"/>
-      <c r="AX1" s="7">
+      <c r="AW1" s="8"/>
+      <c r="AX1" s="8">
         <v>25</v>
       </c>
-      <c r="AY1" s="7"/>
-      <c r="AZ1" s="7">
+      <c r="AY1" s="8"/>
+      <c r="AZ1" s="8">
         <v>26</v>
       </c>
-      <c r="BA1" s="7"/>
-      <c r="BB1" s="7">
+      <c r="BA1" s="8"/>
+      <c r="BB1" s="8">
         <v>27</v>
       </c>
-      <c r="BC1" s="7"/>
-      <c r="BD1" s="7">
+      <c r="BC1" s="8"/>
+      <c r="BD1" s="8">
         <v>28</v>
       </c>
-      <c r="BE1" s="7"/>
-      <c r="BF1" s="7">
+      <c r="BE1" s="8"/>
+      <c r="BF1" s="8">
         <v>29</v>
       </c>
-      <c r="BG1" s="7"/>
-      <c r="BH1" s="7">
+      <c r="BG1" s="8"/>
+      <c r="BH1" s="8">
         <v>30</v>
       </c>
-      <c r="BI1" s="7"/>
-      <c r="BJ1" s="7">
+      <c r="BI1" s="8"/>
+      <c r="BJ1" s="8">
         <v>31</v>
       </c>
-      <c r="BK1" s="7"/>
-      <c r="BL1" s="7">
+      <c r="BK1" s="8"/>
+      <c r="BL1" s="8">
         <v>32</v>
       </c>
-      <c r="BM1" s="7"/>
-      <c r="BN1" s="7">
+      <c r="BM1" s="8"/>
+      <c r="BN1" s="8">
         <v>33</v>
       </c>
-      <c r="BO1" s="7"/>
-      <c r="BP1" s="7">
+      <c r="BO1" s="8"/>
+      <c r="BP1" s="8">
         <v>34</v>
       </c>
-      <c r="BQ1" s="7"/>
-      <c r="BR1" s="7">
+      <c r="BQ1" s="8"/>
+      <c r="BR1" s="8">
         <v>35</v>
       </c>
-      <c r="BS1" s="7"/>
-      <c r="BT1" s="7">
+      <c r="BS1" s="8"/>
+      <c r="BT1" s="8">
         <v>36</v>
       </c>
-      <c r="BU1" s="7"/>
-      <c r="BV1" s="7">
+      <c r="BU1" s="8"/>
+      <c r="BV1" s="8">
         <v>37</v>
       </c>
-      <c r="BW1" s="7"/>
-      <c r="BX1" s="7">
+      <c r="BW1" s="8"/>
+      <c r="BX1" s="8">
         <v>38</v>
       </c>
-      <c r="BY1" s="7"/>
-      <c r="BZ1" s="7">
+      <c r="BY1" s="8"/>
+      <c r="BZ1" s="8">
         <v>39</v>
       </c>
-      <c r="CA1" s="7"/>
-      <c r="CB1" s="7">
+      <c r="CA1" s="8"/>
+      <c r="CB1" s="8">
         <v>40</v>
       </c>
-      <c r="CC1" s="7"/>
-      <c r="CD1" s="7">
+      <c r="CC1" s="8"/>
+      <c r="CD1" s="8">
         <v>41</v>
       </c>
-      <c r="CE1" s="7"/>
-      <c r="CF1" s="7">
+      <c r="CE1" s="8"/>
+      <c r="CF1" s="8">
         <v>42</v>
       </c>
-      <c r="CG1" s="7"/>
-      <c r="CH1" s="7">
+      <c r="CG1" s="8"/>
+      <c r="CH1" s="8">
         <v>43</v>
       </c>
-      <c r="CI1" s="7"/>
-      <c r="CJ1" s="7">
+      <c r="CI1" s="8"/>
+      <c r="CJ1" s="8">
         <v>44</v>
       </c>
-      <c r="CK1" s="7"/>
+      <c r="CK1" s="8"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -2779,7 +2784,7 @@
       <c r="CK2" s="4"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
@@ -2870,7 +2875,7 @@
       <c r="CK3" s="5"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -2963,7 +2968,7 @@
       <c r="CK4" s="4"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -3054,7 +3059,7 @@
       <c r="CK5" s="5"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="7">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -3147,7 +3152,7 @@
       <c r="CK6" s="4"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -3238,7 +3243,7 @@
       <c r="CK7" s="5"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="7">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -3331,7 +3336,7 @@
       <c r="CK8" s="4"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
+      <c r="A9" s="7"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -3422,7 +3427,7 @@
       <c r="CK9" s="5"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="7">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -3515,7 +3520,7 @@
       <c r="CK10" s="4"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -3606,7 +3611,7 @@
       <c r="CK11" s="5"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="7">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -3699,7 +3704,7 @@
       <c r="CK12" s="4"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="6"/>
@@ -3790,7 +3795,7 @@
       <c r="CK13" s="5"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="7">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -3883,7 +3888,7 @@
       <c r="CK14" s="4"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
+      <c r="A15" s="7"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -3974,7 +3979,7 @@
       <c r="CK15" s="5"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="7">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -4067,7 +4072,7 @@
       <c r="CK16" s="4"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9"/>
+      <c r="A17" s="7"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -4158,7 +4163,7 @@
       <c r="CK17" s="5"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
+      <c r="A18" s="7">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -4251,7 +4256,7 @@
       <c r="CK18" s="4"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9"/>
+      <c r="A19" s="7"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -4342,7 +4347,7 @@
       <c r="CK19" s="5"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
+      <c r="A20" s="7">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -4435,7 +4440,7 @@
       <c r="CK20" s="4"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
+      <c r="A21" s="7"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -4526,7 +4531,7 @@
       <c r="CK21" s="5"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
+      <c r="A22" s="7">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -4619,7 +4624,7 @@
       <c r="CK22" s="4"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
+      <c r="A23" s="7"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -4710,7 +4715,7 @@
       <c r="CK23" s="5"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
+      <c r="A24" s="7">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -4803,7 +4808,7 @@
       <c r="CK24" s="4"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
+      <c r="A25" s="7"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -4894,7 +4899,7 @@
       <c r="CK25" s="5"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9">
+      <c r="A26" s="7">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -4987,7 +4992,7 @@
       <c r="CK26" s="4"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="9"/>
+      <c r="A27" s="7"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -5078,7 +5083,7 @@
       <c r="CK27" s="5"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9">
+      <c r="A28" s="7">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -5171,7 +5176,7 @@
       <c r="CK28" s="4"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
+      <c r="A29" s="7"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -5262,7 +5267,7 @@
       <c r="CK29" s="5"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9">
+      <c r="A30" s="7">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -5355,7 +5360,7 @@
       <c r="CK30" s="4"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
+      <c r="A31" s="7"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -5446,7 +5451,7 @@
       <c r="CK31" s="5"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9">
+      <c r="A32" s="7">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -5539,7 +5544,7 @@
       <c r="CK32" s="4"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="9"/>
+      <c r="A33" s="7"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -5630,7 +5635,7 @@
       <c r="CK33" s="5"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9">
+      <c r="A34" s="7">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -5723,7 +5728,7 @@
       <c r="CK34" s="4"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
+      <c r="A35" s="7"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -5814,7 +5819,7 @@
       <c r="CK35" s="5"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9">
+      <c r="A36" s="7">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -5907,7 +5912,7 @@
       <c r="CK36" s="4"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -5998,7 +6003,7 @@
       <c r="CK37" s="5"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9">
+      <c r="A38" s="7">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -6091,7 +6096,7 @@
       <c r="CK38" s="4"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -6182,7 +6187,7 @@
       <c r="CK39" s="5"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9">
+      <c r="A40" s="7">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -6275,7 +6280,7 @@
       <c r="CK40" s="4"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -6366,7 +6371,7 @@
       <c r="CK41" s="5"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9">
+      <c r="A42" s="7">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -6459,7 +6464,7 @@
       <c r="CK42" s="4"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="9"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -6550,7 +6555,7 @@
       <c r="CK43" s="5"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9">
+      <c r="A44" s="7">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -6643,7 +6648,7 @@
       <c r="CK44" s="4"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="9"/>
+      <c r="A45" s="7"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -6734,7 +6739,7 @@
       <c r="CK45" s="5"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9">
+      <c r="A46" s="7">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -6827,7 +6832,7 @@
       <c r="CK46" s="4"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -6918,7 +6923,7 @@
       <c r="CK47" s="5"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9">
+      <c r="A48" s="7">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -7011,7 +7016,7 @@
       <c r="CK48" s="4"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
+      <c r="A49" s="7"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
@@ -7102,7 +7107,7 @@
       <c r="CK49" s="5"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9">
+      <c r="A50" s="7">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -7195,7 +7200,7 @@
       <c r="CK50" s="4"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="9"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -7286,7 +7291,7 @@
       <c r="CK51" s="5"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9">
+      <c r="A52" s="7">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -7379,7 +7384,7 @@
       <c r="CK52" s="4"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
+      <c r="A53" s="7"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -7470,7 +7475,7 @@
       <c r="CK53" s="5"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9">
+      <c r="A54" s="7">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -7563,7 +7568,7 @@
       <c r="CK54" s="4"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="9"/>
+      <c r="A55" s="7"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -7654,7 +7659,7 @@
       <c r="CK55" s="5"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="9">
+      <c r="A56" s="7">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -7747,7 +7752,7 @@
       <c r="CK56" s="4"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
+      <c r="A57" s="7"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -7838,7 +7843,7 @@
       <c r="CK57" s="5"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9">
+      <c r="A58" s="7">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -7931,7 +7936,7 @@
       <c r="CK58" s="4"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="9"/>
+      <c r="A59" s="7"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -8022,7 +8027,7 @@
       <c r="CK59" s="5"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9">
+      <c r="A60" s="7">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -8115,7 +8120,7 @@
       <c r="CK60" s="4"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="9"/>
+      <c r="A61" s="7"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -8206,7 +8211,7 @@
       <c r="CK61" s="5"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9">
+      <c r="A62" s="7">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -8299,7 +8304,7 @@
       <c r="CK62" s="4"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="9"/>
+      <c r="A63" s="7"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -8390,7 +8395,7 @@
       <c r="CK63" s="5"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="9">
+      <c r="A64" s="7">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -8483,7 +8488,7 @@
       <c r="CK64" s="4"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="9"/>
+      <c r="A65" s="7"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -8574,7 +8579,7 @@
       <c r="CK65" s="5"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9">
+      <c r="A66" s="7">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -8667,7 +8672,7 @@
       <c r="CK66" s="4"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="9"/>
+      <c r="A67" s="7"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -8758,7 +8763,7 @@
       <c r="CK67" s="5"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9">
+      <c r="A68" s="7">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -8851,7 +8856,7 @@
       <c r="CK68" s="4"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="9"/>
+      <c r="A69" s="7"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
@@ -8942,7 +8947,7 @@
       <c r="CK69" s="5"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9">
+      <c r="A70" s="7">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -9035,7 +9040,7 @@
       <c r="CK70" s="4"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="9"/>
+      <c r="A71" s="7"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -9126,7 +9131,7 @@
       <c r="CK71" s="5"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9">
+      <c r="A72" s="7">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -9219,7 +9224,7 @@
       <c r="CK72" s="4"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="9"/>
+      <c r="A73" s="7"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -9310,7 +9315,7 @@
       <c r="CK73" s="5"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9">
+      <c r="A74" s="7">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -9403,7 +9408,7 @@
       <c r="CK74" s="4"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="9"/>
+      <c r="A75" s="7"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -9494,7 +9499,7 @@
       <c r="CK75" s="5"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="9">
+      <c r="A76" s="7">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -9587,7 +9592,7 @@
       <c r="CK76" s="4"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="9"/>
+      <c r="A77" s="7"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -9678,7 +9683,7 @@
       <c r="CK77" s="5"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9">
+      <c r="A78" s="7">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -9771,7 +9776,7 @@
       <c r="CK78" s="4"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="9"/>
+      <c r="A79" s="7"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -9862,7 +9867,7 @@
       <c r="CK79" s="5"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="9">
+      <c r="A80" s="7">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -9955,7 +9960,7 @@
       <c r="CK80" s="4"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="9"/>
+      <c r="A81" s="7"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -10046,7 +10051,7 @@
       <c r="CK81" s="5"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9">
+      <c r="A82" s="7">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -10139,7 +10144,7 @@
       <c r="CK82" s="4"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="9"/>
+      <c r="A83" s="7"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
@@ -10230,7 +10235,7 @@
       <c r="CK83" s="5"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9">
+      <c r="A84" s="7">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -10323,7 +10328,7 @@
       <c r="CK84" s="4"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="9"/>
+      <c r="A85" s="7"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
@@ -10414,7 +10419,7 @@
       <c r="CK85" s="5"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9">
+      <c r="A86" s="7">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -10507,7 +10512,7 @@
       <c r="CK86" s="4"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="9"/>
+      <c r="A87" s="7"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
@@ -10598,7 +10603,7 @@
       <c r="CK87" s="5"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="9">
+      <c r="A88" s="7">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -10691,7 +10696,7 @@
       <c r="CK88" s="4"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="9"/>
+      <c r="A89" s="7"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
@@ -10782,7 +10787,7 @@
       <c r="CK89" s="5"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="9">
+      <c r="A90" s="7">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -10875,7 +10880,7 @@
       <c r="CK90" s="4"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="9"/>
+      <c r="A91" s="7"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -10966,7 +10971,7 @@
       <c r="CK91" s="5"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="9">
+      <c r="A92" s="7">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -11059,7 +11064,7 @@
       <c r="CK92" s="4"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="9"/>
+      <c r="A93" s="7"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -11150,7 +11155,7 @@
       <c r="CK93" s="5"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9">
+      <c r="A94" s="7">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -11243,7 +11248,7 @@
       <c r="CK94" s="4"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="9"/>
+      <c r="A95" s="7"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -11334,7 +11339,7 @@
       <c r="CK95" s="5"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="9">
+      <c r="A96" s="7">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -11427,7 +11432,7 @@
       <c r="CK96" s="4"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="9"/>
+      <c r="A97" s="7"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
       <c r="D97" s="5"/>
@@ -11518,7 +11523,7 @@
       <c r="CK97" s="5"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9">
+      <c r="A98" s="7">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -11611,7 +11616,7 @@
       <c r="CK98" s="4"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="9"/>
+      <c r="A99" s="7"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -11702,7 +11707,7 @@
       <c r="CK99" s="5"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="9">
+      <c r="A100" s="7">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -11795,7 +11800,7 @@
       <c r="CK100" s="4"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="9"/>
+      <c r="A101" s="7"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
@@ -11886,7 +11891,7 @@
       <c r="CK101" s="5"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="9">
+      <c r="A102" s="7">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -11979,7 +11984,7 @@
       <c r="CK102" s="4"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="9"/>
+      <c r="A103" s="7"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
@@ -12070,7 +12075,7 @@
       <c r="CK103" s="5"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="9">
+      <c r="A104" s="7">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -12163,7 +12168,7 @@
       <c r="CK104" s="4"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="9"/>
+      <c r="A105" s="7"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -12254,7 +12259,7 @@
       <c r="CK105" s="5"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="9">
+      <c r="A106" s="7">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -12347,7 +12352,7 @@
       <c r="CK106" s="4"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="9"/>
+      <c r="A107" s="7"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
       <c r="D107" s="5"/>
@@ -12438,7 +12443,7 @@
       <c r="CK107" s="5"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="9">
+      <c r="A108" s="7">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -12531,7 +12536,7 @@
       <c r="CK108" s="4"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="9"/>
+      <c r="A109" s="7"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -12622,7 +12627,7 @@
       <c r="CK109" s="5"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="9">
+      <c r="A110" s="7">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -12715,7 +12720,7 @@
       <c r="CK110" s="4"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="9"/>
+      <c r="A111" s="7"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
@@ -12806,7 +12811,7 @@
       <c r="CK111" s="5"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="9">
+      <c r="A112" s="7">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -12899,7 +12904,7 @@
       <c r="CK112" s="4"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="9"/>
+      <c r="A113" s="7"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
       <c r="D113" s="5"/>
@@ -12990,7 +12995,7 @@
       <c r="CK113" s="5"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="9">
+      <c r="A114" s="7">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -13083,7 +13088,7 @@
       <c r="CK114" s="4"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="9"/>
+      <c r="A115" s="7"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -13174,7 +13179,7 @@
       <c r="CK115" s="5"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="9">
+      <c r="A116" s="7">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -13267,7 +13272,7 @@
       <c r="CK116" s="4"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="9"/>
+      <c r="A117" s="7"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
@@ -13358,7 +13363,7 @@
       <c r="CK117" s="5"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="9">
+      <c r="A118" s="7">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -13451,7 +13456,7 @@
       <c r="CK118" s="4"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="9"/>
+      <c r="A119" s="7"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
@@ -13542,7 +13547,7 @@
       <c r="CK119" s="5"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="9">
+      <c r="A120" s="7">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -13635,7 +13640,7 @@
       <c r="CK120" s="4"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="9"/>
+      <c r="A121" s="7"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
@@ -13726,7 +13731,7 @@
       <c r="CK121" s="5"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="9">
+      <c r="A122" s="7">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -13819,7 +13824,7 @@
       <c r="CK122" s="4"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="9"/>
+      <c r="A123" s="7"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
@@ -13910,7 +13915,7 @@
       <c r="CK123" s="5"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="9">
+      <c r="A124" s="7">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -14003,7 +14008,7 @@
       <c r="CK124" s="4"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="9"/>
+      <c r="A125" s="7"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
@@ -14094,7 +14099,7 @@
       <c r="CK125" s="5"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="9">
+      <c r="A126" s="7">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -14187,7 +14192,7 @@
       <c r="CK126" s="4"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="9"/>
+      <c r="A127" s="7"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
@@ -14278,7 +14283,7 @@
       <c r="CK127" s="5"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="9">
+      <c r="A128" s="7">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -14371,7 +14376,7 @@
       <c r="CK128" s="4"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="9"/>
+      <c r="A129" s="7"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
@@ -14462,7 +14467,7 @@
       <c r="CK129" s="5"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="9">
+      <c r="A130" s="7">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -14555,7 +14560,7 @@
       <c r="CK130" s="4"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="9"/>
+      <c r="A131" s="7"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
@@ -14646,7 +14651,7 @@
       <c r="CK131" s="5"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="9">
+      <c r="A132" s="7">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -14739,7 +14744,7 @@
       <c r="CK132" s="4"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="9"/>
+      <c r="A133" s="7"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
@@ -14830,7 +14835,7 @@
       <c r="CK133" s="5"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="9">
+      <c r="A134" s="7">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -14923,7 +14928,7 @@
       <c r="CK134" s="4"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="9"/>
+      <c r="A135" s="7"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
@@ -15014,7 +15019,7 @@
       <c r="CK135" s="5"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="9">
+      <c r="A136" s="7">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -15107,7 +15112,7 @@
       <c r="CK136" s="4"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="9"/>
+      <c r="A137" s="7"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
       <c r="D137" s="5"/>
@@ -15198,7 +15203,7 @@
       <c r="CK137" s="5"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="9">
+      <c r="A138" s="7">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -15291,7 +15296,7 @@
       <c r="CK138" s="4"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="9"/>
+      <c r="A139" s="7"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
       <c r="D139" s="5"/>
@@ -15382,7 +15387,7 @@
       <c r="CK139" s="5"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="9">
+      <c r="A140" s="7">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -15475,7 +15480,7 @@
       <c r="CK140" s="4"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="9"/>
+      <c r="A141" s="7"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
       <c r="D141" s="5"/>
@@ -15566,7 +15571,7 @@
       <c r="CK141" s="5"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="9">
+      <c r="A142" s="7">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -15659,7 +15664,7 @@
       <c r="CK142" s="4"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="9"/>
+      <c r="A143" s="7"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
@@ -15750,7 +15755,7 @@
       <c r="CK143" s="5"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="9">
+      <c r="A144" s="7">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -15843,7 +15848,7 @@
       <c r="CK144" s="4"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="9"/>
+      <c r="A145" s="7"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
       <c r="D145" s="5"/>
@@ -15934,7 +15939,7 @@
       <c r="CK145" s="5"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="9">
+      <c r="A146" s="7">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -16027,7 +16032,7 @@
       <c r="CK146" s="4"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="9"/>
+      <c r="A147" s="7"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
       <c r="D147" s="5"/>
@@ -16118,7 +16123,7 @@
       <c r="CK147" s="5"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="9">
+      <c r="A148" s="7">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -16211,7 +16216,7 @@
       <c r="CK148" s="4"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="9"/>
+      <c r="A149" s="7"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
       <c r="D149" s="5"/>
@@ -16302,7 +16307,7 @@
       <c r="CK149" s="5"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="9">
+      <c r="A150" s="7">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -16395,7 +16400,7 @@
       <c r="CK150" s="4"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="9"/>
+      <c r="A151" s="7"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
       <c r="D151" s="5"/>
@@ -16486,7 +16491,7 @@
       <c r="CK151" s="5"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="9">
+      <c r="A152" s="7">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -16579,7 +16584,7 @@
       <c r="CK152" s="4"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="9"/>
+      <c r="A153" s="7"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
       <c r="D153" s="5"/>
@@ -16670,7 +16675,7 @@
       <c r="CK153" s="5"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="9">
+      <c r="A154" s="7">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -16763,7 +16768,7 @@
       <c r="CK154" s="4"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="9"/>
+      <c r="A155" s="7"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
       <c r="D155" s="5"/>
@@ -16854,7 +16859,7 @@
       <c r="CK155" s="5"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="9">
+      <c r="A156" s="7">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -16947,7 +16952,7 @@
       <c r="CK156" s="4"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="9"/>
+      <c r="A157" s="7"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
       <c r="D157" s="5"/>
@@ -17038,7 +17043,7 @@
       <c r="CK157" s="5"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="9">
+      <c r="A158" s="7">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -17131,7 +17136,7 @@
       <c r="CK158" s="4"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="9"/>
+      <c r="A159" s="7"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
       <c r="D159" s="5"/>
@@ -17222,7 +17227,7 @@
       <c r="CK159" s="5"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="9">
+      <c r="A160" s="7">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -17315,7 +17320,7 @@
       <c r="CK160" s="4"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="9"/>
+      <c r="A161" s="7"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
       <c r="D161" s="5"/>
@@ -17406,7 +17411,7 @@
       <c r="CK161" s="5"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="9">
+      <c r="A162" s="7">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -17499,7 +17504,7 @@
       <c r="CK162" s="4"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="9"/>
+      <c r="A163" s="7"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
@@ -17590,7 +17595,7 @@
       <c r="CK163" s="5"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="9">
+      <c r="A164" s="7">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -17683,7 +17688,7 @@
       <c r="CK164" s="4"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="9"/>
+      <c r="A165" s="7"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
@@ -17774,7 +17779,7 @@
       <c r="CK165" s="5"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="9">
+      <c r="A166" s="7">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -17867,7 +17872,7 @@
       <c r="CK166" s="4"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="9"/>
+      <c r="A167" s="7"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
@@ -17958,7 +17963,7 @@
       <c r="CK167" s="5"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="9">
+      <c r="A168" s="7">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -18051,7 +18056,7 @@
       <c r="CK168" s="4"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="9"/>
+      <c r="A169" s="7"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
@@ -18142,7 +18147,7 @@
       <c r="CK169" s="5"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="9">
+      <c r="A170" s="7">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -18235,7 +18240,7 @@
       <c r="CK170" s="4"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="9"/>
+      <c r="A171" s="7"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
@@ -18326,7 +18331,7 @@
       <c r="CK171" s="5"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="9">
+      <c r="A172" s="7">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -18419,7 +18424,7 @@
       <c r="CK172" s="4"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="9"/>
+      <c r="A173" s="7"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
@@ -18510,7 +18515,7 @@
       <c r="CK173" s="5"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="9">
+      <c r="A174" s="7">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -18603,7 +18608,7 @@
       <c r="CK174" s="4"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="9"/>
+      <c r="A175" s="7"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
       <c r="D175" s="5"/>
@@ -18694,7 +18699,7 @@
       <c r="CK175" s="5"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="9">
+      <c r="A176" s="7">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -18787,7 +18792,7 @@
       <c r="CK176" s="4"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="9"/>
+      <c r="A177" s="7"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
       <c r="D177" s="5"/>
@@ -18878,7 +18883,7 @@
       <c r="CK177" s="5"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="9">
+      <c r="A178" s="7">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -18971,7 +18976,7 @@
       <c r="CK178" s="4"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="9"/>
+      <c r="A179" s="7"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
       <c r="D179" s="5"/>
@@ -19062,7 +19067,7 @@
       <c r="CK179" s="5"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="9">
+      <c r="A180" s="7">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -19155,7 +19160,7 @@
       <c r="CK180" s="4"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="9"/>
+      <c r="A181" s="7"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
       <c r="D181" s="5"/>
@@ -19246,7 +19251,7 @@
       <c r="CK181" s="5"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="9">
+      <c r="A182" s="7">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -19339,7 +19344,7 @@
       <c r="CK182" s="4"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="9"/>
+      <c r="A183" s="7"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
       <c r="D183" s="5"/>
@@ -19430,7 +19435,7 @@
       <c r="CK183" s="5"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="9">
+      <c r="A184" s="7">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -19523,7 +19528,7 @@
       <c r="CK184" s="4"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="9"/>
+      <c r="A185" s="7"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
       <c r="D185" s="5"/>
@@ -19614,7 +19619,7 @@
       <c r="CK185" s="5"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="9">
+      <c r="A186" s="7">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -19707,7 +19712,7 @@
       <c r="CK186" s="4"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="9"/>
+      <c r="A187" s="7"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
       <c r="D187" s="5"/>
@@ -19798,7 +19803,7 @@
       <c r="CK187" s="5"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="9">
+      <c r="A188" s="7">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -19891,7 +19896,7 @@
       <c r="CK188" s="4"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="9"/>
+      <c r="A189" s="7"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
       <c r="D189" s="5"/>
@@ -19982,7 +19987,7 @@
       <c r="CK189" s="5"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="9">
+      <c r="A190" s="7">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -20075,7 +20080,7 @@
       <c r="CK190" s="4"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="9"/>
+      <c r="A191" s="7"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
@@ -20167,91 +20172,36 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="BN1:BO1"/>
+    <mergeCell ref="BP1:BQ1"/>
+    <mergeCell ref="BR1:BS1"/>
+    <mergeCell ref="CD1:CE1"/>
+    <mergeCell ref="CF1:CG1"/>
+    <mergeCell ref="CH1:CI1"/>
+    <mergeCell ref="CJ1:CK1"/>
+    <mergeCell ref="BT1:BU1"/>
+    <mergeCell ref="BV1:BW1"/>
+    <mergeCell ref="BX1:BY1"/>
+    <mergeCell ref="BZ1:CA1"/>
+    <mergeCell ref="CB1:CC1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -20276,36 +20226,91 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="BL1:BM1"/>
-    <mergeCell ref="BN1:BO1"/>
-    <mergeCell ref="BP1:BQ1"/>
-    <mergeCell ref="BR1:BS1"/>
-    <mergeCell ref="CD1:CE1"/>
-    <mergeCell ref="CF1:CG1"/>
-    <mergeCell ref="CH1:CI1"/>
-    <mergeCell ref="CJ1:CK1"/>
-    <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="BV1:BW1"/>
-    <mergeCell ref="BX1:BY1"/>
-    <mergeCell ref="BZ1:CA1"/>
-    <mergeCell ref="CB1:CC1"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A179"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>

--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87FED35-C8AF-4DEE-B249-5227B195F64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DB1067-6E6B-45CA-9023-8C09D4CFB2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="43200" windowHeight="23985" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -237,22 +237,22 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>57871</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>58434</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>124812</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFF9C972-3C66-F121-3141-A146972B26F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30878DD8-ABCD-EAF0-3825-5F0AD3098111}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -268,53 +268,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="906517" y="1510863"/>
-          <a:ext cx="2475251" cy="1964120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>58435</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>124811</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30878DD8-ABCD-EAF0-3825-5F0AD3098111}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="906518" y="3626069"/>
-          <a:ext cx="2475814" cy="1937845"/>
+          <a:off x="923192" y="3846635"/>
+          <a:ext cx="2520280" cy="1971196"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -607,227 +562,14 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="テキスト ボックス 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{192B7513-550F-159D-2B1F-9817EA75EC24}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3538904" y="1538653"/>
-          <a:ext cx="4769827" cy="2000251"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>RO-RL78-G12-R5F1026AASP (JP)</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>RL78/G12</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>を使いやすくしたものです。</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>OSHWLab</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>で設計データを公開中です。</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>画像をクリックすることで</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>OSHWLab</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>の当該のサイトに飛びます。</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>回路図もガーバーも</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>BOM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>もそこで手に入ります。</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>54</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>43961</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -842,8 +584,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3538904" y="3692769"/>
-          <a:ext cx="4769827" cy="1890346"/>
+          <a:off x="3538904" y="3846634"/>
+          <a:ext cx="4769827" cy="1846385"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1075,278 +817,23 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>54</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="テキスト ボックス 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB148A02-44C8-10FE-027E-7D7EB5D6D318}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3538904" y="5846885"/>
-          <a:ext cx="4769827" cy="1384788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>RO-3D-GEAR-FORGE (JP)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>Free</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>版の</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>DesignSpark</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t> Mechanical</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>でもインボリュート歯車を簡単に作ることができるソフトです。</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>Python</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>の</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>ファイルでできています。</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>画像をクリックすることで</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>GitHub</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>の当該のリポジトリに飛びます。</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-GB" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>82416</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>146538</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B29BEFD-53CB-498D-91F2-FC449692B0C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="923193" y="5846886"/>
-          <a:ext cx="2544261" cy="1377460"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>98426</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>58615</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>58614</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="13" name="図 12" descr="Image">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{587F590E-3D62-3C52-91F9-95E4800B37C7}"/>
@@ -1358,7 +845,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1372,7 +859,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="923192" y="7385539"/>
+          <a:off x="923192" y="8462596"/>
           <a:ext cx="2560272" cy="1904999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1396,14 +883,14 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>153864</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1418,7 +905,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3538904" y="7385538"/>
+          <a:off x="3538904" y="8462597"/>
           <a:ext cx="4769827" cy="1384788"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1642,14 +1129,14 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>153864</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1664,7 +1151,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8462596" y="1538654"/>
+          <a:off x="8462596" y="6154614"/>
           <a:ext cx="4769827" cy="2000251"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1774,14 +1261,14 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>43961</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1796,8 +1283,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8462596" y="3692769"/>
-          <a:ext cx="4769827" cy="1890346"/>
+          <a:off x="8462596" y="3846635"/>
+          <a:ext cx="4769827" cy="1846385"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1920,108 +1407,14 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="テキスト ボックス 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA8F5BF3-4A64-86DF-BD2E-AEA6CC3F6112}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8462596" y="5846885"/>
-          <a:ext cx="4769827" cy="1384788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>RO-3D-GEAR-FORGE (EN)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>This tool makes it easy to create involute gears, even with the free version of DesignSpark Mechanical.It is implemented as a single Python file.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>Click the image to open the corresponding GitHub repository.</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>55</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>86</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>153864</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2036,7 +1429,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8462596" y="7385538"/>
+          <a:off x="8462596" y="8308731"/>
           <a:ext cx="4769827" cy="1384788"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2145,7 +1538,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2175,6 +1568,1598 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="テキスト ボックス 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C22024A-72D4-4825-8453-C70AB79693A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3538904" y="10770577"/>
+          <a:ext cx="4769827" cy="1384788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO-3D-GEAR-FORGE (JP)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Free</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>版の</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>DesignSpark</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t> Mechanical</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>でもインボリュート歯車を簡単に作ることができるソフトです。</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Python</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>の</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>ファイルでできています。</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>画像をクリックすることで</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>GitHub</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>の当該のリポジトリに飛びます。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>7328</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2544261" cy="1377460"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3507AA73-B2AD-4FF9-9D2B-D65DDFDA55EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923192" y="10777905"/>
+          <a:ext cx="2544261" cy="1377460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>86</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="テキスト ボックス 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC93E0AA-FFB3-49B9-89C1-FE1DA2045AA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8462596" y="10770577"/>
+          <a:ext cx="4769827" cy="1384788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO-3D-GEAR-FORGE (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>This tool makes it easy to create involute gears, even with the free version of DesignSpark Mechanical.It is implemented as a single Python file.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Click the image to open the corresponding GitHub repository.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2519717" cy="2000249"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80EA0B74-60F5-4E55-AB72-A7C4709D7023}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923192" y="6154616"/>
+          <a:ext cx="2519717" cy="2000249"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>153864</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5055DA68-6CE3-4BD9-93F8-0052446CD4C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3538904" y="6154614"/>
+          <a:ext cx="4769827" cy="2000251"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO-RL78-G12-R5F1026AASP (JP)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RL78/G12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>を使いやすくしたものです。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>OSHWLab</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>で設計データを公開中です。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>画像をクリックすることで</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>OSHWLab</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>の当該のサイトに飛びます。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>回路図もガーバーも</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>BOM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>もそこで手に入ります。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>5578</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21" descr="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC43E71A-DD37-29E3-D6F9-AE8169BC196C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="923192" y="12463097"/>
+          <a:ext cx="2467424" cy="1846384"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="テキスト ボックス 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{571911C0-D62F-A6EE-4C6A-F7F2E9DF6D29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3538904" y="12463096"/>
+          <a:ext cx="4769827" cy="1384788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO (JP)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Excel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>方眼紙を</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>html</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>に変換する環境一式です</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>このサイトそのもの</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Excel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>ファイルを書いたら、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>make </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>一発で </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>html </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>になります。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Excel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>ファイルは個人情報が侵入しやすいので注意して利用してください。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>86</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="テキスト ボックス 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C36FA17-8593-F8E1-F9C3-09AE62D52F17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8462596" y="12463096"/>
+          <a:ext cx="4769827" cy="1384788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>EN</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>This is an environment for converting Excel Graph Paper(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>エクセル方眼紙</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>into HTML. This website itself is generated with this tool.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>After editing the Excel file, a single make command creates the</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>HTML.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Please use it carefully, as Excel files may contain personal information.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト ボックス 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F48567EA-BE33-A40F-214A-EF4F2F4AB7EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3538904" y="1692519"/>
+          <a:ext cx="4769827" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO-RL78-MAXV-LEARNING (JP)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>MAXV</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>で</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>JTAG</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>とデジタル回路を学習するための基板とソフト一式の設計情報です。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>最終的にはリーズナブルな価格で基板を配布する予定ですが、現時点で、基板に</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>バグが見つかっており、配布は</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>2,3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>か月先になりそうです。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>JTAG</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>が自在に使えると、開発効率が飛躍的に向上しますので、</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>JTAG</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>のインター</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>フェースを持つハードの開発をしている人は必見です。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>画像をクリックすることで</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>GitHub</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>の当該のリポジトリに飛びます</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>英語</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>88</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト ボックス 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67EFFC4-80AB-8472-DB48-0EA6E40E150B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8462596" y="1692519"/>
+          <a:ext cx="5077558" cy="2307981"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>RO-RL78-MAXV-LEARNING (EN)</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>This repository contains the hardware and software design files for learning JTAG and digital circuits with MAX V. The boards are planned to be distributed at a reasonable price, but a PCB bug has been found in the current revision. Distribution will probably be delayed by two to three months.JTAG can greatly improve development efficiency when used properly, so this project is recommended for anyone developing hardware with a JTAG interface.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>Click the image to open the corresponding GitHub repository.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-GB" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>49509</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="図 26">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9CD86EF-4B1C-4E79-BA22-B693CF6D1F8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="923192" y="1692519"/>
+          <a:ext cx="2511355" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -7039,7 +8024,7 @@
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
-      <c r="X49" s="6"/>
+      <c r="X49" s="5"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
@@ -7206,7 +8191,7 @@
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
-      <c r="G51"/>
+      <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -8327,7 +9312,7 @@
       <c r="U63" s="5"/>
       <c r="V63" s="5"/>
       <c r="W63" s="5"/>
-      <c r="X63" s="5"/>
+      <c r="X63" s="6"/>
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
       <c r="AA63" s="5"/>
@@ -10150,7 +11135,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
-      <c r="G83" s="5"/>
+      <c r="G83"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>

--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B1B8EA-F583-4607-85BF-F75518C289EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F9F1E8-EF98-4B7B-AB53-DB927D49E9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="63285" yWindow="3750" windowWidth="32310" windowHeight="23790" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="70125" yWindow="1290" windowWidth="25140" windowHeight="15000" activeTab="2" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -253,17 +253,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3641,14 +3641,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3666,7 +3666,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2000251" y="1846385"/>
+          <a:off x="1846384" y="1846385"/>
           <a:ext cx="1077058" cy="307730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3706,7 +3706,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>256server</a:t>
+            <a:t>256server.com</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3715,13 +3715,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>153865</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>59</xdr:col>
+      <xdr:col>68</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3739,8 +3739,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3077307" y="1846385"/>
-          <a:ext cx="6000751" cy="307730"/>
+          <a:off x="4154365" y="1846385"/>
+          <a:ext cx="6308481" cy="307730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3803,7 +3803,490 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>さんのサイト。物々交換も。</a:t>
+            <a:t>さん。物々交換も。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74F4CFE5-3EF7-98AF-2ECB-BAD403EA61B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1846384" y="2154116"/>
+          <a:ext cx="1077058" cy="307730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="sng">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>koko2rine.com</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>68</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>153864</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B8AB844-5066-D7C3-D482-100014928469}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4154365" y="2154115"/>
+          <a:ext cx="6308481" cy="307730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>知的な内容と淫夢要素が混ざった投稿をされるお方。懐かしい感じのサイトのデザインです。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>153864</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="テキスト ボックス 6">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA4CBB93-320E-8240-E8C7-E572504CE790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3077308" y="2154115"/>
+          <a:ext cx="1077058" cy="307730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="sng">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Wkoko2rine</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7E476E9-473D-120B-8110-E7B09A722646}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3077307" y="1846385"/>
+          <a:ext cx="1077058" cy="307730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" b="1" i="0" u="sng" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+              <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="">
+                <a:extLst>
+                  <a:ext uri="{A12FA001-AC4F-418D-AE19-62706E023703}">
+                    <ahyp:hlinkClr xmlns:ahyp="http://schemas.microsoft.com/office/drawing/2018/hyperlinkcolor" val="tx"/>
+                  </a:ext>
+                </a:extLst>
+              </a:hlinkClick>
+            </a:rPr>
+            <a:t>@256_daisuke</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0" u="sng" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="00B0F0"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="テキスト ボックス 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEBAB490-B62D-0FF5-6ACE-C753FC48C7A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1846386" y="1538653"/>
+          <a:ext cx="1077056" cy="307731"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Web site</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>2</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{774968E5-E39F-E061-36BD-4F51A990C797}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2923444" y="1538654"/>
+          <a:ext cx="1077056" cy="307731"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>𝕏</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0">
             <a:solidFill>
@@ -4153,185 +4636,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="16">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="16">
+      <c r="C1" s="16"/>
+      <c r="D1" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15">
         <v>4</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
         <v>5</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15">
         <v>6</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15">
         <v>7</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15">
         <v>10</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15">
         <v>11</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15">
         <v>12</v>
       </c>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
         <v>13</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15">
         <v>14</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16">
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15">
         <v>15</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16">
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15">
         <v>16</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
         <v>17</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16">
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15">
         <v>18</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15">
         <v>19</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15">
         <v>20</v>
       </c>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16">
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
         <v>21</v>
       </c>
-      <c r="AQ1" s="16"/>
-      <c r="AR1" s="16">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15">
         <v>22</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16">
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15">
         <v>23</v>
       </c>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16">
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15">
         <v>24</v>
       </c>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16">
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
         <v>25</v>
       </c>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15">
         <v>26</v>
       </c>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15">
         <v>27</v>
       </c>
-      <c r="BC1" s="16"/>
-      <c r="BD1" s="16">
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15">
         <v>28</v>
       </c>
-      <c r="BE1" s="16"/>
-      <c r="BF1" s="16">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
         <v>29</v>
       </c>
-      <c r="BG1" s="16"/>
-      <c r="BH1" s="16">
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15">
         <v>30</v>
       </c>
-      <c r="BI1" s="16"/>
-      <c r="BJ1" s="16">
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15">
         <v>31</v>
       </c>
-      <c r="BK1" s="16"/>
-      <c r="BL1" s="16">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15">
         <v>32</v>
       </c>
-      <c r="BM1" s="16"/>
-      <c r="BN1" s="16">
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
         <v>33</v>
       </c>
-      <c r="BO1" s="16"/>
-      <c r="BP1" s="16">
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15">
         <v>34</v>
       </c>
-      <c r="BQ1" s="16"/>
-      <c r="BR1" s="16">
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15">
         <v>35</v>
       </c>
-      <c r="BS1" s="16"/>
-      <c r="BT1" s="16">
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15">
         <v>36</v>
       </c>
-      <c r="BU1" s="16"/>
-      <c r="BV1" s="16">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
         <v>37</v>
       </c>
-      <c r="BW1" s="16"/>
-      <c r="BX1" s="16">
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15">
         <v>38</v>
       </c>
-      <c r="BY1" s="16"/>
-      <c r="BZ1" s="16">
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15">
         <v>39</v>
       </c>
-      <c r="CA1" s="16"/>
-      <c r="CB1" s="16">
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15">
         <v>40</v>
       </c>
-      <c r="CC1" s="16"/>
-      <c r="CD1" s="16">
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15">
         <v>41</v>
       </c>
-      <c r="CE1" s="16"/>
-      <c r="CF1" s="16">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15">
         <v>42</v>
       </c>
-      <c r="CG1" s="16"/>
-      <c r="CH1" s="16">
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15">
         <v>43</v>
       </c>
-      <c r="CI1" s="16"/>
-      <c r="CJ1" s="16">
+      <c r="CI1" s="15"/>
+      <c r="CJ1" s="15">
         <v>44</v>
       </c>
-      <c r="CK1" s="16"/>
+      <c r="CK1" s="15"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -4424,7 +4907,7 @@
       <c r="CK2" s="6"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9"/>
@@ -4515,7 +4998,7 @@
       <c r="CK3" s="10"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -4608,7 +5091,7 @@
       <c r="CK4" s="6"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="11"/>
@@ -4699,7 +5182,7 @@
       <c r="CK5" s="7"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -4792,7 +5275,7 @@
       <c r="CK6" s="6"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="7"/>
       <c r="D7" s="11"/>
@@ -4883,7 +5366,7 @@
       <c r="CK7" s="7"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -4976,7 +5459,7 @@
       <c r="CK8" s="6"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="11"/>
@@ -5069,7 +5552,7 @@
       <c r="CK9" s="7"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -5162,7 +5645,7 @@
       <c r="CK10" s="6"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="7"/>
       <c r="D11" s="11"/>
@@ -5253,7 +5736,7 @@
       <c r="CK11" s="7"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -5346,7 +5829,7 @@
       <c r="CK12" s="12"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11"/>
@@ -5437,7 +5920,7 @@
       <c r="CK13" s="7"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -5530,7 +6013,7 @@
       <c r="CK14" s="6"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="D15" s="11"/>
@@ -5621,7 +6104,7 @@
       <c r="CK15" s="7"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -5714,7 +6197,7 @@
       <c r="CK16" s="6"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="7"/>
       <c r="D17" s="11"/>
@@ -5805,7 +6288,7 @@
       <c r="CK17" s="7"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -5898,7 +6381,7 @@
       <c r="CK18" s="6"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="D19" s="11"/>
@@ -5989,7 +6472,7 @@
       <c r="CK19" s="7"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -6082,7 +6565,7 @@
       <c r="CK20" s="6"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5"/>
       <c r="C21" s="7"/>
       <c r="D21" s="9"/>
@@ -6173,7 +6656,7 @@
       <c r="CK21" s="7"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -6266,7 +6749,7 @@
       <c r="CK22" s="6"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5"/>
       <c r="C23" s="7"/>
       <c r="D23" s="11"/>
@@ -6357,7 +6840,7 @@
       <c r="CK23" s="7"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -6450,7 +6933,7 @@
       <c r="CK24" s="6"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="5"/>
       <c r="C25" s="7"/>
       <c r="D25" s="11"/>
@@ -6541,7 +7024,7 @@
       <c r="CK25" s="7"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -6634,7 +7117,7 @@
       <c r="CK26" s="6"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="11"/>
@@ -6725,7 +7208,7 @@
       <c r="CK27" s="7"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -6818,7 +7301,7 @@
       <c r="CK28" s="6"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="5"/>
       <c r="C29" s="7"/>
       <c r="D29" s="11"/>
@@ -6909,7 +7392,7 @@
       <c r="CK29" s="7"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -7002,7 +7485,7 @@
       <c r="CK30" s="6"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="5"/>
       <c r="C31" s="7"/>
       <c r="D31" s="11"/>
@@ -7093,7 +7576,7 @@
       <c r="CK31" s="7"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -7186,7 +7669,7 @@
       <c r="CK32" s="6"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="7"/>
       <c r="D33" s="11"/>
@@ -7277,7 +7760,7 @@
       <c r="CK33" s="7"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -7370,7 +7853,7 @@
       <c r="CK34" s="6"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="5"/>
       <c r="C35" s="7"/>
       <c r="D35" s="11"/>
@@ -7461,7 +7944,7 @@
       <c r="CK35" s="7"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -7554,7 +8037,7 @@
       <c r="CK36" s="6"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="11"/>
@@ -7645,7 +8128,7 @@
       <c r="CK37" s="7"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -7738,7 +8221,7 @@
       <c r="CK38" s="6"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="5"/>
       <c r="C39" s="7"/>
       <c r="D39" s="11"/>
@@ -7829,7 +8312,7 @@
       <c r="CK39" s="7"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -7922,7 +8405,7 @@
       <c r="CK40" s="6"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="5"/>
       <c r="C41" s="7"/>
       <c r="D41" s="11"/>
@@ -8013,7 +8496,7 @@
       <c r="CK41" s="7"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -8106,7 +8589,7 @@
       <c r="CK42" s="6"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="5"/>
       <c r="C43" s="7"/>
       <c r="D43" s="11"/>
@@ -8197,7 +8680,7 @@
       <c r="CK43" s="7"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -8290,7 +8773,7 @@
       <c r="CK44" s="6"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="5"/>
       <c r="C45" s="7"/>
       <c r="D45" s="11"/>
@@ -8381,7 +8864,7 @@
       <c r="CK45" s="7"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -8474,7 +8957,7 @@
       <c r="CK46" s="6"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="5"/>
       <c r="C47" s="7"/>
       <c r="D47" s="11"/>
@@ -8565,7 +9048,7 @@
       <c r="CK47" s="7"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="17">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -8658,7 +9141,7 @@
       <c r="CK48" s="6"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="5"/>
       <c r="C49" s="7"/>
       <c r="D49" s="11"/>
@@ -8749,7 +9232,7 @@
       <c r="CK49" s="7"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="17">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -8842,7 +9325,7 @@
       <c r="CK50" s="6"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="5"/>
       <c r="C51" s="7"/>
       <c r="D51" s="11"/>
@@ -8933,7 +9416,7 @@
       <c r="CK51" s="7"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="17">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -9026,7 +9509,7 @@
       <c r="CK52" s="6"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="5"/>
       <c r="C53" s="7"/>
       <c r="D53" s="11"/>
@@ -9117,7 +9600,7 @@
       <c r="CK53" s="7"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="17">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -9210,7 +9693,7 @@
       <c r="CK54" s="6"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
       <c r="D55" s="11"/>
@@ -9301,7 +9784,7 @@
       <c r="CK55" s="7"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="17">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -9394,7 +9877,7 @@
       <c r="CK56" s="6"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
       <c r="D57" s="11"/>
@@ -9485,7 +9968,7 @@
       <c r="CK57" s="7"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="17">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -9578,7 +10061,7 @@
       <c r="CK58" s="6"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
       <c r="D59" s="11"/>
@@ -9669,7 +10152,7 @@
       <c r="CK59" s="7"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="17">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -9762,7 +10245,7 @@
       <c r="CK60" s="6"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="5"/>
       <c r="C61" s="7"/>
       <c r="D61" s="11"/>
@@ -9853,7 +10336,7 @@
       <c r="CK61" s="7"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="17">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -9946,7 +10429,7 @@
       <c r="CK62" s="6"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="5"/>
       <c r="C63" s="7"/>
       <c r="D63" s="11"/>
@@ -10037,7 +10520,7 @@
       <c r="CK63" s="7"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -10130,7 +10613,7 @@
       <c r="CK64" s="6"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="5"/>
       <c r="C65" s="7"/>
       <c r="D65" s="11"/>
@@ -10221,7 +10704,7 @@
       <c r="CK65" s="7"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -10314,7 +10797,7 @@
       <c r="CK66" s="6"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="5"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
@@ -10405,7 +10888,7 @@
       <c r="CK67" s="7"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="17">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -10498,7 +10981,7 @@
       <c r="CK68" s="6"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="5"/>
       <c r="C69" s="7"/>
       <c r="D69" s="11"/>
@@ -10589,7 +11072,7 @@
       <c r="CK69" s="7"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="17">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -10682,7 +11165,7 @@
       <c r="CK70" s="6"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="5"/>
       <c r="C71" s="7"/>
       <c r="D71" s="11"/>
@@ -10773,7 +11256,7 @@
       <c r="CK71" s="7"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -10866,7 +11349,7 @@
       <c r="CK72" s="6"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="5"/>
       <c r="C73" s="7"/>
       <c r="D73" s="11"/>
@@ -10957,7 +11440,7 @@
       <c r="CK73" s="7"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="17">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -11050,7 +11533,7 @@
       <c r="CK74" s="6"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="5"/>
       <c r="C75" s="7"/>
       <c r="D75" s="11"/>
@@ -11141,7 +11624,7 @@
       <c r="CK75" s="7"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="17">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -11234,7 +11717,7 @@
       <c r="CK76" s="6"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="5"/>
       <c r="C77" s="7"/>
       <c r="D77" s="11"/>
@@ -11325,7 +11808,7 @@
       <c r="CK77" s="7"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="17">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -11418,7 +11901,7 @@
       <c r="CK78" s="6"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="5"/>
       <c r="C79" s="7"/>
       <c r="D79" s="11"/>
@@ -11509,7 +11992,7 @@
       <c r="CK79" s="7"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15">
+      <c r="A80" s="17">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -11602,7 +12085,7 @@
       <c r="CK80" s="6"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="5"/>
       <c r="C81" s="7"/>
       <c r="D81" s="11"/>
@@ -11693,7 +12176,7 @@
       <c r="CK81" s="7"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="17">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -11786,7 +12269,7 @@
       <c r="CK82" s="6"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="5"/>
       <c r="C83" s="7"/>
       <c r="D83" s="11"/>
@@ -11877,7 +12360,7 @@
       <c r="CK83" s="7"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="17">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -11970,7 +12453,7 @@
       <c r="CK84" s="6"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="5"/>
       <c r="C85" s="7"/>
       <c r="D85" s="11"/>
@@ -12061,7 +12544,7 @@
       <c r="CK85" s="7"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15">
+      <c r="A86" s="17">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -12154,7 +12637,7 @@
       <c r="CK86" s="6"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="5"/>
       <c r="C87" s="7"/>
       <c r="D87" s="11"/>
@@ -12245,7 +12728,7 @@
       <c r="CK87" s="7"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15">
+      <c r="A88" s="17">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -12338,7 +12821,7 @@
       <c r="CK88" s="6"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="5"/>
       <c r="C89" s="7"/>
       <c r="D89" s="11"/>
@@ -12429,7 +12912,7 @@
       <c r="CK89" s="7"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15">
+      <c r="A90" s="17">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -12522,7 +13005,7 @@
       <c r="CK90" s="6"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="5"/>
       <c r="C91" s="7"/>
       <c r="D91" s="11"/>
@@ -12613,7 +13096,7 @@
       <c r="CK91" s="7"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15">
+      <c r="A92" s="17">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -12706,7 +13189,7 @@
       <c r="CK92" s="6"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="5"/>
       <c r="C93" s="7"/>
       <c r="D93" s="11"/>
@@ -12797,7 +13280,7 @@
       <c r="CK93" s="7"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15">
+      <c r="A94" s="17">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -12890,7 +13373,7 @@
       <c r="CK94" s="6"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="5"/>
       <c r="C95" s="7"/>
       <c r="D95" s="11"/>
@@ -12981,7 +13464,7 @@
       <c r="CK95" s="7"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="17">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -13074,7 +13557,7 @@
       <c r="CK96" s="6"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="5"/>
       <c r="C97" s="7"/>
       <c r="D97" s="11"/>
@@ -13165,7 +13648,7 @@
       <c r="CK97" s="7"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="17">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -13258,7 +13741,7 @@
       <c r="CK98" s="6"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="5"/>
       <c r="C99" s="7"/>
       <c r="D99" s="11"/>
@@ -13349,7 +13832,7 @@
       <c r="CK99" s="7"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="17">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -13442,7 +13925,7 @@
       <c r="CK100" s="6"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="5"/>
       <c r="C101" s="7"/>
       <c r="D101" s="11"/>
@@ -13533,7 +14016,7 @@
       <c r="CK101" s="7"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="17">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -13626,7 +14109,7 @@
       <c r="CK102" s="6"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="5"/>
       <c r="C103" s="7"/>
       <c r="D103" s="11"/>
@@ -13717,7 +14200,7 @@
       <c r="CK103" s="7"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="17">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -13810,7 +14293,7 @@
       <c r="CK104" s="6"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="5"/>
       <c r="C105" s="7"/>
       <c r="D105" s="11"/>
@@ -13901,7 +14384,7 @@
       <c r="CK105" s="7"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="17">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -13994,7 +14477,7 @@
       <c r="CK106" s="6"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="5"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
@@ -14085,7 +14568,7 @@
       <c r="CK107" s="7"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="17">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -14178,7 +14661,7 @@
       <c r="CK108" s="6"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="5"/>
       <c r="C109" s="7"/>
       <c r="D109" s="11"/>
@@ -14269,7 +14752,7 @@
       <c r="CK109" s="7"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="17">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -14362,7 +14845,7 @@
       <c r="CK110" s="6"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="5"/>
       <c r="C111" s="7"/>
       <c r="D111" s="11"/>
@@ -14453,7 +14936,7 @@
       <c r="CK111" s="7"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="17">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -14546,7 +15029,7 @@
       <c r="CK112" s="6"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="5"/>
       <c r="C113" s="7"/>
       <c r="D113" s="11"/>
@@ -14637,7 +15120,7 @@
       <c r="CK113" s="7"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="17">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -14730,7 +15213,7 @@
       <c r="CK114" s="6"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="5"/>
       <c r="C115" s="7"/>
       <c r="D115" s="11"/>
@@ -14821,7 +15304,7 @@
       <c r="CK115" s="7"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="17">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -14914,7 +15397,7 @@
       <c r="CK116" s="6"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="5"/>
       <c r="C117" s="7"/>
       <c r="D117" s="11"/>
@@ -15005,7 +15488,7 @@
       <c r="CK117" s="7"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="17">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -15098,7 +15581,7 @@
       <c r="CK118" s="6"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="5"/>
       <c r="C119" s="7"/>
       <c r="D119" s="11"/>
@@ -15189,7 +15672,7 @@
       <c r="CK119" s="7"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="17">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -15282,7 +15765,7 @@
       <c r="CK120" s="6"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="5"/>
       <c r="C121" s="7"/>
       <c r="D121" s="11"/>
@@ -15373,7 +15856,7 @@
       <c r="CK121" s="7"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="17">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -15466,7 +15949,7 @@
       <c r="CK122" s="6"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="5"/>
       <c r="C123" s="7"/>
       <c r="D123" s="11"/>
@@ -15557,7 +16040,7 @@
       <c r="CK123" s="7"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="17">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -15650,7 +16133,7 @@
       <c r="CK124" s="6"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="5"/>
       <c r="C125" s="7"/>
       <c r="D125" s="11"/>
@@ -15741,7 +16224,7 @@
       <c r="CK125" s="7"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="17">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -15834,7 +16317,7 @@
       <c r="CK126" s="6"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="5"/>
       <c r="C127" s="7"/>
       <c r="D127" s="11"/>
@@ -15925,7 +16408,7 @@
       <c r="CK127" s="7"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="17">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -16018,7 +16501,7 @@
       <c r="CK128" s="6"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="5"/>
       <c r="C129" s="7"/>
       <c r="D129" s="11"/>
@@ -16109,7 +16592,7 @@
       <c r="CK129" s="7"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="17">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -16202,7 +16685,7 @@
       <c r="CK130" s="6"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="5"/>
       <c r="C131" s="7"/>
       <c r="D131" s="11"/>
@@ -16293,7 +16776,7 @@
       <c r="CK131" s="7"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="17">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -16386,7 +16869,7 @@
       <c r="CK132" s="6"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
       <c r="D133" s="11"/>
@@ -16477,7 +16960,7 @@
       <c r="CK133" s="7"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15">
+      <c r="A134" s="17">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -16570,7 +17053,7 @@
       <c r="CK134" s="6"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="5"/>
       <c r="C135" s="7"/>
       <c r="D135" s="11"/>
@@ -16661,7 +17144,7 @@
       <c r="CK135" s="7"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="17">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -16754,7 +17237,7 @@
       <c r="CK136" s="6"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
       <c r="D137" s="11"/>
@@ -16845,7 +17328,7 @@
       <c r="CK137" s="7"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="17">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -16938,7 +17421,7 @@
       <c r="CK138" s="6"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="5"/>
       <c r="C139" s="7"/>
       <c r="D139" s="11"/>
@@ -17029,7 +17512,7 @@
       <c r="CK139" s="7"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15">
+      <c r="A140" s="17">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -17122,7 +17605,7 @@
       <c r="CK140" s="6"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="5"/>
       <c r="C141" s="7"/>
       <c r="D141" s="11"/>
@@ -17213,7 +17696,7 @@
       <c r="CK141" s="7"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15">
+      <c r="A142" s="17">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -17306,7 +17789,7 @@
       <c r="CK142" s="6"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="5"/>
       <c r="C143" s="7"/>
       <c r="D143" s="11"/>
@@ -17397,7 +17880,7 @@
       <c r="CK143" s="7"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15">
+      <c r="A144" s="17">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -17490,7 +17973,7 @@
       <c r="CK144" s="6"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="5"/>
       <c r="C145" s="7"/>
       <c r="D145" s="11"/>
@@ -17581,7 +18064,7 @@
       <c r="CK145" s="7"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15">
+      <c r="A146" s="17">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -17674,7 +18157,7 @@
       <c r="CK146" s="6"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="5"/>
       <c r="C147" s="7"/>
       <c r="D147" s="11"/>
@@ -17765,7 +18248,7 @@
       <c r="CK147" s="7"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15">
+      <c r="A148" s="17">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -17858,7 +18341,7 @@
       <c r="CK148" s="6"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="5"/>
       <c r="C149" s="7"/>
       <c r="D149" s="11"/>
@@ -17949,7 +18432,7 @@
       <c r="CK149" s="7"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15">
+      <c r="A150" s="17">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -18042,7 +18525,7 @@
       <c r="CK150" s="6"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="5"/>
       <c r="C151" s="7"/>
       <c r="D151" s="11"/>
@@ -18133,7 +18616,7 @@
       <c r="CK151" s="7"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15">
+      <c r="A152" s="17">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -18226,7 +18709,7 @@
       <c r="CK152" s="6"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="5"/>
       <c r="C153" s="7"/>
       <c r="D153" s="11"/>
@@ -18317,7 +18800,7 @@
       <c r="CK153" s="7"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15">
+      <c r="A154" s="17">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -18410,7 +18893,7 @@
       <c r="CK154" s="6"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="5"/>
       <c r="C155" s="7"/>
       <c r="D155" s="11"/>
@@ -18501,7 +18984,7 @@
       <c r="CK155" s="7"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15">
+      <c r="A156" s="17">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -18594,7 +19077,7 @@
       <c r="CK156" s="6"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="5"/>
       <c r="C157" s="7"/>
       <c r="D157" s="11"/>
@@ -18685,7 +19168,7 @@
       <c r="CK157" s="7"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15">
+      <c r="A158" s="17">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -18778,7 +19261,7 @@
       <c r="CK158" s="6"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="5"/>
       <c r="C159" s="7"/>
       <c r="D159" s="11"/>
@@ -18869,7 +19352,7 @@
       <c r="CK159" s="7"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15">
+      <c r="A160" s="17">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -18962,7 +19445,7 @@
       <c r="CK160" s="6"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="5"/>
       <c r="C161" s="7"/>
       <c r="D161" s="11"/>
@@ -19053,7 +19536,7 @@
       <c r="CK161" s="7"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15">
+      <c r="A162" s="17">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -19146,7 +19629,7 @@
       <c r="CK162" s="6"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="5"/>
       <c r="C163" s="7"/>
       <c r="D163" s="11"/>
@@ -19237,7 +19720,7 @@
       <c r="CK163" s="7"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15">
+      <c r="A164" s="17">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -19330,7 +19813,7 @@
       <c r="CK164" s="6"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="5"/>
       <c r="C165" s="7"/>
       <c r="D165" s="11"/>
@@ -19421,7 +19904,7 @@
       <c r="CK165" s="7"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15">
+      <c r="A166" s="17">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -19514,7 +19997,7 @@
       <c r="CK166" s="6"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="5"/>
       <c r="C167" s="7"/>
       <c r="D167" s="11"/>
@@ -19605,7 +20088,7 @@
       <c r="CK167" s="7"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15">
+      <c r="A168" s="17">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -19698,7 +20181,7 @@
       <c r="CK168" s="6"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="5"/>
       <c r="C169" s="7"/>
       <c r="D169" s="11"/>
@@ -19789,7 +20272,7 @@
       <c r="CK169" s="7"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15">
+      <c r="A170" s="17">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -19882,7 +20365,7 @@
       <c r="CK170" s="6"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="5"/>
       <c r="C171" s="7"/>
       <c r="D171" s="11"/>
@@ -19973,7 +20456,7 @@
       <c r="CK171" s="7"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15">
+      <c r="A172" s="17">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -20066,7 +20549,7 @@
       <c r="CK172" s="6"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="5"/>
       <c r="C173" s="7"/>
       <c r="D173" s="11"/>
@@ -20157,7 +20640,7 @@
       <c r="CK173" s="7"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15">
+      <c r="A174" s="17">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -20250,7 +20733,7 @@
       <c r="CK174" s="6"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="5"/>
       <c r="C175" s="7"/>
       <c r="D175" s="11"/>
@@ -20341,7 +20824,7 @@
       <c r="CK175" s="7"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15">
+      <c r="A176" s="17">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -20434,7 +20917,7 @@
       <c r="CK176" s="6"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="5"/>
       <c r="C177" s="7"/>
       <c r="D177" s="11"/>
@@ -20525,7 +21008,7 @@
       <c r="CK177" s="7"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15">
+      <c r="A178" s="17">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -20618,7 +21101,7 @@
       <c r="CK178" s="6"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="5"/>
       <c r="C179" s="7"/>
       <c r="D179" s="11"/>
@@ -20709,7 +21192,7 @@
       <c r="CK179" s="7"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15">
+      <c r="A180" s="17">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -20802,7 +21285,7 @@
       <c r="CK180" s="6"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="5"/>
       <c r="C181" s="7"/>
       <c r="D181" s="11"/>
@@ -20893,7 +21376,7 @@
       <c r="CK181" s="7"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15">
+      <c r="A182" s="17">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -20986,7 +21469,7 @@
       <c r="CK182" s="6"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="5"/>
       <c r="C183" s="7"/>
       <c r="D183" s="11"/>
@@ -21077,7 +21560,7 @@
       <c r="CK183" s="7"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15">
+      <c r="A184" s="17">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -21170,7 +21653,7 @@
       <c r="CK184" s="6"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="5"/>
       <c r="C185" s="7"/>
       <c r="D185" s="11"/>
@@ -21261,7 +21744,7 @@
       <c r="CK185" s="7"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15">
+      <c r="A186" s="17">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -21354,7 +21837,7 @@
       <c r="CK186" s="6"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="5"/>
       <c r="C187" s="7"/>
       <c r="D187" s="11"/>
@@ -21445,7 +21928,7 @@
       <c r="CK187" s="7"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15">
+      <c r="A188" s="17">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -21538,7 +22021,7 @@
       <c r="CK188" s="6"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="5"/>
       <c r="C189" s="7"/>
       <c r="D189" s="11"/>
@@ -21629,7 +22112,7 @@
       <c r="CK189" s="7"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15">
+      <c r="A190" s="17">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -21722,7 +22205,7 @@
       <c r="CK190" s="6"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="5"/>
       <c r="C191" s="7"/>
       <c r="D191" s="11"/>
@@ -21814,36 +22297,91 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="BN1:BO1"/>
-    <mergeCell ref="BP1:BQ1"/>
-    <mergeCell ref="BR1:BS1"/>
-    <mergeCell ref="CD1:CE1"/>
-    <mergeCell ref="CF1:CG1"/>
-    <mergeCell ref="CH1:CI1"/>
-    <mergeCell ref="CJ1:CK1"/>
-    <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="BV1:BW1"/>
-    <mergeCell ref="BX1:BY1"/>
-    <mergeCell ref="BZ1:CA1"/>
-    <mergeCell ref="CB1:CC1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="BL1:BM1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -21868,91 +22406,36 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="BN1:BO1"/>
+    <mergeCell ref="BP1:BQ1"/>
+    <mergeCell ref="BR1:BS1"/>
+    <mergeCell ref="CD1:CE1"/>
+    <mergeCell ref="CF1:CG1"/>
+    <mergeCell ref="CH1:CI1"/>
+    <mergeCell ref="CJ1:CK1"/>
+    <mergeCell ref="BT1:BU1"/>
+    <mergeCell ref="BV1:BW1"/>
+    <mergeCell ref="BX1:BY1"/>
+    <mergeCell ref="BZ1:CA1"/>
+    <mergeCell ref="CB1:CC1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
@@ -21977,185 +22460,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="16">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="16">
+      <c r="C1" s="16"/>
+      <c r="D1" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15">
         <v>4</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
         <v>5</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15">
         <v>6</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15">
         <v>7</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15">
         <v>10</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15">
         <v>11</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15">
         <v>12</v>
       </c>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
         <v>13</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15">
         <v>14</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16">
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15">
         <v>15</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16">
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15">
         <v>16</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
         <v>17</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16">
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15">
         <v>18</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15">
         <v>19</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15">
         <v>20</v>
       </c>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16">
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
         <v>21</v>
       </c>
-      <c r="AQ1" s="16"/>
-      <c r="AR1" s="16">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15">
         <v>22</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16">
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15">
         <v>23</v>
       </c>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16">
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15">
         <v>24</v>
       </c>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16">
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
         <v>25</v>
       </c>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15">
         <v>26</v>
       </c>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15">
         <v>27</v>
       </c>
-      <c r="BC1" s="16"/>
-      <c r="BD1" s="16">
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15">
         <v>28</v>
       </c>
-      <c r="BE1" s="16"/>
-      <c r="BF1" s="16">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
         <v>29</v>
       </c>
-      <c r="BG1" s="16"/>
-      <c r="BH1" s="16">
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15">
         <v>30</v>
       </c>
-      <c r="BI1" s="16"/>
-      <c r="BJ1" s="16">
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15">
         <v>31</v>
       </c>
-      <c r="BK1" s="16"/>
-      <c r="BL1" s="16">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15">
         <v>32</v>
       </c>
-      <c r="BM1" s="16"/>
-      <c r="BN1" s="16">
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
         <v>33</v>
       </c>
-      <c r="BO1" s="16"/>
-      <c r="BP1" s="16">
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15">
         <v>34</v>
       </c>
-      <c r="BQ1" s="16"/>
-      <c r="BR1" s="16">
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15">
         <v>35</v>
       </c>
-      <c r="BS1" s="16"/>
-      <c r="BT1" s="16">
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15">
         <v>36</v>
       </c>
-      <c r="BU1" s="16"/>
-      <c r="BV1" s="16">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
         <v>37</v>
       </c>
-      <c r="BW1" s="16"/>
-      <c r="BX1" s="16">
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15">
         <v>38</v>
       </c>
-      <c r="BY1" s="16"/>
-      <c r="BZ1" s="16">
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15">
         <v>39</v>
       </c>
-      <c r="CA1" s="16"/>
-      <c r="CB1" s="16">
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15">
         <v>40</v>
       </c>
-      <c r="CC1" s="16"/>
-      <c r="CD1" s="16">
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15">
         <v>41</v>
       </c>
-      <c r="CE1" s="16"/>
-      <c r="CF1" s="16">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15">
         <v>42</v>
       </c>
-      <c r="CG1" s="16"/>
-      <c r="CH1" s="16">
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15">
         <v>43</v>
       </c>
-      <c r="CI1" s="16"/>
-      <c r="CJ1" s="16">
+      <c r="CI1" s="15"/>
+      <c r="CJ1" s="15">
         <v>44</v>
       </c>
-      <c r="CK1" s="16"/>
+      <c r="CK1" s="15"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -22248,7 +22731,7 @@
       <c r="CK2" s="6"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9"/>
@@ -22339,7 +22822,7 @@
       <c r="CK3" s="10"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -22432,7 +22915,7 @@
       <c r="CK4" s="6"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="11"/>
@@ -22523,7 +23006,7 @@
       <c r="CK5" s="7"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -22616,7 +23099,7 @@
       <c r="CK6" s="6"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="7"/>
       <c r="D7" s="11"/>
@@ -22707,7 +23190,7 @@
       <c r="CK7" s="7"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -22800,7 +23283,7 @@
       <c r="CK8" s="6"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="11"/>
@@ -22891,7 +23374,7 @@
       <c r="CK9" s="7"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -22984,7 +23467,7 @@
       <c r="CK10" s="6"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="7"/>
       <c r="D11" s="11"/>
@@ -23075,7 +23558,7 @@
       <c r="CK11" s="7"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -23168,7 +23651,7 @@
       <c r="CK12" s="12"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11"/>
@@ -23259,7 +23742,7 @@
       <c r="CK13" s="7"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -23352,7 +23835,7 @@
       <c r="CK14" s="6"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="D15" s="11"/>
@@ -23443,7 +23926,7 @@
       <c r="CK15" s="7"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -23536,7 +24019,7 @@
       <c r="CK16" s="6"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="7"/>
       <c r="D17" s="11"/>
@@ -23627,7 +24110,7 @@
       <c r="CK17" s="7"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -23720,7 +24203,7 @@
       <c r="CK18" s="6"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="D19" s="11"/>
@@ -23811,7 +24294,7 @@
       <c r="CK19" s="7"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -23904,7 +24387,7 @@
       <c r="CK20" s="6"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5"/>
       <c r="C21" s="7"/>
       <c r="D21" s="9"/>
@@ -23995,7 +24478,7 @@
       <c r="CK21" s="7"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -24088,7 +24571,7 @@
       <c r="CK22" s="6"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5"/>
       <c r="C23" s="7"/>
       <c r="D23" s="11"/>
@@ -24179,7 +24662,7 @@
       <c r="CK23" s="7"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -24272,7 +24755,7 @@
       <c r="CK24" s="6"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="5"/>
       <c r="C25" s="7"/>
       <c r="D25" s="11"/>
@@ -24363,7 +24846,7 @@
       <c r="CK25" s="7"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -24456,7 +24939,7 @@
       <c r="CK26" s="6"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="11"/>
@@ -24547,7 +25030,7 @@
       <c r="CK27" s="7"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -24640,7 +25123,7 @@
       <c r="CK28" s="6"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="5"/>
       <c r="C29" s="7"/>
       <c r="D29" s="11"/>
@@ -24731,7 +25214,7 @@
       <c r="CK29" s="7"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -24824,7 +25307,7 @@
       <c r="CK30" s="6"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="5"/>
       <c r="C31" s="7"/>
       <c r="D31" s="11"/>
@@ -24915,7 +25398,7 @@
       <c r="CK31" s="7"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -25008,7 +25491,7 @@
       <c r="CK32" s="6"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="7"/>
       <c r="D33" s="11"/>
@@ -25099,7 +25582,7 @@
       <c r="CK33" s="7"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -25192,7 +25675,7 @@
       <c r="CK34" s="6"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="5"/>
       <c r="C35" s="7"/>
       <c r="D35" s="11"/>
@@ -25283,7 +25766,7 @@
       <c r="CK35" s="7"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -25376,7 +25859,7 @@
       <c r="CK36" s="6"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="11"/>
@@ -25467,7 +25950,7 @@
       <c r="CK37" s="7"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -25560,7 +26043,7 @@
       <c r="CK38" s="6"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="5"/>
       <c r="C39" s="7"/>
       <c r="D39" s="11"/>
@@ -25651,7 +26134,7 @@
       <c r="CK39" s="7"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -25744,7 +26227,7 @@
       <c r="CK40" s="6"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="5"/>
       <c r="C41" s="7"/>
       <c r="D41" s="11"/>
@@ -25835,7 +26318,7 @@
       <c r="CK41" s="7"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -25928,7 +26411,7 @@
       <c r="CK42" s="6"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="5"/>
       <c r="C43" s="7"/>
       <c r="D43" s="11"/>
@@ -26019,7 +26502,7 @@
       <c r="CK43" s="7"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -26112,7 +26595,7 @@
       <c r="CK44" s="6"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="5"/>
       <c r="C45" s="7"/>
       <c r="D45" s="11"/>
@@ -26203,7 +26686,7 @@
       <c r="CK45" s="7"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -26296,7 +26779,7 @@
       <c r="CK46" s="6"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="5"/>
       <c r="C47" s="7"/>
       <c r="D47" s="11"/>
@@ -26387,7 +26870,7 @@
       <c r="CK47" s="7"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="17">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -26480,7 +26963,7 @@
       <c r="CK48" s="6"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="5"/>
       <c r="C49" s="7"/>
       <c r="D49" s="11"/>
@@ -26571,7 +27054,7 @@
       <c r="CK49" s="7"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="17">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -26664,7 +27147,7 @@
       <c r="CK50" s="6"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="5"/>
       <c r="C51" s="7"/>
       <c r="D51" s="11"/>
@@ -26755,7 +27238,7 @@
       <c r="CK51" s="7"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="17">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -26848,7 +27331,7 @@
       <c r="CK52" s="6"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="5"/>
       <c r="C53" s="7"/>
       <c r="D53" s="11"/>
@@ -26939,7 +27422,7 @@
       <c r="CK53" s="7"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="17">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -27032,7 +27515,7 @@
       <c r="CK54" s="6"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
       <c r="D55" s="11"/>
@@ -27123,7 +27606,7 @@
       <c r="CK55" s="7"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="17">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -27216,7 +27699,7 @@
       <c r="CK56" s="6"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
       <c r="D57" s="11"/>
@@ -27307,7 +27790,7 @@
       <c r="CK57" s="7"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="17">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -27400,7 +27883,7 @@
       <c r="CK58" s="6"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
       <c r="D59" s="11"/>
@@ -27491,7 +27974,7 @@
       <c r="CK59" s="7"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="17">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -27584,7 +28067,7 @@
       <c r="CK60" s="6"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="5"/>
       <c r="C61" s="7"/>
       <c r="D61" s="11"/>
@@ -27675,7 +28158,7 @@
       <c r="CK61" s="7"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="17">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -27768,7 +28251,7 @@
       <c r="CK62" s="6"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="5"/>
       <c r="C63" s="7"/>
       <c r="D63" s="11"/>
@@ -27859,7 +28342,7 @@
       <c r="CK63" s="7"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -27952,7 +28435,7 @@
       <c r="CK64" s="6"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="5"/>
       <c r="C65" s="7"/>
       <c r="D65" s="11"/>
@@ -28043,7 +28526,7 @@
       <c r="CK65" s="7"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -28136,7 +28619,7 @@
       <c r="CK66" s="6"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="5"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
@@ -28227,7 +28710,7 @@
       <c r="CK67" s="7"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="17">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -28320,7 +28803,7 @@
       <c r="CK68" s="6"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="5"/>
       <c r="C69" s="7"/>
       <c r="D69" s="11"/>
@@ -28411,7 +28894,7 @@
       <c r="CK69" s="7"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="17">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -28504,7 +28987,7 @@
       <c r="CK70" s="6"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="5"/>
       <c r="C71" s="7"/>
       <c r="D71" s="11"/>
@@ -28595,7 +29078,7 @@
       <c r="CK71" s="7"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -28688,7 +29171,7 @@
       <c r="CK72" s="6"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="5"/>
       <c r="C73" s="7"/>
       <c r="D73" s="11"/>
@@ -28779,7 +29262,7 @@
       <c r="CK73" s="7"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="17">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -28872,7 +29355,7 @@
       <c r="CK74" s="6"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="5"/>
       <c r="C75" s="7"/>
       <c r="D75" s="11"/>
@@ -28963,7 +29446,7 @@
       <c r="CK75" s="7"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="17">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -29056,7 +29539,7 @@
       <c r="CK76" s="6"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="5"/>
       <c r="C77" s="7"/>
       <c r="D77" s="11"/>
@@ -29147,7 +29630,7 @@
       <c r="CK77" s="7"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="17">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -29240,7 +29723,7 @@
       <c r="CK78" s="6"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="5"/>
       <c r="C79" s="7"/>
       <c r="D79" s="11"/>
@@ -29331,7 +29814,7 @@
       <c r="CK79" s="7"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15">
+      <c r="A80" s="17">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -29424,7 +29907,7 @@
       <c r="CK80" s="6"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="5"/>
       <c r="C81" s="7"/>
       <c r="D81" s="11"/>
@@ -29515,7 +29998,7 @@
       <c r="CK81" s="7"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="17">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -29608,7 +30091,7 @@
       <c r="CK82" s="6"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="5"/>
       <c r="C83" s="7"/>
       <c r="D83" s="11"/>
@@ -29699,7 +30182,7 @@
       <c r="CK83" s="7"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="17">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -29792,7 +30275,7 @@
       <c r="CK84" s="6"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="5"/>
       <c r="C85" s="7"/>
       <c r="D85" s="11"/>
@@ -29883,7 +30366,7 @@
       <c r="CK85" s="7"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15">
+      <c r="A86" s="17">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -29976,7 +30459,7 @@
       <c r="CK86" s="6"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="5"/>
       <c r="C87" s="7"/>
       <c r="D87" s="11"/>
@@ -30067,7 +30550,7 @@
       <c r="CK87" s="7"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15">
+      <c r="A88" s="17">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -30160,7 +30643,7 @@
       <c r="CK88" s="6"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="5"/>
       <c r="C89" s="7"/>
       <c r="D89" s="11"/>
@@ -30251,7 +30734,7 @@
       <c r="CK89" s="7"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15">
+      <c r="A90" s="17">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -30344,7 +30827,7 @@
       <c r="CK90" s="6"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="5"/>
       <c r="C91" s="7"/>
       <c r="D91" s="11"/>
@@ -30435,7 +30918,7 @@
       <c r="CK91" s="7"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15">
+      <c r="A92" s="17">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -30528,7 +31011,7 @@
       <c r="CK92" s="6"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="5"/>
       <c r="C93" s="7"/>
       <c r="D93" s="11"/>
@@ -30619,7 +31102,7 @@
       <c r="CK93" s="7"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15">
+      <c r="A94" s="17">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -30712,7 +31195,7 @@
       <c r="CK94" s="6"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="5"/>
       <c r="C95" s="7"/>
       <c r="D95" s="11"/>
@@ -30803,7 +31286,7 @@
       <c r="CK95" s="7"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="17">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -30896,7 +31379,7 @@
       <c r="CK96" s="6"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="5"/>
       <c r="C97" s="7"/>
       <c r="D97" s="11"/>
@@ -30987,7 +31470,7 @@
       <c r="CK97" s="7"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="17">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -31080,7 +31563,7 @@
       <c r="CK98" s="6"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="5"/>
       <c r="C99" s="7"/>
       <c r="D99" s="11"/>
@@ -31171,7 +31654,7 @@
       <c r="CK99" s="7"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="17">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -31264,7 +31747,7 @@
       <c r="CK100" s="6"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="5"/>
       <c r="C101" s="7"/>
       <c r="D101" s="11"/>
@@ -31355,7 +31838,7 @@
       <c r="CK101" s="7"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="17">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -31448,7 +31931,7 @@
       <c r="CK102" s="6"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="5"/>
       <c r="C103" s="7"/>
       <c r="D103" s="11"/>
@@ -31539,7 +32022,7 @@
       <c r="CK103" s="7"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="17">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -31632,7 +32115,7 @@
       <c r="CK104" s="6"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="5"/>
       <c r="C105" s="7"/>
       <c r="D105" s="11"/>
@@ -31723,7 +32206,7 @@
       <c r="CK105" s="7"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="17">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -31816,7 +32299,7 @@
       <c r="CK106" s="6"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="5"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
@@ -31907,7 +32390,7 @@
       <c r="CK107" s="7"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="17">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -32000,7 +32483,7 @@
       <c r="CK108" s="6"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="5"/>
       <c r="C109" s="7"/>
       <c r="D109" s="11"/>
@@ -32091,7 +32574,7 @@
       <c r="CK109" s="7"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="17">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -32184,7 +32667,7 @@
       <c r="CK110" s="6"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="5"/>
       <c r="C111" s="7"/>
       <c r="D111" s="11"/>
@@ -32275,7 +32758,7 @@
       <c r="CK111" s="7"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="17">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -32368,7 +32851,7 @@
       <c r="CK112" s="6"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="5"/>
       <c r="C113" s="7"/>
       <c r="D113" s="11"/>
@@ -32459,7 +32942,7 @@
       <c r="CK113" s="7"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="17">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -32552,7 +33035,7 @@
       <c r="CK114" s="6"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="5"/>
       <c r="C115" s="7"/>
       <c r="D115" s="11"/>
@@ -32643,7 +33126,7 @@
       <c r="CK115" s="7"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="17">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -32736,7 +33219,7 @@
       <c r="CK116" s="6"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="5"/>
       <c r="C117" s="7"/>
       <c r="D117" s="11"/>
@@ -32827,7 +33310,7 @@
       <c r="CK117" s="7"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="17">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -32920,7 +33403,7 @@
       <c r="CK118" s="6"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="5"/>
       <c r="C119" s="7"/>
       <c r="D119" s="11"/>
@@ -33011,7 +33494,7 @@
       <c r="CK119" s="7"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="17">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -33104,7 +33587,7 @@
       <c r="CK120" s="6"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="5"/>
       <c r="C121" s="7"/>
       <c r="D121" s="11"/>
@@ -33195,7 +33678,7 @@
       <c r="CK121" s="7"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="17">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -33288,7 +33771,7 @@
       <c r="CK122" s="6"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="5"/>
       <c r="C123" s="7"/>
       <c r="D123" s="11"/>
@@ -33379,7 +33862,7 @@
       <c r="CK123" s="7"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="17">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -33472,7 +33955,7 @@
       <c r="CK124" s="6"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="5"/>
       <c r="C125" s="7"/>
       <c r="D125" s="11"/>
@@ -33563,7 +34046,7 @@
       <c r="CK125" s="7"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="17">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -33656,7 +34139,7 @@
       <c r="CK126" s="6"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="5"/>
       <c r="C127" s="7"/>
       <c r="D127" s="11"/>
@@ -33747,7 +34230,7 @@
       <c r="CK127" s="7"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="17">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -33840,7 +34323,7 @@
       <c r="CK128" s="6"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="5"/>
       <c r="C129" s="7"/>
       <c r="D129" s="11"/>
@@ -33931,7 +34414,7 @@
       <c r="CK129" s="7"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="17">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -34024,7 +34507,7 @@
       <c r="CK130" s="6"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="5"/>
       <c r="C131" s="7"/>
       <c r="D131" s="11"/>
@@ -34115,7 +34598,7 @@
       <c r="CK131" s="7"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="17">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -34208,7 +34691,7 @@
       <c r="CK132" s="6"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
       <c r="D133" s="11"/>
@@ -34299,7 +34782,7 @@
       <c r="CK133" s="7"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15">
+      <c r="A134" s="17">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -34392,7 +34875,7 @@
       <c r="CK134" s="6"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="5"/>
       <c r="C135" s="7"/>
       <c r="D135" s="11"/>
@@ -34483,7 +34966,7 @@
       <c r="CK135" s="7"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="17">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -34576,7 +35059,7 @@
       <c r="CK136" s="6"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
       <c r="D137" s="11"/>
@@ -34667,7 +35150,7 @@
       <c r="CK137" s="7"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="17">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -34760,7 +35243,7 @@
       <c r="CK138" s="6"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="5"/>
       <c r="C139" s="7"/>
       <c r="D139" s="11"/>
@@ -34851,7 +35334,7 @@
       <c r="CK139" s="7"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15">
+      <c r="A140" s="17">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -34944,7 +35427,7 @@
       <c r="CK140" s="6"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="5"/>
       <c r="C141" s="7"/>
       <c r="D141" s="11"/>
@@ -35035,7 +35518,7 @@
       <c r="CK141" s="7"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15">
+      <c r="A142" s="17">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -35128,7 +35611,7 @@
       <c r="CK142" s="6"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="5"/>
       <c r="C143" s="7"/>
       <c r="D143" s="11"/>
@@ -35219,7 +35702,7 @@
       <c r="CK143" s="7"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15">
+      <c r="A144" s="17">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -35312,7 +35795,7 @@
       <c r="CK144" s="6"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="5"/>
       <c r="C145" s="7"/>
       <c r="D145" s="11"/>
@@ -35403,7 +35886,7 @@
       <c r="CK145" s="7"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15">
+      <c r="A146" s="17">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -35496,7 +35979,7 @@
       <c r="CK146" s="6"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="5"/>
       <c r="C147" s="7"/>
       <c r="D147" s="11"/>
@@ -35587,7 +36070,7 @@
       <c r="CK147" s="7"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15">
+      <c r="A148" s="17">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -35680,7 +36163,7 @@
       <c r="CK148" s="6"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="5"/>
       <c r="C149" s="7"/>
       <c r="D149" s="11"/>
@@ -35771,7 +36254,7 @@
       <c r="CK149" s="7"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15">
+      <c r="A150" s="17">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -35864,7 +36347,7 @@
       <c r="CK150" s="6"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="5"/>
       <c r="C151" s="7"/>
       <c r="D151" s="11"/>
@@ -35955,7 +36438,7 @@
       <c r="CK151" s="7"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15">
+      <c r="A152" s="17">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -36048,7 +36531,7 @@
       <c r="CK152" s="6"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="5"/>
       <c r="C153" s="7"/>
       <c r="D153" s="11"/>
@@ -36139,7 +36622,7 @@
       <c r="CK153" s="7"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15">
+      <c r="A154" s="17">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -36232,7 +36715,7 @@
       <c r="CK154" s="6"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="5"/>
       <c r="C155" s="7"/>
       <c r="D155" s="11"/>
@@ -36323,7 +36806,7 @@
       <c r="CK155" s="7"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15">
+      <c r="A156" s="17">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -36416,7 +36899,7 @@
       <c r="CK156" s="6"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="5"/>
       <c r="C157" s="7"/>
       <c r="D157" s="11"/>
@@ -36507,7 +36990,7 @@
       <c r="CK157" s="7"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15">
+      <c r="A158" s="17">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -36600,7 +37083,7 @@
       <c r="CK158" s="6"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="5"/>
       <c r="C159" s="7"/>
       <c r="D159" s="11"/>
@@ -36691,7 +37174,7 @@
       <c r="CK159" s="7"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15">
+      <c r="A160" s="17">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -36784,7 +37267,7 @@
       <c r="CK160" s="6"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="5"/>
       <c r="C161" s="7"/>
       <c r="D161" s="11"/>
@@ -36875,7 +37358,7 @@
       <c r="CK161" s="7"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15">
+      <c r="A162" s="17">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -36968,7 +37451,7 @@
       <c r="CK162" s="6"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="5"/>
       <c r="C163" s="7"/>
       <c r="D163" s="11"/>
@@ -37059,7 +37542,7 @@
       <c r="CK163" s="7"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15">
+      <c r="A164" s="17">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -37152,7 +37635,7 @@
       <c r="CK164" s="6"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="5"/>
       <c r="C165" s="7"/>
       <c r="D165" s="11"/>
@@ -37243,7 +37726,7 @@
       <c r="CK165" s="7"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15">
+      <c r="A166" s="17">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -37336,7 +37819,7 @@
       <c r="CK166" s="6"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="5"/>
       <c r="C167" s="7"/>
       <c r="D167" s="11"/>
@@ -37427,7 +37910,7 @@
       <c r="CK167" s="7"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15">
+      <c r="A168" s="17">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -37520,7 +38003,7 @@
       <c r="CK168" s="6"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="5"/>
       <c r="C169" s="7"/>
       <c r="D169" s="11"/>
@@ -37611,7 +38094,7 @@
       <c r="CK169" s="7"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15">
+      <c r="A170" s="17">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -37704,7 +38187,7 @@
       <c r="CK170" s="6"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="5"/>
       <c r="C171" s="7"/>
       <c r="D171" s="11"/>
@@ -37795,7 +38278,7 @@
       <c r="CK171" s="7"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15">
+      <c r="A172" s="17">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -37888,7 +38371,7 @@
       <c r="CK172" s="6"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="5"/>
       <c r="C173" s="7"/>
       <c r="D173" s="11"/>
@@ -37979,7 +38462,7 @@
       <c r="CK173" s="7"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15">
+      <c r="A174" s="17">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -38072,7 +38555,7 @@
       <c r="CK174" s="6"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="5"/>
       <c r="C175" s="7"/>
       <c r="D175" s="11"/>
@@ -38163,7 +38646,7 @@
       <c r="CK175" s="7"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15">
+      <c r="A176" s="17">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -38256,7 +38739,7 @@
       <c r="CK176" s="6"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="5"/>
       <c r="C177" s="7"/>
       <c r="D177" s="11"/>
@@ -38347,7 +38830,7 @@
       <c r="CK177" s="7"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15">
+      <c r="A178" s="17">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -38440,7 +38923,7 @@
       <c r="CK178" s="6"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="5"/>
       <c r="C179" s="7"/>
       <c r="D179" s="11"/>
@@ -38531,7 +39014,7 @@
       <c r="CK179" s="7"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15">
+      <c r="A180" s="17">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -38624,7 +39107,7 @@
       <c r="CK180" s="6"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="5"/>
       <c r="C181" s="7"/>
       <c r="D181" s="11"/>
@@ -38715,7 +39198,7 @@
       <c r="CK181" s="7"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15">
+      <c r="A182" s="17">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -38808,7 +39291,7 @@
       <c r="CK182" s="6"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="5"/>
       <c r="C183" s="7"/>
       <c r="D183" s="11"/>
@@ -38899,7 +39382,7 @@
       <c r="CK183" s="7"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15">
+      <c r="A184" s="17">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -38992,7 +39475,7 @@
       <c r="CK184" s="6"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="5"/>
       <c r="C185" s="7"/>
       <c r="D185" s="11"/>
@@ -39083,7 +39566,7 @@
       <c r="CK185" s="7"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15">
+      <c r="A186" s="17">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -39176,7 +39659,7 @@
       <c r="CK186" s="6"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="5"/>
       <c r="C187" s="7"/>
       <c r="D187" s="11"/>
@@ -39267,7 +39750,7 @@
       <c r="CK187" s="7"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15">
+      <c r="A188" s="17">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -39360,7 +39843,7 @@
       <c r="CK188" s="6"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="5"/>
       <c r="C189" s="7"/>
       <c r="D189" s="11"/>
@@ -39451,7 +39934,7 @@
       <c r="CK189" s="7"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15">
+      <c r="A190" s="17">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -39544,7 +40027,7 @@
       <c r="CK190" s="6"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="5"/>
       <c r="C191" s="7"/>
       <c r="D191" s="11"/>
@@ -39636,91 +40119,36 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -39745,36 +40173,91 @@
     <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
@@ -39799,185 +40282,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="16">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="16">
+      <c r="C1" s="16"/>
+      <c r="D1" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15">
         <v>4</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
         <v>5</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15">
         <v>6</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15">
         <v>7</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15">
         <v>10</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15">
         <v>11</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15">
         <v>12</v>
       </c>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
         <v>13</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15">
         <v>14</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16">
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15">
         <v>15</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16">
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15">
         <v>16</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
         <v>17</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16">
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15">
         <v>18</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15">
         <v>19</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15">
         <v>20</v>
       </c>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16">
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
         <v>21</v>
       </c>
-      <c r="AQ1" s="16"/>
-      <c r="AR1" s="16">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15">
         <v>22</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16">
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15">
         <v>23</v>
       </c>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16">
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15">
         <v>24</v>
       </c>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16">
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
         <v>25</v>
       </c>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15">
         <v>26</v>
       </c>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15">
         <v>27</v>
       </c>
-      <c r="BC1" s="16"/>
-      <c r="BD1" s="16">
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15">
         <v>28</v>
       </c>
-      <c r="BE1" s="16"/>
-      <c r="BF1" s="16">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
         <v>29</v>
       </c>
-      <c r="BG1" s="16"/>
-      <c r="BH1" s="16">
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15">
         <v>30</v>
       </c>
-      <c r="BI1" s="16"/>
-      <c r="BJ1" s="16">
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15">
         <v>31</v>
       </c>
-      <c r="BK1" s="16"/>
-      <c r="BL1" s="16">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15">
         <v>32</v>
       </c>
-      <c r="BM1" s="16"/>
-      <c r="BN1" s="16">
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
         <v>33</v>
       </c>
-      <c r="BO1" s="16"/>
-      <c r="BP1" s="16">
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15">
         <v>34</v>
       </c>
-      <c r="BQ1" s="16"/>
-      <c r="BR1" s="16">
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15">
         <v>35</v>
       </c>
-      <c r="BS1" s="16"/>
-      <c r="BT1" s="16">
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15">
         <v>36</v>
       </c>
-      <c r="BU1" s="16"/>
-      <c r="BV1" s="16">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
         <v>37</v>
       </c>
-      <c r="BW1" s="16"/>
-      <c r="BX1" s="16">
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15">
         <v>38</v>
       </c>
-      <c r="BY1" s="16"/>
-      <c r="BZ1" s="16">
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15">
         <v>39</v>
       </c>
-      <c r="CA1" s="16"/>
-      <c r="CB1" s="16">
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15">
         <v>40</v>
       </c>
-      <c r="CC1" s="16"/>
-      <c r="CD1" s="16">
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15">
         <v>41</v>
       </c>
-      <c r="CE1" s="16"/>
-      <c r="CF1" s="16">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15">
         <v>42</v>
       </c>
-      <c r="CG1" s="16"/>
-      <c r="CH1" s="16">
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15">
         <v>43</v>
       </c>
-      <c r="CI1" s="16"/>
-      <c r="CJ1" s="16">
+      <c r="CI1" s="15"/>
+      <c r="CJ1" s="15">
         <v>44</v>
       </c>
-      <c r="CK1" s="16"/>
+      <c r="CK1" s="15"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -40070,7 +40553,7 @@
       <c r="CK2" s="6"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9"/>
@@ -40161,7 +40644,7 @@
       <c r="CK3" s="10"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -40254,7 +40737,7 @@
       <c r="CK4" s="6"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="11"/>
@@ -40345,7 +40828,7 @@
       <c r="CK5" s="7"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -40438,7 +40921,7 @@
       <c r="CK6" s="6"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="7"/>
       <c r="D7" s="11"/>
@@ -40529,7 +41012,7 @@
       <c r="CK7" s="7"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -40622,7 +41105,7 @@
       <c r="CK8" s="6"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="11"/>
@@ -40713,7 +41196,7 @@
       <c r="CK9" s="7"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -40806,7 +41289,7 @@
       <c r="CK10" s="6"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="7"/>
       <c r="D11" s="11"/>
@@ -40897,7 +41380,7 @@
       <c r="CK11" s="7"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -40987,10 +41470,10 @@
       <c r="CH12" s="8"/>
       <c r="CI12" s="12"/>
       <c r="CJ12" s="8"/>
-      <c r="CK12" s="12"/>
+      <c r="CK12" s="6"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11"/>
@@ -41081,7 +41564,7 @@
       <c r="CK13" s="7"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -41174,7 +41657,7 @@
       <c r="CK14" s="6"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="D15" s="11"/>
@@ -41265,7 +41748,7 @@
       <c r="CK15" s="7"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -41358,7 +41841,7 @@
       <c r="CK16" s="6"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="7"/>
       <c r="D17" s="11"/>
@@ -41449,7 +41932,7 @@
       <c r="CK17" s="7"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -41542,7 +42025,7 @@
       <c r="CK18" s="6"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="D19" s="11"/>
@@ -41633,7 +42116,7 @@
       <c r="CK19" s="7"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -41726,7 +42209,7 @@
       <c r="CK20" s="6"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5"/>
       <c r="C21" s="7"/>
       <c r="D21" s="9"/>
@@ -41817,7 +42300,7 @@
       <c r="CK21" s="7"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -41910,7 +42393,7 @@
       <c r="CK22" s="6"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5"/>
       <c r="C23" s="7"/>
       <c r="D23" s="11"/>
@@ -42001,7 +42484,7 @@
       <c r="CK23" s="7"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -42094,7 +42577,7 @@
       <c r="CK24" s="6"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="5"/>
       <c r="C25" s="7"/>
       <c r="D25" s="11"/>
@@ -42185,7 +42668,7 @@
       <c r="CK25" s="7"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -42278,7 +42761,7 @@
       <c r="CK26" s="6"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="11"/>
@@ -42369,7 +42852,7 @@
       <c r="CK27" s="7"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -42462,7 +42945,7 @@
       <c r="CK28" s="6"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="5"/>
       <c r="C29" s="7"/>
       <c r="D29" s="11"/>
@@ -42553,7 +43036,7 @@
       <c r="CK29" s="7"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -42646,7 +43129,7 @@
       <c r="CK30" s="6"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="5"/>
       <c r="C31" s="7"/>
       <c r="D31" s="11"/>
@@ -42737,7 +43220,7 @@
       <c r="CK31" s="7"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -42830,7 +43313,7 @@
       <c r="CK32" s="6"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="7"/>
       <c r="D33" s="11"/>
@@ -42921,7 +43404,7 @@
       <c r="CK33" s="7"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -43014,7 +43497,7 @@
       <c r="CK34" s="6"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="5"/>
       <c r="C35" s="7"/>
       <c r="D35" s="11"/>
@@ -43105,7 +43588,7 @@
       <c r="CK35" s="7"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -43198,7 +43681,7 @@
       <c r="CK36" s="6"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="11"/>
@@ -43289,7 +43772,7 @@
       <c r="CK37" s="7"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -43382,7 +43865,7 @@
       <c r="CK38" s="6"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="5"/>
       <c r="C39" s="7"/>
       <c r="D39" s="11"/>
@@ -43473,7 +43956,7 @@
       <c r="CK39" s="7"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -43566,7 +44049,7 @@
       <c r="CK40" s="6"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="5"/>
       <c r="C41" s="7"/>
       <c r="D41" s="11"/>
@@ -43657,7 +44140,7 @@
       <c r="CK41" s="7"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -43750,7 +44233,7 @@
       <c r="CK42" s="6"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="5"/>
       <c r="C43" s="7"/>
       <c r="D43" s="11"/>
@@ -43841,7 +44324,7 @@
       <c r="CK43" s="7"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -43934,7 +44417,7 @@
       <c r="CK44" s="6"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="5"/>
       <c r="C45" s="7"/>
       <c r="D45" s="11"/>
@@ -44025,7 +44508,7 @@
       <c r="CK45" s="7"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -44118,7 +44601,7 @@
       <c r="CK46" s="6"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="5"/>
       <c r="C47" s="7"/>
       <c r="D47" s="11"/>
@@ -44209,7 +44692,7 @@
       <c r="CK47" s="7"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="17">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -44302,7 +44785,7 @@
       <c r="CK48" s="6"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="5"/>
       <c r="C49" s="7"/>
       <c r="D49" s="11"/>
@@ -44393,7 +44876,7 @@
       <c r="CK49" s="7"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="17">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -44486,7 +44969,7 @@
       <c r="CK50" s="6"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="5"/>
       <c r="C51" s="7"/>
       <c r="D51" s="11"/>
@@ -44577,7 +45060,7 @@
       <c r="CK51" s="7"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="17">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -44670,7 +45153,7 @@
       <c r="CK52" s="6"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="5"/>
       <c r="C53" s="7"/>
       <c r="D53" s="11"/>
@@ -44761,7 +45244,7 @@
       <c r="CK53" s="7"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="17">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -44854,7 +45337,7 @@
       <c r="CK54" s="6"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
       <c r="D55" s="11"/>
@@ -44945,7 +45428,7 @@
       <c r="CK55" s="7"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="17">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -45038,7 +45521,7 @@
       <c r="CK56" s="6"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
       <c r="D57" s="11"/>
@@ -45129,7 +45612,7 @@
       <c r="CK57" s="7"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="17">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -45222,7 +45705,7 @@
       <c r="CK58" s="6"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
       <c r="D59" s="11"/>
@@ -45313,7 +45796,7 @@
       <c r="CK59" s="7"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="17">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -45406,7 +45889,7 @@
       <c r="CK60" s="6"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="5"/>
       <c r="C61" s="7"/>
       <c r="D61" s="11"/>
@@ -45497,7 +45980,7 @@
       <c r="CK61" s="7"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="17">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -45590,7 +46073,7 @@
       <c r="CK62" s="6"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="5"/>
       <c r="C63" s="7"/>
       <c r="D63" s="11"/>
@@ -45681,7 +46164,7 @@
       <c r="CK63" s="7"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -45774,7 +46257,7 @@
       <c r="CK64" s="6"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="5"/>
       <c r="C65" s="7"/>
       <c r="D65" s="11"/>
@@ -45865,7 +46348,7 @@
       <c r="CK65" s="7"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -45958,7 +46441,7 @@
       <c r="CK66" s="6"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="5"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
@@ -46049,7 +46532,7 @@
       <c r="CK67" s="7"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="17">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -46142,7 +46625,7 @@
       <c r="CK68" s="6"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="5"/>
       <c r="C69" s="7"/>
       <c r="D69" s="11"/>
@@ -46233,7 +46716,7 @@
       <c r="CK69" s="7"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="17">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -46326,7 +46809,7 @@
       <c r="CK70" s="6"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="5"/>
       <c r="C71" s="7"/>
       <c r="D71" s="11"/>
@@ -46417,7 +46900,7 @@
       <c r="CK71" s="7"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -46510,7 +46993,7 @@
       <c r="CK72" s="6"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="5"/>
       <c r="C73" s="7"/>
       <c r="D73" s="11"/>
@@ -46601,7 +47084,7 @@
       <c r="CK73" s="7"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="17">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -46694,7 +47177,7 @@
       <c r="CK74" s="6"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="5"/>
       <c r="C75" s="7"/>
       <c r="D75" s="11"/>
@@ -46785,7 +47268,7 @@
       <c r="CK75" s="7"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="17">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -46878,7 +47361,7 @@
       <c r="CK76" s="6"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="5"/>
       <c r="C77" s="7"/>
       <c r="D77" s="11"/>
@@ -46969,7 +47452,7 @@
       <c r="CK77" s="7"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="17">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -47062,7 +47545,7 @@
       <c r="CK78" s="6"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="5"/>
       <c r="C79" s="7"/>
       <c r="D79" s="11"/>
@@ -47153,7 +47636,7 @@
       <c r="CK79" s="7"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15">
+      <c r="A80" s="17">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -47246,7 +47729,7 @@
       <c r="CK80" s="6"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="5"/>
       <c r="C81" s="7"/>
       <c r="D81" s="11"/>
@@ -47337,7 +47820,7 @@
       <c r="CK81" s="7"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="17">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -47430,7 +47913,7 @@
       <c r="CK82" s="6"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="5"/>
       <c r="C83" s="7"/>
       <c r="D83" s="11"/>
@@ -47521,7 +48004,7 @@
       <c r="CK83" s="7"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="17">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -47614,7 +48097,7 @@
       <c r="CK84" s="6"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="5"/>
       <c r="C85" s="7"/>
       <c r="D85" s="11"/>
@@ -47705,7 +48188,7 @@
       <c r="CK85" s="7"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15">
+      <c r="A86" s="17">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -47798,7 +48281,7 @@
       <c r="CK86" s="6"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="5"/>
       <c r="C87" s="7"/>
       <c r="D87" s="11"/>
@@ -47889,7 +48372,7 @@
       <c r="CK87" s="7"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15">
+      <c r="A88" s="17">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -47982,7 +48465,7 @@
       <c r="CK88" s="6"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="5"/>
       <c r="C89" s="7"/>
       <c r="D89" s="11"/>
@@ -48073,7 +48556,7 @@
       <c r="CK89" s="7"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15">
+      <c r="A90" s="17">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -48166,7 +48649,7 @@
       <c r="CK90" s="6"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="5"/>
       <c r="C91" s="7"/>
       <c r="D91" s="11"/>
@@ -48257,7 +48740,7 @@
       <c r="CK91" s="7"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15">
+      <c r="A92" s="17">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -48350,7 +48833,7 @@
       <c r="CK92" s="6"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="5"/>
       <c r="C93" s="7"/>
       <c r="D93" s="11"/>
@@ -48441,7 +48924,7 @@
       <c r="CK93" s="7"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15">
+      <c r="A94" s="17">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -48534,7 +49017,7 @@
       <c r="CK94" s="6"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="5"/>
       <c r="C95" s="7"/>
       <c r="D95" s="11"/>
@@ -48625,7 +49108,7 @@
       <c r="CK95" s="7"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="17">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -48718,7 +49201,7 @@
       <c r="CK96" s="6"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="5"/>
       <c r="C97" s="7"/>
       <c r="D97" s="11"/>
@@ -48809,7 +49292,7 @@
       <c r="CK97" s="7"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="17">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -48902,7 +49385,7 @@
       <c r="CK98" s="6"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="5"/>
       <c r="C99" s="7"/>
       <c r="D99" s="11"/>
@@ -48993,7 +49476,7 @@
       <c r="CK99" s="7"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="17">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -49086,7 +49569,7 @@
       <c r="CK100" s="6"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="5"/>
       <c r="C101" s="7"/>
       <c r="D101" s="11"/>
@@ -49177,7 +49660,7 @@
       <c r="CK101" s="7"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="17">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -49270,7 +49753,7 @@
       <c r="CK102" s="6"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="5"/>
       <c r="C103" s="7"/>
       <c r="D103" s="11"/>
@@ -49361,7 +49844,7 @@
       <c r="CK103" s="7"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="17">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -49454,7 +49937,7 @@
       <c r="CK104" s="6"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="5"/>
       <c r="C105" s="7"/>
       <c r="D105" s="11"/>
@@ -49545,7 +50028,7 @@
       <c r="CK105" s="7"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="17">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -49638,7 +50121,7 @@
       <c r="CK106" s="6"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="5"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
@@ -49729,7 +50212,7 @@
       <c r="CK107" s="7"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="17">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -49822,7 +50305,7 @@
       <c r="CK108" s="6"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="5"/>
       <c r="C109" s="7"/>
       <c r="D109" s="11"/>
@@ -49913,7 +50396,7 @@
       <c r="CK109" s="7"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="17">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -50006,7 +50489,7 @@
       <c r="CK110" s="6"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="5"/>
       <c r="C111" s="7"/>
       <c r="D111" s="11"/>
@@ -50097,7 +50580,7 @@
       <c r="CK111" s="7"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="17">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -50190,7 +50673,7 @@
       <c r="CK112" s="6"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="5"/>
       <c r="C113" s="7"/>
       <c r="D113" s="11"/>
@@ -50281,7 +50764,7 @@
       <c r="CK113" s="7"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="17">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -50374,7 +50857,7 @@
       <c r="CK114" s="6"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="5"/>
       <c r="C115" s="7"/>
       <c r="D115" s="11"/>
@@ -50465,7 +50948,7 @@
       <c r="CK115" s="7"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="17">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -50558,7 +51041,7 @@
       <c r="CK116" s="6"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="5"/>
       <c r="C117" s="7"/>
       <c r="D117" s="11"/>
@@ -50649,7 +51132,7 @@
       <c r="CK117" s="7"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="17">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -50742,7 +51225,7 @@
       <c r="CK118" s="6"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="5"/>
       <c r="C119" s="7"/>
       <c r="D119" s="11"/>
@@ -50833,7 +51316,7 @@
       <c r="CK119" s="7"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="17">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -50926,7 +51409,7 @@
       <c r="CK120" s="6"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="5"/>
       <c r="C121" s="7"/>
       <c r="D121" s="11"/>
@@ -51017,7 +51500,7 @@
       <c r="CK121" s="7"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="17">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -51110,7 +51593,7 @@
       <c r="CK122" s="6"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="5"/>
       <c r="C123" s="7"/>
       <c r="D123" s="11"/>
@@ -51201,7 +51684,7 @@
       <c r="CK123" s="7"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="17">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -51294,7 +51777,7 @@
       <c r="CK124" s="6"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="5"/>
       <c r="C125" s="7"/>
       <c r="D125" s="11"/>
@@ -51385,7 +51868,7 @@
       <c r="CK125" s="7"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="17">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -51478,7 +51961,7 @@
       <c r="CK126" s="6"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="5"/>
       <c r="C127" s="7"/>
       <c r="D127" s="11"/>
@@ -51569,7 +52052,7 @@
       <c r="CK127" s="7"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="17">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -51662,7 +52145,7 @@
       <c r="CK128" s="6"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="5"/>
       <c r="C129" s="7"/>
       <c r="D129" s="11"/>
@@ -51753,7 +52236,7 @@
       <c r="CK129" s="7"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="17">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -51846,7 +52329,7 @@
       <c r="CK130" s="6"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="5"/>
       <c r="C131" s="7"/>
       <c r="D131" s="11"/>
@@ -51937,7 +52420,7 @@
       <c r="CK131" s="7"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="17">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -52030,7 +52513,7 @@
       <c r="CK132" s="6"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
       <c r="D133" s="11"/>
@@ -52121,7 +52604,7 @@
       <c r="CK133" s="7"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15">
+      <c r="A134" s="17">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -52214,7 +52697,7 @@
       <c r="CK134" s="6"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="5"/>
       <c r="C135" s="7"/>
       <c r="D135" s="11"/>
@@ -52305,7 +52788,7 @@
       <c r="CK135" s="7"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="17">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -52398,7 +52881,7 @@
       <c r="CK136" s="6"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
       <c r="D137" s="11"/>
@@ -52489,7 +52972,7 @@
       <c r="CK137" s="7"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="17">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -52582,7 +53065,7 @@
       <c r="CK138" s="6"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="5"/>
       <c r="C139" s="7"/>
       <c r="D139" s="11"/>
@@ -52673,7 +53156,7 @@
       <c r="CK139" s="7"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15">
+      <c r="A140" s="17">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -52766,7 +53249,7 @@
       <c r="CK140" s="6"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="5"/>
       <c r="C141" s="7"/>
       <c r="D141" s="11"/>
@@ -52857,7 +53340,7 @@
       <c r="CK141" s="7"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15">
+      <c r="A142" s="17">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -52950,7 +53433,7 @@
       <c r="CK142" s="6"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="5"/>
       <c r="C143" s="7"/>
       <c r="D143" s="11"/>
@@ -53041,7 +53524,7 @@
       <c r="CK143" s="7"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15">
+      <c r="A144" s="17">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -53134,7 +53617,7 @@
       <c r="CK144" s="6"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="5"/>
       <c r="C145" s="7"/>
       <c r="D145" s="11"/>
@@ -53225,7 +53708,7 @@
       <c r="CK145" s="7"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15">
+      <c r="A146" s="17">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -53318,7 +53801,7 @@
       <c r="CK146" s="6"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="5"/>
       <c r="C147" s="7"/>
       <c r="D147" s="11"/>
@@ -53409,7 +53892,7 @@
       <c r="CK147" s="7"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15">
+      <c r="A148" s="17">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -53502,7 +53985,7 @@
       <c r="CK148" s="6"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="5"/>
       <c r="C149" s="7"/>
       <c r="D149" s="11"/>
@@ -53593,7 +54076,7 @@
       <c r="CK149" s="7"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15">
+      <c r="A150" s="17">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -53686,7 +54169,7 @@
       <c r="CK150" s="6"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="5"/>
       <c r="C151" s="7"/>
       <c r="D151" s="11"/>
@@ -53777,7 +54260,7 @@
       <c r="CK151" s="7"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15">
+      <c r="A152" s="17">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -53870,7 +54353,7 @@
       <c r="CK152" s="6"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="5"/>
       <c r="C153" s="7"/>
       <c r="D153" s="11"/>
@@ -53961,7 +54444,7 @@
       <c r="CK153" s="7"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15">
+      <c r="A154" s="17">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -54054,7 +54537,7 @@
       <c r="CK154" s="6"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="5"/>
       <c r="C155" s="7"/>
       <c r="D155" s="11"/>
@@ -54145,7 +54628,7 @@
       <c r="CK155" s="7"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15">
+      <c r="A156" s="17">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -54238,7 +54721,7 @@
       <c r="CK156" s="6"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="5"/>
       <c r="C157" s="7"/>
       <c r="D157" s="11"/>
@@ -54329,7 +54812,7 @@
       <c r="CK157" s="7"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15">
+      <c r="A158" s="17">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -54422,7 +54905,7 @@
       <c r="CK158" s="6"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="5"/>
       <c r="C159" s="7"/>
       <c r="D159" s="11"/>
@@ -54513,7 +54996,7 @@
       <c r="CK159" s="7"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15">
+      <c r="A160" s="17">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -54606,7 +55089,7 @@
       <c r="CK160" s="6"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="5"/>
       <c r="C161" s="7"/>
       <c r="D161" s="11"/>
@@ -54697,7 +55180,7 @@
       <c r="CK161" s="7"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15">
+      <c r="A162" s="17">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -54790,7 +55273,7 @@
       <c r="CK162" s="6"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="5"/>
       <c r="C163" s="7"/>
       <c r="D163" s="11"/>
@@ -54881,7 +55364,7 @@
       <c r="CK163" s="7"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15">
+      <c r="A164" s="17">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -54974,7 +55457,7 @@
       <c r="CK164" s="6"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="5"/>
       <c r="C165" s="7"/>
       <c r="D165" s="11"/>
@@ -55065,7 +55548,7 @@
       <c r="CK165" s="7"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15">
+      <c r="A166" s="17">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -55158,7 +55641,7 @@
       <c r="CK166" s="6"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="5"/>
       <c r="C167" s="7"/>
       <c r="D167" s="11"/>
@@ -55249,7 +55732,7 @@
       <c r="CK167" s="7"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15">
+      <c r="A168" s="17">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -55342,7 +55825,7 @@
       <c r="CK168" s="6"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="5"/>
       <c r="C169" s="7"/>
       <c r="D169" s="11"/>
@@ -55433,7 +55916,7 @@
       <c r="CK169" s="7"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15">
+      <c r="A170" s="17">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -55526,7 +56009,7 @@
       <c r="CK170" s="6"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="5"/>
       <c r="C171" s="7"/>
       <c r="D171" s="11"/>
@@ -55617,7 +56100,7 @@
       <c r="CK171" s="7"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15">
+      <c r="A172" s="17">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -55710,7 +56193,7 @@
       <c r="CK172" s="6"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="5"/>
       <c r="C173" s="7"/>
       <c r="D173" s="11"/>
@@ -55801,7 +56284,7 @@
       <c r="CK173" s="7"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15">
+      <c r="A174" s="17">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -55894,7 +56377,7 @@
       <c r="CK174" s="6"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="5"/>
       <c r="C175" s="7"/>
       <c r="D175" s="11"/>
@@ -55985,7 +56468,7 @@
       <c r="CK175" s="7"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15">
+      <c r="A176" s="17">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -56078,7 +56561,7 @@
       <c r="CK176" s="6"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="5"/>
       <c r="C177" s="7"/>
       <c r="D177" s="11"/>
@@ -56169,7 +56652,7 @@
       <c r="CK177" s="7"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15">
+      <c r="A178" s="17">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -56262,7 +56745,7 @@
       <c r="CK178" s="6"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="5"/>
       <c r="C179" s="7"/>
       <c r="D179" s="11"/>
@@ -56353,7 +56836,7 @@
       <c r="CK179" s="7"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15">
+      <c r="A180" s="17">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -56446,7 +56929,7 @@
       <c r="CK180" s="6"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="5"/>
       <c r="C181" s="7"/>
       <c r="D181" s="11"/>
@@ -56537,7 +57020,7 @@
       <c r="CK181" s="7"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15">
+      <c r="A182" s="17">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -56630,7 +57113,7 @@
       <c r="CK182" s="6"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="5"/>
       <c r="C183" s="7"/>
       <c r="D183" s="11"/>
@@ -56721,7 +57204,7 @@
       <c r="CK183" s="7"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15">
+      <c r="A184" s="17">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -56814,7 +57297,7 @@
       <c r="CK184" s="6"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="5"/>
       <c r="C185" s="7"/>
       <c r="D185" s="11"/>
@@ -56905,7 +57388,7 @@
       <c r="CK185" s="7"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15">
+      <c r="A186" s="17">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -56998,7 +57481,7 @@
       <c r="CK186" s="6"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="5"/>
       <c r="C187" s="7"/>
       <c r="D187" s="11"/>
@@ -57089,7 +57572,7 @@
       <c r="CK187" s="7"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15">
+      <c r="A188" s="17">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -57182,7 +57665,7 @@
       <c r="CK188" s="6"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="5"/>
       <c r="C189" s="7"/>
       <c r="D189" s="11"/>
@@ -57273,7 +57756,7 @@
       <c r="CK189" s="7"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15">
+      <c r="A190" s="17">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -57366,7 +57849,7 @@
       <c r="CK190" s="6"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="5"/>
       <c r="C191" s="7"/>
       <c r="D191" s="11"/>
@@ -57458,91 +57941,36 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -57567,36 +57995,91 @@
     <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>

--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F9F1E8-EF98-4B7B-AB53-DB927D49E9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EA1995-6406-4A24-B3FD-03517ED8442F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="70125" yWindow="1290" windowWidth="25140" windowHeight="15000" activeTab="2" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="58155" yWindow="1440" windowWidth="34200" windowHeight="24660" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -5826,7 +5826,7 @@
       <c r="CH12" s="8"/>
       <c r="CI12" s="12"/>
       <c r="CJ12" s="8"/>
-      <c r="CK12" s="12"/>
+      <c r="CK12" s="6"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>
@@ -23648,7 +23648,7 @@
       <c r="CH12" s="8"/>
       <c r="CI12" s="12"/>
       <c r="CJ12" s="8"/>
-      <c r="CK12" s="12"/>
+      <c r="CK12" s="6"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17"/>

--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EA1995-6406-4A24-B3FD-03517ED8442F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38534053-E70C-44ED-978C-62DB6129D771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58155" yWindow="1440" windowWidth="34200" windowHeight="24660" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="68985" yWindow="3120" windowWidth="43200" windowHeight="23985" activeTab="1" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -253,17 +253,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -343,10 +343,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>58434</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>124811</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -370,8 +370,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="923192" y="4615962"/>
-          <a:ext cx="2520280" cy="1971196"/>
+          <a:off x="923192" y="5231423"/>
+          <a:ext cx="2461846" cy="1846385"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -643,14 +643,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>98426</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>58615</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -681,8 +681,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="923192" y="9231923"/>
-          <a:ext cx="2560272" cy="1904999"/>
+          <a:off x="923192" y="9539654"/>
+          <a:ext cx="2461846" cy="1846384"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -705,13 +705,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -727,8 +727,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3538904" y="9231924"/>
-          <a:ext cx="4769827" cy="1384788"/>
+          <a:off x="3538904" y="9539655"/>
+          <a:ext cx="4769827" cy="1384787"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -951,13 +951,13 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -973,7 +973,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8462596" y="6923942"/>
+          <a:off x="8462596" y="7385538"/>
           <a:ext cx="4769827" cy="2000252"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1229,14 +1229,14 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>139212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>139211</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1251,7 +1251,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8462596" y="8308731"/>
+          <a:off x="8462596" y="9525000"/>
           <a:ext cx="4769827" cy="1384788"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1337,13 +1337,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1359,8 +1359,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3538904" y="11539904"/>
-          <a:ext cx="4769827" cy="1384789"/>
+          <a:off x="3538904" y="11693769"/>
+          <a:ext cx="4769827" cy="1384790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1547,10 +1547,10 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>153864</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2544261" cy="1377460"/>
+    <xdr:ext cx="2461847" cy="1384789"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="18" name="図 17">
@@ -1573,8 +1573,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="923192" y="11539904"/>
-          <a:ext cx="2544261" cy="1377460"/>
+          <a:off x="923192" y="11693768"/>
+          <a:ext cx="2461847" cy="1384789"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1587,14 +1587,14 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1610,7 +1610,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8462596" y="11539904"/>
-          <a:ext cx="4769827" cy="1384789"/>
+          <a:ext cx="4769827" cy="1384790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1680,11 +1680,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>745</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2519717" cy="2000249"/>
+    <xdr:ext cx="2461846" cy="1846384"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="20" name="図 19">
@@ -1707,8 +1707,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="923937" y="7539404"/>
-          <a:ext cx="2519717" cy="2000249"/>
+          <a:off x="923192" y="7385538"/>
+          <a:ext cx="2461846" cy="1846384"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1721,13 +1721,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>2</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1743,7 +1743,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3538904" y="6923942"/>
+          <a:off x="3538904" y="7385538"/>
           <a:ext cx="4769827" cy="2000252"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1933,15 +1933,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>9075</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>14653</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1971,8 +1971,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="932267" y="13386288"/>
-          <a:ext cx="2467424" cy="1846384"/>
+          <a:off x="923192" y="13386289"/>
+          <a:ext cx="2461846" cy="1846384"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1995,14 +1995,14 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>54</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2017,7 +2017,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3538904" y="12463096"/>
+          <a:off x="3538904" y="13386289"/>
           <a:ext cx="4769827" cy="1384788"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2254,14 +2254,14 @@
     <xdr:from>
       <xdr:col>55</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>86</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>153865</xdr:rowOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>153864</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2276,7 +2276,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8462596" y="12463096"/>
+          <a:off x="8462596" y="13386288"/>
           <a:ext cx="4769827" cy="1384788"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2491,7 +2491,17 @@
               <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
               <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
             </a:rPr>
-            <a:t>RO-RL78-MAXV-LEARNING (JP)</a:t>
+            <a:t>RO-RL78-MAXV-LEARNING (JP) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>継続中</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
@@ -2835,6 +2845,26 @@
             </a:rPr>
             <a:t>RO-RL78-MAXV-LEARNING (EN)</a:t>
           </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" altLang="ja-JP" sz="1400" b="1" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>ONGOING</a:t>
+          </a:r>
           <a:br>
             <a:rPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
               <a:solidFill>
@@ -2883,13 +2913,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>49509</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2915,8 +2945,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="923192" y="2923442"/>
-          <a:ext cx="2511355" cy="2000250"/>
+          <a:off x="923193" y="2923442"/>
+          <a:ext cx="2461846" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2975,8 +3005,8 @@
     <xdr:to>
       <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2992,7 +3022,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="769327" y="1077058"/>
-          <a:ext cx="3231173" cy="1941634"/>
+          <a:ext cx="3231173" cy="1692519"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3087,7 +3117,7 @@
               <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
               <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
             </a:rPr>
-            <a:t>アホみたいなサイトへようこそ来てくださいました。</a:t>
+            <a:t>アホみたいなサイトへようこそ。</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100" baseline="0">
             <a:solidFill>
@@ -3321,14 +3351,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>64</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>63</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>153865</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>83</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>153864</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3345,8 +3375,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9847385" y="1077057"/>
-          <a:ext cx="2923442" cy="1692520"/>
+          <a:off x="9847384" y="1077057"/>
+          <a:ext cx="3077307" cy="1692520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3584,6 +3614,449 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="テキスト ボックス 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7567970F-422D-43AB-A816-686F9ABC1AE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4000500" y="3385038"/>
+          <a:ext cx="4923692" cy="923193"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1500"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>ここには放置されたプロジェクトの一部を置きます。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1500"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+              <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            </a:rPr>
+            <a:t>反響があれば再開するかもです。画像をクリックすると関連の記事に飛びます。</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPts val="1500"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>Placing some of my abandoned/shelved projects here. If there's enough interest,</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPts val="1500"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-GB">
+              <a:solidFill>
+                <a:schemeClr val="bg2"/>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>I might revive them. Clicking on the image will take you to the related article/post.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPts val="1500"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1500"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB" altLang="ja-JP" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:latin typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+            <a:ea typeface="Yu Gothic UI" panose="020B0500000000000000" pitchFamily="34" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3" descr="Image">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F4D3551-5178-07B8-A6F7-2F0611C68BBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4923692" y="1230923"/>
+          <a:ext cx="2461846" cy="2154115"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>112058</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>136038</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B90825E-8EA0-3E85-6C71-6864002530A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="470647" y="4818529"/>
+          <a:ext cx="3922059" cy="3789156"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>21528</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>24179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{220E288A-BF15-5787-84BD-B104865226C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4392706" y="4706471"/>
+          <a:ext cx="4100469" cy="4260002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>145677</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>134472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>83</xdr:col>
+      <xdr:colOff>73233</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>156454</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E09A429E-19C9-A13C-3524-8B2B3B751595}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8617324" y="4684060"/>
+          <a:ext cx="4477144" cy="4885335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>29740</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>121881</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22413</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>118525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55996062-30B4-DDE9-1B63-ECE4C40A9B6D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1912328" y="8907293"/>
+          <a:ext cx="3914732" cy="3448056"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3721,7 +4194,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>68</xdr:col>
+      <xdr:col>70</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3740,7 +4213,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4154365" y="1846385"/>
-          <a:ext cx="6308481" cy="307730"/>
+          <a:ext cx="6616212" cy="307730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3895,14 +4368,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>153864</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>68</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>153865</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>153864</xdr:rowOff>
     </xdr:to>
@@ -3919,8 +4392,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4154365" y="2154115"/>
-          <a:ext cx="6308481" cy="307730"/>
+          <a:off x="4154364" y="2154115"/>
+          <a:ext cx="6923943" cy="307730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3959,7 +4432,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>知的な内容と淫夢要素が混ざった投稿をされるお方。懐かしい感じのサイトのデザインです。</a:t>
+            <a:t>知的な内容と淫夢要素が混ざった投稿をされるココリーネさん。懐かしい感じのサイトのデザインです。</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0">
             <a:solidFill>
@@ -4636,185 +5109,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="16">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="16">
+      <c r="C1" s="16"/>
+      <c r="D1" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15">
         <v>4</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
         <v>5</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15">
         <v>6</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15">
         <v>7</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15">
         <v>10</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15">
         <v>11</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15">
         <v>12</v>
       </c>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
         <v>13</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15">
         <v>14</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16">
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15">
         <v>15</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16">
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15">
         <v>16</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
         <v>17</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16">
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15">
         <v>18</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15">
         <v>19</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15">
         <v>20</v>
       </c>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16">
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
         <v>21</v>
       </c>
-      <c r="AQ1" s="16"/>
-      <c r="AR1" s="16">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15">
         <v>22</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16">
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15">
         <v>23</v>
       </c>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16">
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15">
         <v>24</v>
       </c>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16">
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
         <v>25</v>
       </c>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15">
         <v>26</v>
       </c>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15">
         <v>27</v>
       </c>
-      <c r="BC1" s="16"/>
-      <c r="BD1" s="16">
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15">
         <v>28</v>
       </c>
-      <c r="BE1" s="16"/>
-      <c r="BF1" s="16">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
         <v>29</v>
       </c>
-      <c r="BG1" s="16"/>
-      <c r="BH1" s="16">
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15">
         <v>30</v>
       </c>
-      <c r="BI1" s="16"/>
-      <c r="BJ1" s="16">
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15">
         <v>31</v>
       </c>
-      <c r="BK1" s="16"/>
-      <c r="BL1" s="16">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15">
         <v>32</v>
       </c>
-      <c r="BM1" s="16"/>
-      <c r="BN1" s="16">
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
         <v>33</v>
       </c>
-      <c r="BO1" s="16"/>
-      <c r="BP1" s="16">
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15">
         <v>34</v>
       </c>
-      <c r="BQ1" s="16"/>
-      <c r="BR1" s="16">
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15">
         <v>35</v>
       </c>
-      <c r="BS1" s="16"/>
-      <c r="BT1" s="16">
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15">
         <v>36</v>
       </c>
-      <c r="BU1" s="16"/>
-      <c r="BV1" s="16">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
         <v>37</v>
       </c>
-      <c r="BW1" s="16"/>
-      <c r="BX1" s="16">
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15">
         <v>38</v>
       </c>
-      <c r="BY1" s="16"/>
-      <c r="BZ1" s="16">
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15">
         <v>39</v>
       </c>
-      <c r="CA1" s="16"/>
-      <c r="CB1" s="16">
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15">
         <v>40</v>
       </c>
-      <c r="CC1" s="16"/>
-      <c r="CD1" s="16">
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15">
         <v>41</v>
       </c>
-      <c r="CE1" s="16"/>
-      <c r="CF1" s="16">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15">
         <v>42</v>
       </c>
-      <c r="CG1" s="16"/>
-      <c r="CH1" s="16">
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15">
         <v>43</v>
       </c>
-      <c r="CI1" s="16"/>
-      <c r="CJ1" s="16">
+      <c r="CI1" s="15"/>
+      <c r="CJ1" s="15">
         <v>44</v>
       </c>
-      <c r="CK1" s="16"/>
+      <c r="CK1" s="15"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -4907,7 +5380,7 @@
       <c r="CK2" s="6"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9"/>
@@ -4998,7 +5471,7 @@
       <c r="CK3" s="10"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -5091,7 +5564,7 @@
       <c r="CK4" s="6"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="11"/>
@@ -5182,7 +5655,7 @@
       <c r="CK5" s="7"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -5275,7 +5748,7 @@
       <c r="CK6" s="6"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="7"/>
       <c r="D7" s="11"/>
@@ -5366,7 +5839,7 @@
       <c r="CK7" s="7"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -5459,7 +5932,7 @@
       <c r="CK8" s="6"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="11"/>
@@ -5552,7 +6025,7 @@
       <c r="CK9" s="7"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -5645,7 +6118,7 @@
       <c r="CK10" s="6"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="7"/>
       <c r="D11" s="11"/>
@@ -5736,7 +6209,7 @@
       <c r="CK11" s="7"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -5829,7 +6302,7 @@
       <c r="CK12" s="6"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11"/>
@@ -5920,7 +6393,7 @@
       <c r="CK13" s="7"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -6013,7 +6486,7 @@
       <c r="CK14" s="6"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="D15" s="11"/>
@@ -6104,7 +6577,7 @@
       <c r="CK15" s="7"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -6197,7 +6670,7 @@
       <c r="CK16" s="6"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="7"/>
       <c r="D17" s="11"/>
@@ -6288,7 +6761,7 @@
       <c r="CK17" s="7"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -6381,7 +6854,7 @@
       <c r="CK18" s="6"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="D19" s="11"/>
@@ -6472,7 +6945,7 @@
       <c r="CK19" s="7"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -6565,7 +7038,7 @@
       <c r="CK20" s="6"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5"/>
       <c r="C21" s="7"/>
       <c r="D21" s="9"/>
@@ -6656,7 +7129,7 @@
       <c r="CK21" s="7"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -6749,7 +7222,7 @@
       <c r="CK22" s="6"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5"/>
       <c r="C23" s="7"/>
       <c r="D23" s="11"/>
@@ -6840,7 +7313,7 @@
       <c r="CK23" s="7"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -6933,7 +7406,7 @@
       <c r="CK24" s="6"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="5"/>
       <c r="C25" s="7"/>
       <c r="D25" s="11"/>
@@ -7024,7 +7497,7 @@
       <c r="CK25" s="7"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -7117,7 +7590,7 @@
       <c r="CK26" s="6"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="11"/>
@@ -7208,7 +7681,7 @@
       <c r="CK27" s="7"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -7301,7 +7774,7 @@
       <c r="CK28" s="6"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="5"/>
       <c r="C29" s="7"/>
       <c r="D29" s="11"/>
@@ -7392,7 +7865,7 @@
       <c r="CK29" s="7"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -7485,7 +7958,7 @@
       <c r="CK30" s="6"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="5"/>
       <c r="C31" s="7"/>
       <c r="D31" s="11"/>
@@ -7576,7 +8049,7 @@
       <c r="CK31" s="7"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -7669,7 +8142,7 @@
       <c r="CK32" s="6"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="7"/>
       <c r="D33" s="11"/>
@@ -7760,7 +8233,7 @@
       <c r="CK33" s="7"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -7853,7 +8326,7 @@
       <c r="CK34" s="6"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="5"/>
       <c r="C35" s="7"/>
       <c r="D35" s="11"/>
@@ -7944,7 +8417,7 @@
       <c r="CK35" s="7"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -8037,7 +8510,7 @@
       <c r="CK36" s="6"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="11"/>
@@ -8128,7 +8601,7 @@
       <c r="CK37" s="7"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -8221,7 +8694,7 @@
       <c r="CK38" s="6"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="5"/>
       <c r="C39" s="7"/>
       <c r="D39" s="11"/>
@@ -8312,7 +8785,7 @@
       <c r="CK39" s="7"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -8405,7 +8878,7 @@
       <c r="CK40" s="6"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="5"/>
       <c r="C41" s="7"/>
       <c r="D41" s="11"/>
@@ -8496,7 +8969,7 @@
       <c r="CK41" s="7"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -8589,7 +9062,7 @@
       <c r="CK42" s="6"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="5"/>
       <c r="C43" s="7"/>
       <c r="D43" s="11"/>
@@ -8680,7 +9153,7 @@
       <c r="CK43" s="7"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -8773,7 +9246,7 @@
       <c r="CK44" s="6"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="5"/>
       <c r="C45" s="7"/>
       <c r="D45" s="11"/>
@@ -8864,7 +9337,7 @@
       <c r="CK45" s="7"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -8957,7 +9430,7 @@
       <c r="CK46" s="6"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="5"/>
       <c r="C47" s="7"/>
       <c r="D47" s="11"/>
@@ -9048,7 +9521,7 @@
       <c r="CK47" s="7"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="17">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -9141,7 +9614,7 @@
       <c r="CK48" s="6"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="5"/>
       <c r="C49" s="7"/>
       <c r="D49" s="11"/>
@@ -9232,7 +9705,7 @@
       <c r="CK49" s="7"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="17">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -9325,7 +9798,7 @@
       <c r="CK50" s="6"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="5"/>
       <c r="C51" s="7"/>
       <c r="D51" s="11"/>
@@ -9416,7 +9889,7 @@
       <c r="CK51" s="7"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="17">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -9509,7 +9982,7 @@
       <c r="CK52" s="6"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="5"/>
       <c r="C53" s="7"/>
       <c r="D53" s="11"/>
@@ -9600,7 +10073,7 @@
       <c r="CK53" s="7"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="17">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -9693,7 +10166,7 @@
       <c r="CK54" s="6"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
       <c r="D55" s="11"/>
@@ -9784,7 +10257,7 @@
       <c r="CK55" s="7"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="17">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -9877,7 +10350,7 @@
       <c r="CK56" s="6"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
       <c r="D57" s="11"/>
@@ -9968,7 +10441,7 @@
       <c r="CK57" s="7"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="17">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -10061,7 +10534,7 @@
       <c r="CK58" s="6"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
       <c r="D59" s="11"/>
@@ -10152,7 +10625,7 @@
       <c r="CK59" s="7"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="17">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -10245,7 +10718,7 @@
       <c r="CK60" s="6"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="5"/>
       <c r="C61" s="7"/>
       <c r="D61" s="11"/>
@@ -10336,7 +10809,7 @@
       <c r="CK61" s="7"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="17">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -10429,7 +10902,7 @@
       <c r="CK62" s="6"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="5"/>
       <c r="C63" s="7"/>
       <c r="D63" s="11"/>
@@ -10520,7 +10993,7 @@
       <c r="CK63" s="7"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -10613,7 +11086,7 @@
       <c r="CK64" s="6"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="5"/>
       <c r="C65" s="7"/>
       <c r="D65" s="11"/>
@@ -10704,7 +11177,7 @@
       <c r="CK65" s="7"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -10797,7 +11270,7 @@
       <c r="CK66" s="6"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="5"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
@@ -10888,7 +11361,7 @@
       <c r="CK67" s="7"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="17">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -10981,7 +11454,7 @@
       <c r="CK68" s="6"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="5"/>
       <c r="C69" s="7"/>
       <c r="D69" s="11"/>
@@ -11072,7 +11545,7 @@
       <c r="CK69" s="7"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="17">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -11165,7 +11638,7 @@
       <c r="CK70" s="6"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="5"/>
       <c r="C71" s="7"/>
       <c r="D71" s="11"/>
@@ -11256,7 +11729,7 @@
       <c r="CK71" s="7"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -11349,7 +11822,7 @@
       <c r="CK72" s="6"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="5"/>
       <c r="C73" s="7"/>
       <c r="D73" s="11"/>
@@ -11440,7 +11913,7 @@
       <c r="CK73" s="7"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="17">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -11533,7 +12006,7 @@
       <c r="CK74" s="6"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="5"/>
       <c r="C75" s="7"/>
       <c r="D75" s="11"/>
@@ -11624,7 +12097,7 @@
       <c r="CK75" s="7"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="17">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -11717,7 +12190,7 @@
       <c r="CK76" s="6"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="5"/>
       <c r="C77" s="7"/>
       <c r="D77" s="11"/>
@@ -11808,7 +12281,7 @@
       <c r="CK77" s="7"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="17">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -11901,7 +12374,7 @@
       <c r="CK78" s="6"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="5"/>
       <c r="C79" s="7"/>
       <c r="D79" s="11"/>
@@ -11992,7 +12465,7 @@
       <c r="CK79" s="7"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15">
+      <c r="A80" s="17">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -12085,7 +12558,7 @@
       <c r="CK80" s="6"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="5"/>
       <c r="C81" s="7"/>
       <c r="D81" s="11"/>
@@ -12176,7 +12649,7 @@
       <c r="CK81" s="7"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="17">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -12269,7 +12742,7 @@
       <c r="CK82" s="6"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="5"/>
       <c r="C83" s="7"/>
       <c r="D83" s="11"/>
@@ -12360,7 +12833,7 @@
       <c r="CK83" s="7"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="17">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -12453,7 +12926,7 @@
       <c r="CK84" s="6"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="5"/>
       <c r="C85" s="7"/>
       <c r="D85" s="11"/>
@@ -12544,7 +13017,7 @@
       <c r="CK85" s="7"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15">
+      <c r="A86" s="17">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -12637,7 +13110,7 @@
       <c r="CK86" s="6"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="5"/>
       <c r="C87" s="7"/>
       <c r="D87" s="11"/>
@@ -12728,7 +13201,7 @@
       <c r="CK87" s="7"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15">
+      <c r="A88" s="17">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -12821,7 +13294,7 @@
       <c r="CK88" s="6"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="5"/>
       <c r="C89" s="7"/>
       <c r="D89" s="11"/>
@@ -12912,7 +13385,7 @@
       <c r="CK89" s="7"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15">
+      <c r="A90" s="17">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -13005,7 +13478,7 @@
       <c r="CK90" s="6"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="5"/>
       <c r="C91" s="7"/>
       <c r="D91" s="11"/>
@@ -13096,7 +13569,7 @@
       <c r="CK91" s="7"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15">
+      <c r="A92" s="17">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -13189,7 +13662,7 @@
       <c r="CK92" s="6"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="5"/>
       <c r="C93" s="7"/>
       <c r="D93" s="11"/>
@@ -13280,7 +13753,7 @@
       <c r="CK93" s="7"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15">
+      <c r="A94" s="17">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -13373,7 +13846,7 @@
       <c r="CK94" s="6"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="5"/>
       <c r="C95" s="7"/>
       <c r="D95" s="11"/>
@@ -13464,7 +13937,7 @@
       <c r="CK95" s="7"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="17">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -13557,7 +14030,7 @@
       <c r="CK96" s="6"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="5"/>
       <c r="C97" s="7"/>
       <c r="D97" s="11"/>
@@ -13648,7 +14121,7 @@
       <c r="CK97" s="7"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="17">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -13741,7 +14214,7 @@
       <c r="CK98" s="6"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="5"/>
       <c r="C99" s="7"/>
       <c r="D99" s="11"/>
@@ -13832,7 +14305,7 @@
       <c r="CK99" s="7"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="17">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -13925,7 +14398,7 @@
       <c r="CK100" s="6"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="5"/>
       <c r="C101" s="7"/>
       <c r="D101" s="11"/>
@@ -14016,7 +14489,7 @@
       <c r="CK101" s="7"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="17">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -14109,7 +14582,7 @@
       <c r="CK102" s="6"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="5"/>
       <c r="C103" s="7"/>
       <c r="D103" s="11"/>
@@ -14200,7 +14673,7 @@
       <c r="CK103" s="7"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="17">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -14293,7 +14766,7 @@
       <c r="CK104" s="6"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="5"/>
       <c r="C105" s="7"/>
       <c r="D105" s="11"/>
@@ -14384,7 +14857,7 @@
       <c r="CK105" s="7"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="17">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -14477,7 +14950,7 @@
       <c r="CK106" s="6"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="5"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
@@ -14568,7 +15041,7 @@
       <c r="CK107" s="7"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="17">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -14661,7 +15134,7 @@
       <c r="CK108" s="6"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="5"/>
       <c r="C109" s="7"/>
       <c r="D109" s="11"/>
@@ -14752,7 +15225,7 @@
       <c r="CK109" s="7"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="17">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -14845,7 +15318,7 @@
       <c r="CK110" s="6"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="5"/>
       <c r="C111" s="7"/>
       <c r="D111" s="11"/>
@@ -14936,7 +15409,7 @@
       <c r="CK111" s="7"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="17">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -15029,7 +15502,7 @@
       <c r="CK112" s="6"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="5"/>
       <c r="C113" s="7"/>
       <c r="D113" s="11"/>
@@ -15120,7 +15593,7 @@
       <c r="CK113" s="7"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="17">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -15213,7 +15686,7 @@
       <c r="CK114" s="6"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="5"/>
       <c r="C115" s="7"/>
       <c r="D115" s="11"/>
@@ -15304,7 +15777,7 @@
       <c r="CK115" s="7"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="17">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -15397,7 +15870,7 @@
       <c r="CK116" s="6"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="5"/>
       <c r="C117" s="7"/>
       <c r="D117" s="11"/>
@@ -15488,7 +15961,7 @@
       <c r="CK117" s="7"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="17">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -15581,7 +16054,7 @@
       <c r="CK118" s="6"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="5"/>
       <c r="C119" s="7"/>
       <c r="D119" s="11"/>
@@ -15672,7 +16145,7 @@
       <c r="CK119" s="7"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="17">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -15765,7 +16238,7 @@
       <c r="CK120" s="6"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="5"/>
       <c r="C121" s="7"/>
       <c r="D121" s="11"/>
@@ -15856,7 +16329,7 @@
       <c r="CK121" s="7"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="17">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -15949,7 +16422,7 @@
       <c r="CK122" s="6"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="5"/>
       <c r="C123" s="7"/>
       <c r="D123" s="11"/>
@@ -16040,7 +16513,7 @@
       <c r="CK123" s="7"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="17">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -16133,7 +16606,7 @@
       <c r="CK124" s="6"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="5"/>
       <c r="C125" s="7"/>
       <c r="D125" s="11"/>
@@ -16224,7 +16697,7 @@
       <c r="CK125" s="7"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="17">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -16317,7 +16790,7 @@
       <c r="CK126" s="6"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="5"/>
       <c r="C127" s="7"/>
       <c r="D127" s="11"/>
@@ -16408,7 +16881,7 @@
       <c r="CK127" s="7"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="17">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -16501,7 +16974,7 @@
       <c r="CK128" s="6"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="5"/>
       <c r="C129" s="7"/>
       <c r="D129" s="11"/>
@@ -16592,7 +17065,7 @@
       <c r="CK129" s="7"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="17">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -16685,7 +17158,7 @@
       <c r="CK130" s="6"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="5"/>
       <c r="C131" s="7"/>
       <c r="D131" s="11"/>
@@ -16776,7 +17249,7 @@
       <c r="CK131" s="7"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="17">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -16869,7 +17342,7 @@
       <c r="CK132" s="6"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
       <c r="D133" s="11"/>
@@ -16960,7 +17433,7 @@
       <c r="CK133" s="7"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15">
+      <c r="A134" s="17">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -17053,7 +17526,7 @@
       <c r="CK134" s="6"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="5"/>
       <c r="C135" s="7"/>
       <c r="D135" s="11"/>
@@ -17144,7 +17617,7 @@
       <c r="CK135" s="7"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="17">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -17237,7 +17710,7 @@
       <c r="CK136" s="6"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
       <c r="D137" s="11"/>
@@ -17328,7 +17801,7 @@
       <c r="CK137" s="7"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="17">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -17421,7 +17894,7 @@
       <c r="CK138" s="6"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="5"/>
       <c r="C139" s="7"/>
       <c r="D139" s="11"/>
@@ -17512,7 +17985,7 @@
       <c r="CK139" s="7"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15">
+      <c r="A140" s="17">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -17605,7 +18078,7 @@
       <c r="CK140" s="6"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="5"/>
       <c r="C141" s="7"/>
       <c r="D141" s="11"/>
@@ -17696,7 +18169,7 @@
       <c r="CK141" s="7"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15">
+      <c r="A142" s="17">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -17789,7 +18262,7 @@
       <c r="CK142" s="6"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="5"/>
       <c r="C143" s="7"/>
       <c r="D143" s="11"/>
@@ -17880,7 +18353,7 @@
       <c r="CK143" s="7"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15">
+      <c r="A144" s="17">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -17973,7 +18446,7 @@
       <c r="CK144" s="6"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="5"/>
       <c r="C145" s="7"/>
       <c r="D145" s="11"/>
@@ -18064,7 +18537,7 @@
       <c r="CK145" s="7"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15">
+      <c r="A146" s="17">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -18157,7 +18630,7 @@
       <c r="CK146" s="6"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="5"/>
       <c r="C147" s="7"/>
       <c r="D147" s="11"/>
@@ -18248,7 +18721,7 @@
       <c r="CK147" s="7"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15">
+      <c r="A148" s="17">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -18341,7 +18814,7 @@
       <c r="CK148" s="6"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="5"/>
       <c r="C149" s="7"/>
       <c r="D149" s="11"/>
@@ -18432,7 +18905,7 @@
       <c r="CK149" s="7"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15">
+      <c r="A150" s="17">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -18525,7 +18998,7 @@
       <c r="CK150" s="6"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="5"/>
       <c r="C151" s="7"/>
       <c r="D151" s="11"/>
@@ -18616,7 +19089,7 @@
       <c r="CK151" s="7"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15">
+      <c r="A152" s="17">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -18709,7 +19182,7 @@
       <c r="CK152" s="6"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="5"/>
       <c r="C153" s="7"/>
       <c r="D153" s="11"/>
@@ -18800,7 +19273,7 @@
       <c r="CK153" s="7"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15">
+      <c r="A154" s="17">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -18893,7 +19366,7 @@
       <c r="CK154" s="6"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="5"/>
       <c r="C155" s="7"/>
       <c r="D155" s="11"/>
@@ -18984,7 +19457,7 @@
       <c r="CK155" s="7"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15">
+      <c r="A156" s="17">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -19077,7 +19550,7 @@
       <c r="CK156" s="6"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="5"/>
       <c r="C157" s="7"/>
       <c r="D157" s="11"/>
@@ -19168,7 +19641,7 @@
       <c r="CK157" s="7"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15">
+      <c r="A158" s="17">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -19261,7 +19734,7 @@
       <c r="CK158" s="6"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="5"/>
       <c r="C159" s="7"/>
       <c r="D159" s="11"/>
@@ -19352,7 +19825,7 @@
       <c r="CK159" s="7"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15">
+      <c r="A160" s="17">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -19445,7 +19918,7 @@
       <c r="CK160" s="6"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="5"/>
       <c r="C161" s="7"/>
       <c r="D161" s="11"/>
@@ -19536,7 +20009,7 @@
       <c r="CK161" s="7"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15">
+      <c r="A162" s="17">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -19629,7 +20102,7 @@
       <c r="CK162" s="6"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="5"/>
       <c r="C163" s="7"/>
       <c r="D163" s="11"/>
@@ -19720,7 +20193,7 @@
       <c r="CK163" s="7"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15">
+      <c r="A164" s="17">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -19813,7 +20286,7 @@
       <c r="CK164" s="6"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="5"/>
       <c r="C165" s="7"/>
       <c r="D165" s="11"/>
@@ -19904,7 +20377,7 @@
       <c r="CK165" s="7"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15">
+      <c r="A166" s="17">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -19997,7 +20470,7 @@
       <c r="CK166" s="6"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="5"/>
       <c r="C167" s="7"/>
       <c r="D167" s="11"/>
@@ -20088,7 +20561,7 @@
       <c r="CK167" s="7"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15">
+      <c r="A168" s="17">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -20181,7 +20654,7 @@
       <c r="CK168" s="6"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="5"/>
       <c r="C169" s="7"/>
       <c r="D169" s="11"/>
@@ -20272,7 +20745,7 @@
       <c r="CK169" s="7"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15">
+      <c r="A170" s="17">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -20365,7 +20838,7 @@
       <c r="CK170" s="6"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="5"/>
       <c r="C171" s="7"/>
       <c r="D171" s="11"/>
@@ -20456,7 +20929,7 @@
       <c r="CK171" s="7"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15">
+      <c r="A172" s="17">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -20549,7 +21022,7 @@
       <c r="CK172" s="6"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="5"/>
       <c r="C173" s="7"/>
       <c r="D173" s="11"/>
@@ -20640,7 +21113,7 @@
       <c r="CK173" s="7"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15">
+      <c r="A174" s="17">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -20733,7 +21206,7 @@
       <c r="CK174" s="6"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="5"/>
       <c r="C175" s="7"/>
       <c r="D175" s="11"/>
@@ -20824,7 +21297,7 @@
       <c r="CK175" s="7"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15">
+      <c r="A176" s="17">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -20917,7 +21390,7 @@
       <c r="CK176" s="6"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="5"/>
       <c r="C177" s="7"/>
       <c r="D177" s="11"/>
@@ -21008,7 +21481,7 @@
       <c r="CK177" s="7"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15">
+      <c r="A178" s="17">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -21101,7 +21574,7 @@
       <c r="CK178" s="6"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="5"/>
       <c r="C179" s="7"/>
       <c r="D179" s="11"/>
@@ -21192,7 +21665,7 @@
       <c r="CK179" s="7"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15">
+      <c r="A180" s="17">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -21285,7 +21758,7 @@
       <c r="CK180" s="6"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="5"/>
       <c r="C181" s="7"/>
       <c r="D181" s="11"/>
@@ -21376,7 +21849,7 @@
       <c r="CK181" s="7"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15">
+      <c r="A182" s="17">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -21469,7 +21942,7 @@
       <c r="CK182" s="6"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="5"/>
       <c r="C183" s="7"/>
       <c r="D183" s="11"/>
@@ -21560,7 +22033,7 @@
       <c r="CK183" s="7"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15">
+      <c r="A184" s="17">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -21653,7 +22126,7 @@
       <c r="CK184" s="6"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="5"/>
       <c r="C185" s="7"/>
       <c r="D185" s="11"/>
@@ -21744,7 +22217,7 @@
       <c r="CK185" s="7"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15">
+      <c r="A186" s="17">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -21837,7 +22310,7 @@
       <c r="CK186" s="6"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="5"/>
       <c r="C187" s="7"/>
       <c r="D187" s="11"/>
@@ -21928,7 +22401,7 @@
       <c r="CK187" s="7"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15">
+      <c r="A188" s="17">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -22021,7 +22494,7 @@
       <c r="CK188" s="6"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="5"/>
       <c r="C189" s="7"/>
       <c r="D189" s="11"/>
@@ -22112,7 +22585,7 @@
       <c r="CK189" s="7"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15">
+      <c r="A190" s="17">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -22205,7 +22678,7 @@
       <c r="CK190" s="6"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="5"/>
       <c r="C191" s="7"/>
       <c r="D191" s="11"/>
@@ -22297,36 +22770,91 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="BN1:BO1"/>
-    <mergeCell ref="BP1:BQ1"/>
-    <mergeCell ref="BR1:BS1"/>
-    <mergeCell ref="CD1:CE1"/>
-    <mergeCell ref="CF1:CG1"/>
-    <mergeCell ref="CH1:CI1"/>
-    <mergeCell ref="CJ1:CK1"/>
-    <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="BV1:BW1"/>
-    <mergeCell ref="BX1:BY1"/>
-    <mergeCell ref="BZ1:CA1"/>
-    <mergeCell ref="CB1:CC1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="BL1:BM1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -22351,91 +22879,36 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="BN1:BO1"/>
+    <mergeCell ref="BP1:BQ1"/>
+    <mergeCell ref="BR1:BS1"/>
+    <mergeCell ref="CD1:CE1"/>
+    <mergeCell ref="CF1:CG1"/>
+    <mergeCell ref="CH1:CI1"/>
+    <mergeCell ref="CJ1:CK1"/>
+    <mergeCell ref="BT1:BU1"/>
+    <mergeCell ref="BV1:BW1"/>
+    <mergeCell ref="BX1:BY1"/>
+    <mergeCell ref="BZ1:CA1"/>
+    <mergeCell ref="CB1:CC1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
@@ -22460,185 +22933,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="16">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="16">
+      <c r="C1" s="16"/>
+      <c r="D1" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15">
         <v>4</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
         <v>5</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15">
         <v>6</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15">
         <v>7</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15">
         <v>10</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15">
         <v>11</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15">
         <v>12</v>
       </c>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
         <v>13</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15">
         <v>14</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16">
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15">
         <v>15</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16">
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15">
         <v>16</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
         <v>17</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16">
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15">
         <v>18</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15">
         <v>19</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15">
         <v>20</v>
       </c>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16">
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
         <v>21</v>
       </c>
-      <c r="AQ1" s="16"/>
-      <c r="AR1" s="16">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15">
         <v>22</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16">
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15">
         <v>23</v>
       </c>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16">
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15">
         <v>24</v>
       </c>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16">
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
         <v>25</v>
       </c>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15">
         <v>26</v>
       </c>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15">
         <v>27</v>
       </c>
-      <c r="BC1" s="16"/>
-      <c r="BD1" s="16">
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15">
         <v>28</v>
       </c>
-      <c r="BE1" s="16"/>
-      <c r="BF1" s="16">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
         <v>29</v>
       </c>
-      <c r="BG1" s="16"/>
-      <c r="BH1" s="16">
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15">
         <v>30</v>
       </c>
-      <c r="BI1" s="16"/>
-      <c r="BJ1" s="16">
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15">
         <v>31</v>
       </c>
-      <c r="BK1" s="16"/>
-      <c r="BL1" s="16">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15">
         <v>32</v>
       </c>
-      <c r="BM1" s="16"/>
-      <c r="BN1" s="16">
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
         <v>33</v>
       </c>
-      <c r="BO1" s="16"/>
-      <c r="BP1" s="16">
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15">
         <v>34</v>
       </c>
-      <c r="BQ1" s="16"/>
-      <c r="BR1" s="16">
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15">
         <v>35</v>
       </c>
-      <c r="BS1" s="16"/>
-      <c r="BT1" s="16">
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15">
         <v>36</v>
       </c>
-      <c r="BU1" s="16"/>
-      <c r="BV1" s="16">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
         <v>37</v>
       </c>
-      <c r="BW1" s="16"/>
-      <c r="BX1" s="16">
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15">
         <v>38</v>
       </c>
-      <c r="BY1" s="16"/>
-      <c r="BZ1" s="16">
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15">
         <v>39</v>
       </c>
-      <c r="CA1" s="16"/>
-      <c r="CB1" s="16">
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15">
         <v>40</v>
       </c>
-      <c r="CC1" s="16"/>
-      <c r="CD1" s="16">
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15">
         <v>41</v>
       </c>
-      <c r="CE1" s="16"/>
-      <c r="CF1" s="16">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15">
         <v>42</v>
       </c>
-      <c r="CG1" s="16"/>
-      <c r="CH1" s="16">
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15">
         <v>43</v>
       </c>
-      <c r="CI1" s="16"/>
-      <c r="CJ1" s="16">
+      <c r="CI1" s="15"/>
+      <c r="CJ1" s="15">
         <v>44</v>
       </c>
-      <c r="CK1" s="16"/>
+      <c r="CK1" s="15"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -22731,7 +23204,7 @@
       <c r="CK2" s="6"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9"/>
@@ -22822,7 +23295,7 @@
       <c r="CK3" s="10"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -22915,7 +23388,7 @@
       <c r="CK4" s="6"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="11"/>
@@ -23006,7 +23479,7 @@
       <c r="CK5" s="7"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -23099,7 +23572,7 @@
       <c r="CK6" s="6"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="7"/>
       <c r="D7" s="11"/>
@@ -23190,7 +23663,7 @@
       <c r="CK7" s="7"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -23283,7 +23756,7 @@
       <c r="CK8" s="6"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="11"/>
@@ -23374,7 +23847,7 @@
       <c r="CK9" s="7"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -23467,7 +23940,7 @@
       <c r="CK10" s="6"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="7"/>
       <c r="D11" s="11"/>
@@ -23500,7 +23973,7 @@
       <c r="AE11" s="7"/>
       <c r="AF11" s="11"/>
       <c r="AG11" s="7"/>
-      <c r="AH11" s="11"/>
+      <c r="AH11"/>
       <c r="AI11" s="7"/>
       <c r="AJ11" s="11"/>
       <c r="AK11" s="7"/>
@@ -23558,7 +24031,7 @@
       <c r="CK11" s="7"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -23651,7 +24124,7 @@
       <c r="CK12" s="6"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11"/>
@@ -23742,7 +24215,7 @@
       <c r="CK13" s="7"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -23835,7 +24308,7 @@
       <c r="CK14" s="6"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="D15" s="11"/>
@@ -23926,7 +24399,7 @@
       <c r="CK15" s="7"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -24019,7 +24492,7 @@
       <c r="CK16" s="6"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="7"/>
       <c r="D17" s="11"/>
@@ -24110,7 +24583,7 @@
       <c r="CK17" s="7"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -24203,7 +24676,7 @@
       <c r="CK18" s="6"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="D19" s="11"/>
@@ -24294,7 +24767,7 @@
       <c r="CK19" s="7"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -24387,7 +24860,7 @@
       <c r="CK20" s="6"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5"/>
       <c r="C21" s="7"/>
       <c r="D21" s="9"/>
@@ -24478,7 +24951,7 @@
       <c r="CK21" s="7"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -24571,7 +25044,7 @@
       <c r="CK22" s="6"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5"/>
       <c r="C23" s="7"/>
       <c r="D23" s="11"/>
@@ -24662,7 +25135,7 @@
       <c r="CK23" s="7"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -24755,7 +25228,7 @@
       <c r="CK24" s="6"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="5"/>
       <c r="C25" s="7"/>
       <c r="D25" s="11"/>
@@ -24846,7 +25319,7 @@
       <c r="CK25" s="7"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -24939,7 +25412,7 @@
       <c r="CK26" s="6"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="11"/>
@@ -25030,7 +25503,7 @@
       <c r="CK27" s="7"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -25123,7 +25596,7 @@
       <c r="CK28" s="6"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="5"/>
       <c r="C29" s="7"/>
       <c r="D29" s="11"/>
@@ -25214,7 +25687,7 @@
       <c r="CK29" s="7"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -25307,7 +25780,7 @@
       <c r="CK30" s="6"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="5"/>
       <c r="C31" s="7"/>
       <c r="D31" s="11"/>
@@ -25398,7 +25871,7 @@
       <c r="CK31" s="7"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -25491,7 +25964,7 @@
       <c r="CK32" s="6"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="7"/>
       <c r="D33" s="11"/>
@@ -25582,7 +26055,7 @@
       <c r="CK33" s="7"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -25675,7 +26148,7 @@
       <c r="CK34" s="6"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="5"/>
       <c r="C35" s="7"/>
       <c r="D35" s="11"/>
@@ -25766,7 +26239,7 @@
       <c r="CK35" s="7"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -25859,7 +26332,7 @@
       <c r="CK36" s="6"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="11"/>
@@ -25950,7 +26423,7 @@
       <c r="CK37" s="7"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -26043,7 +26516,7 @@
       <c r="CK38" s="6"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="5"/>
       <c r="C39" s="7"/>
       <c r="D39" s="11"/>
@@ -26134,7 +26607,7 @@
       <c r="CK39" s="7"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -26227,7 +26700,7 @@
       <c r="CK40" s="6"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="5"/>
       <c r="C41" s="7"/>
       <c r="D41" s="11"/>
@@ -26318,7 +26791,7 @@
       <c r="CK41" s="7"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -26411,7 +26884,7 @@
       <c r="CK42" s="6"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="5"/>
       <c r="C43" s="7"/>
       <c r="D43" s="11"/>
@@ -26502,7 +26975,7 @@
       <c r="CK43" s="7"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -26595,7 +27068,7 @@
       <c r="CK44" s="6"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="5"/>
       <c r="C45" s="7"/>
       <c r="D45" s="11"/>
@@ -26686,7 +27159,7 @@
       <c r="CK45" s="7"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -26779,7 +27252,7 @@
       <c r="CK46" s="6"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="5"/>
       <c r="C47" s="7"/>
       <c r="D47" s="11"/>
@@ -26870,7 +27343,7 @@
       <c r="CK47" s="7"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="17">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -26963,7 +27436,7 @@
       <c r="CK48" s="6"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="5"/>
       <c r="C49" s="7"/>
       <c r="D49" s="11"/>
@@ -27054,7 +27527,7 @@
       <c r="CK49" s="7"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="17">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -27147,7 +27620,7 @@
       <c r="CK50" s="6"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="5"/>
       <c r="C51" s="7"/>
       <c r="D51" s="11"/>
@@ -27238,7 +27711,7 @@
       <c r="CK51" s="7"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="17">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -27331,7 +27804,7 @@
       <c r="CK52" s="6"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="5"/>
       <c r="C53" s="7"/>
       <c r="D53" s="11"/>
@@ -27422,7 +27895,7 @@
       <c r="CK53" s="7"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="17">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -27515,7 +27988,7 @@
       <c r="CK54" s="6"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
       <c r="D55" s="11"/>
@@ -27606,7 +28079,7 @@
       <c r="CK55" s="7"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="17">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -27699,7 +28172,7 @@
       <c r="CK56" s="6"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
       <c r="D57" s="11"/>
@@ -27790,7 +28263,7 @@
       <c r="CK57" s="7"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="17">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -27883,7 +28356,7 @@
       <c r="CK58" s="6"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
       <c r="D59" s="11"/>
@@ -27974,7 +28447,7 @@
       <c r="CK59" s="7"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="17">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -28067,7 +28540,7 @@
       <c r="CK60" s="6"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="5"/>
       <c r="C61" s="7"/>
       <c r="D61" s="11"/>
@@ -28158,7 +28631,7 @@
       <c r="CK61" s="7"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="17">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -28251,7 +28724,7 @@
       <c r="CK62" s="6"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="5"/>
       <c r="C63" s="7"/>
       <c r="D63" s="11"/>
@@ -28342,7 +28815,7 @@
       <c r="CK63" s="7"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -28435,7 +28908,7 @@
       <c r="CK64" s="6"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="5"/>
       <c r="C65" s="7"/>
       <c r="D65" s="11"/>
@@ -28526,7 +28999,7 @@
       <c r="CK65" s="7"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -28619,7 +29092,7 @@
       <c r="CK66" s="6"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="5"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
@@ -28710,7 +29183,7 @@
       <c r="CK67" s="7"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="17">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -28803,7 +29276,7 @@
       <c r="CK68" s="6"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="5"/>
       <c r="C69" s="7"/>
       <c r="D69" s="11"/>
@@ -28894,7 +29367,7 @@
       <c r="CK69" s="7"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="17">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -28987,7 +29460,7 @@
       <c r="CK70" s="6"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="5"/>
       <c r="C71" s="7"/>
       <c r="D71" s="11"/>
@@ -29078,7 +29551,7 @@
       <c r="CK71" s="7"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -29171,7 +29644,7 @@
       <c r="CK72" s="6"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="5"/>
       <c r="C73" s="7"/>
       <c r="D73" s="11"/>
@@ -29262,7 +29735,7 @@
       <c r="CK73" s="7"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="17">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -29355,7 +29828,7 @@
       <c r="CK74" s="6"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="5"/>
       <c r="C75" s="7"/>
       <c r="D75" s="11"/>
@@ -29446,7 +29919,7 @@
       <c r="CK75" s="7"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="17">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -29539,7 +30012,7 @@
       <c r="CK76" s="6"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="5"/>
       <c r="C77" s="7"/>
       <c r="D77" s="11"/>
@@ -29630,7 +30103,7 @@
       <c r="CK77" s="7"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="17">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -29723,7 +30196,7 @@
       <c r="CK78" s="6"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="5"/>
       <c r="C79" s="7"/>
       <c r="D79" s="11"/>
@@ -29814,7 +30287,7 @@
       <c r="CK79" s="7"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15">
+      <c r="A80" s="17">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -29907,7 +30380,7 @@
       <c r="CK80" s="6"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="5"/>
       <c r="C81" s="7"/>
       <c r="D81" s="11"/>
@@ -29998,7 +30471,7 @@
       <c r="CK81" s="7"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="17">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -30091,7 +30564,7 @@
       <c r="CK82" s="6"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="5"/>
       <c r="C83" s="7"/>
       <c r="D83" s="11"/>
@@ -30182,7 +30655,7 @@
       <c r="CK83" s="7"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="17">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -30275,7 +30748,7 @@
       <c r="CK84" s="6"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="5"/>
       <c r="C85" s="7"/>
       <c r="D85" s="11"/>
@@ -30366,7 +30839,7 @@
       <c r="CK85" s="7"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15">
+      <c r="A86" s="17">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -30459,7 +30932,7 @@
       <c r="CK86" s="6"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="5"/>
       <c r="C87" s="7"/>
       <c r="D87" s="11"/>
@@ -30550,7 +31023,7 @@
       <c r="CK87" s="7"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15">
+      <c r="A88" s="17">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -30643,7 +31116,7 @@
       <c r="CK88" s="6"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="5"/>
       <c r="C89" s="7"/>
       <c r="D89" s="11"/>
@@ -30734,7 +31207,7 @@
       <c r="CK89" s="7"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15">
+      <c r="A90" s="17">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -30827,7 +31300,7 @@
       <c r="CK90" s="6"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="5"/>
       <c r="C91" s="7"/>
       <c r="D91" s="11"/>
@@ -30918,7 +31391,7 @@
       <c r="CK91" s="7"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15">
+      <c r="A92" s="17">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -31011,7 +31484,7 @@
       <c r="CK92" s="6"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="5"/>
       <c r="C93" s="7"/>
       <c r="D93" s="11"/>
@@ -31102,7 +31575,7 @@
       <c r="CK93" s="7"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15">
+      <c r="A94" s="17">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -31195,7 +31668,7 @@
       <c r="CK94" s="6"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="5"/>
       <c r="C95" s="7"/>
       <c r="D95" s="11"/>
@@ -31286,7 +31759,7 @@
       <c r="CK95" s="7"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="17">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -31379,7 +31852,7 @@
       <c r="CK96" s="6"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="5"/>
       <c r="C97" s="7"/>
       <c r="D97" s="11"/>
@@ -31470,7 +31943,7 @@
       <c r="CK97" s="7"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="17">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -31563,7 +32036,7 @@
       <c r="CK98" s="6"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="5"/>
       <c r="C99" s="7"/>
       <c r="D99" s="11"/>
@@ -31654,7 +32127,7 @@
       <c r="CK99" s="7"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="17">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -31747,7 +32220,7 @@
       <c r="CK100" s="6"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="5"/>
       <c r="C101" s="7"/>
       <c r="D101" s="11"/>
@@ -31838,7 +32311,7 @@
       <c r="CK101" s="7"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="17">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -31931,7 +32404,7 @@
       <c r="CK102" s="6"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="5"/>
       <c r="C103" s="7"/>
       <c r="D103" s="11"/>
@@ -32022,7 +32495,7 @@
       <c r="CK103" s="7"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="17">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -32115,7 +32588,7 @@
       <c r="CK104" s="6"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="5"/>
       <c r="C105" s="7"/>
       <c r="D105" s="11"/>
@@ -32206,7 +32679,7 @@
       <c r="CK105" s="7"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="17">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -32299,7 +32772,7 @@
       <c r="CK106" s="6"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="5"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
@@ -32390,7 +32863,7 @@
       <c r="CK107" s="7"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="17">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -32483,7 +32956,7 @@
       <c r="CK108" s="6"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="5"/>
       <c r="C109" s="7"/>
       <c r="D109" s="11"/>
@@ -32574,7 +33047,7 @@
       <c r="CK109" s="7"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="17">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -32667,7 +33140,7 @@
       <c r="CK110" s="6"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="5"/>
       <c r="C111" s="7"/>
       <c r="D111" s="11"/>
@@ -32758,7 +33231,7 @@
       <c r="CK111" s="7"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="17">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -32851,7 +33324,7 @@
       <c r="CK112" s="6"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="5"/>
       <c r="C113" s="7"/>
       <c r="D113" s="11"/>
@@ -32942,7 +33415,7 @@
       <c r="CK113" s="7"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="17">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -33035,7 +33508,7 @@
       <c r="CK114" s="6"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="5"/>
       <c r="C115" s="7"/>
       <c r="D115" s="11"/>
@@ -33126,7 +33599,7 @@
       <c r="CK115" s="7"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="17">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -33219,7 +33692,7 @@
       <c r="CK116" s="6"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="5"/>
       <c r="C117" s="7"/>
       <c r="D117" s="11"/>
@@ -33310,7 +33783,7 @@
       <c r="CK117" s="7"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="17">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -33403,7 +33876,7 @@
       <c r="CK118" s="6"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="5"/>
       <c r="C119" s="7"/>
       <c r="D119" s="11"/>
@@ -33494,7 +33967,7 @@
       <c r="CK119" s="7"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="17">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -33587,7 +34060,7 @@
       <c r="CK120" s="6"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="5"/>
       <c r="C121" s="7"/>
       <c r="D121" s="11"/>
@@ -33678,7 +34151,7 @@
       <c r="CK121" s="7"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="17">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -33771,7 +34244,7 @@
       <c r="CK122" s="6"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="5"/>
       <c r="C123" s="7"/>
       <c r="D123" s="11"/>
@@ -33862,7 +34335,7 @@
       <c r="CK123" s="7"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="17">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -33955,7 +34428,7 @@
       <c r="CK124" s="6"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="5"/>
       <c r="C125" s="7"/>
       <c r="D125" s="11"/>
@@ -34046,7 +34519,7 @@
       <c r="CK125" s="7"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="17">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -34139,7 +34612,7 @@
       <c r="CK126" s="6"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="5"/>
       <c r="C127" s="7"/>
       <c r="D127" s="11"/>
@@ -34230,7 +34703,7 @@
       <c r="CK127" s="7"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="17">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -34323,7 +34796,7 @@
       <c r="CK128" s="6"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="5"/>
       <c r="C129" s="7"/>
       <c r="D129" s="11"/>
@@ -34414,7 +34887,7 @@
       <c r="CK129" s="7"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="17">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -34507,7 +34980,7 @@
       <c r="CK130" s="6"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="5"/>
       <c r="C131" s="7"/>
       <c r="D131" s="11"/>
@@ -34598,7 +35071,7 @@
       <c r="CK131" s="7"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="17">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -34691,7 +35164,7 @@
       <c r="CK132" s="6"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
       <c r="D133" s="11"/>
@@ -34782,7 +35255,7 @@
       <c r="CK133" s="7"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15">
+      <c r="A134" s="17">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -34875,7 +35348,7 @@
       <c r="CK134" s="6"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="5"/>
       <c r="C135" s="7"/>
       <c r="D135" s="11"/>
@@ -34966,7 +35439,7 @@
       <c r="CK135" s="7"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="17">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -35059,7 +35532,7 @@
       <c r="CK136" s="6"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
       <c r="D137" s="11"/>
@@ -35150,7 +35623,7 @@
       <c r="CK137" s="7"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="17">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -35243,7 +35716,7 @@
       <c r="CK138" s="6"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="5"/>
       <c r="C139" s="7"/>
       <c r="D139" s="11"/>
@@ -35334,7 +35807,7 @@
       <c r="CK139" s="7"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15">
+      <c r="A140" s="17">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -35427,7 +35900,7 @@
       <c r="CK140" s="6"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="5"/>
       <c r="C141" s="7"/>
       <c r="D141" s="11"/>
@@ -35518,7 +35991,7 @@
       <c r="CK141" s="7"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15">
+      <c r="A142" s="17">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -35611,7 +36084,7 @@
       <c r="CK142" s="6"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="5"/>
       <c r="C143" s="7"/>
       <c r="D143" s="11"/>
@@ -35702,7 +36175,7 @@
       <c r="CK143" s="7"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15">
+      <c r="A144" s="17">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -35795,7 +36268,7 @@
       <c r="CK144" s="6"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="5"/>
       <c r="C145" s="7"/>
       <c r="D145" s="11"/>
@@ -35886,7 +36359,7 @@
       <c r="CK145" s="7"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15">
+      <c r="A146" s="17">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -35979,7 +36452,7 @@
       <c r="CK146" s="6"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="5"/>
       <c r="C147" s="7"/>
       <c r="D147" s="11"/>
@@ -36070,7 +36543,7 @@
       <c r="CK147" s="7"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15">
+      <c r="A148" s="17">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -36163,7 +36636,7 @@
       <c r="CK148" s="6"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="5"/>
       <c r="C149" s="7"/>
       <c r="D149" s="11"/>
@@ -36254,7 +36727,7 @@
       <c r="CK149" s="7"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15">
+      <c r="A150" s="17">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -36347,7 +36820,7 @@
       <c r="CK150" s="6"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="5"/>
       <c r="C151" s="7"/>
       <c r="D151" s="11"/>
@@ -36438,7 +36911,7 @@
       <c r="CK151" s="7"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15">
+      <c r="A152" s="17">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -36531,7 +37004,7 @@
       <c r="CK152" s="6"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="5"/>
       <c r="C153" s="7"/>
       <c r="D153" s="11"/>
@@ -36622,7 +37095,7 @@
       <c r="CK153" s="7"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15">
+      <c r="A154" s="17">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -36715,7 +37188,7 @@
       <c r="CK154" s="6"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="5"/>
       <c r="C155" s="7"/>
       <c r="D155" s="11"/>
@@ -36806,7 +37279,7 @@
       <c r="CK155" s="7"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15">
+      <c r="A156" s="17">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -36899,7 +37372,7 @@
       <c r="CK156" s="6"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="5"/>
       <c r="C157" s="7"/>
       <c r="D157" s="11"/>
@@ -36990,7 +37463,7 @@
       <c r="CK157" s="7"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15">
+      <c r="A158" s="17">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -37083,7 +37556,7 @@
       <c r="CK158" s="6"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="5"/>
       <c r="C159" s="7"/>
       <c r="D159" s="11"/>
@@ -37174,7 +37647,7 @@
       <c r="CK159" s="7"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15">
+      <c r="A160" s="17">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -37267,7 +37740,7 @@
       <c r="CK160" s="6"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="5"/>
       <c r="C161" s="7"/>
       <c r="D161" s="11"/>
@@ -37358,7 +37831,7 @@
       <c r="CK161" s="7"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15">
+      <c r="A162" s="17">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -37451,7 +37924,7 @@
       <c r="CK162" s="6"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="5"/>
       <c r="C163" s="7"/>
       <c r="D163" s="11"/>
@@ -37542,7 +38015,7 @@
       <c r="CK163" s="7"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15">
+      <c r="A164" s="17">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -37635,7 +38108,7 @@
       <c r="CK164" s="6"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="5"/>
       <c r="C165" s="7"/>
       <c r="D165" s="11"/>
@@ -37726,7 +38199,7 @@
       <c r="CK165" s="7"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15">
+      <c r="A166" s="17">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -37819,7 +38292,7 @@
       <c r="CK166" s="6"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="5"/>
       <c r="C167" s="7"/>
       <c r="D167" s="11"/>
@@ -37910,7 +38383,7 @@
       <c r="CK167" s="7"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15">
+      <c r="A168" s="17">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -38003,7 +38476,7 @@
       <c r="CK168" s="6"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="5"/>
       <c r="C169" s="7"/>
       <c r="D169" s="11"/>
@@ -38094,7 +38567,7 @@
       <c r="CK169" s="7"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15">
+      <c r="A170" s="17">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -38187,7 +38660,7 @@
       <c r="CK170" s="6"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="5"/>
       <c r="C171" s="7"/>
       <c r="D171" s="11"/>
@@ -38278,7 +38751,7 @@
       <c r="CK171" s="7"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15">
+      <c r="A172" s="17">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -38371,7 +38844,7 @@
       <c r="CK172" s="6"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="5"/>
       <c r="C173" s="7"/>
       <c r="D173" s="11"/>
@@ -38462,7 +38935,7 @@
       <c r="CK173" s="7"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15">
+      <c r="A174" s="17">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -38555,7 +39028,7 @@
       <c r="CK174" s="6"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="5"/>
       <c r="C175" s="7"/>
       <c r="D175" s="11"/>
@@ -38646,7 +39119,7 @@
       <c r="CK175" s="7"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15">
+      <c r="A176" s="17">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -38739,7 +39212,7 @@
       <c r="CK176" s="6"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="5"/>
       <c r="C177" s="7"/>
       <c r="D177" s="11"/>
@@ -38830,7 +39303,7 @@
       <c r="CK177" s="7"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15">
+      <c r="A178" s="17">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -38923,7 +39396,7 @@
       <c r="CK178" s="6"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="5"/>
       <c r="C179" s="7"/>
       <c r="D179" s="11"/>
@@ -39014,7 +39487,7 @@
       <c r="CK179" s="7"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15">
+      <c r="A180" s="17">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -39107,7 +39580,7 @@
       <c r="CK180" s="6"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="5"/>
       <c r="C181" s="7"/>
       <c r="D181" s="11"/>
@@ -39198,7 +39671,7 @@
       <c r="CK181" s="7"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15">
+      <c r="A182" s="17">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -39291,7 +39764,7 @@
       <c r="CK182" s="6"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="5"/>
       <c r="C183" s="7"/>
       <c r="D183" s="11"/>
@@ -39382,7 +39855,7 @@
       <c r="CK183" s="7"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15">
+      <c r="A184" s="17">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -39475,7 +39948,7 @@
       <c r="CK184" s="6"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="5"/>
       <c r="C185" s="7"/>
       <c r="D185" s="11"/>
@@ -39566,7 +40039,7 @@
       <c r="CK185" s="7"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15">
+      <c r="A186" s="17">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -39659,7 +40132,7 @@
       <c r="CK186" s="6"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="5"/>
       <c r="C187" s="7"/>
       <c r="D187" s="11"/>
@@ -39750,7 +40223,7 @@
       <c r="CK187" s="7"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15">
+      <c r="A188" s="17">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -39843,7 +40316,7 @@
       <c r="CK188" s="6"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="5"/>
       <c r="C189" s="7"/>
       <c r="D189" s="11"/>
@@ -39934,7 +40407,7 @@
       <c r="CK189" s="7"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15">
+      <c r="A190" s="17">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -40027,7 +40500,7 @@
       <c r="CK190" s="6"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="5"/>
       <c r="C191" s="7"/>
       <c r="D191" s="11"/>
@@ -40119,91 +40592,36 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -40228,36 +40646,91 @@
     <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
@@ -40282,185 +40755,185 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="18">
+      <c r="B1" s="16">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="16">
+      <c r="C1" s="16"/>
+      <c r="D1" s="15">
         <v>2</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15">
         <v>3</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15">
         <v>4</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16">
+      <c r="I1" s="15"/>
+      <c r="J1" s="15">
         <v>5</v>
       </c>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15">
         <v>6</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16">
+      <c r="M1" s="15"/>
+      <c r="N1" s="15">
         <v>7</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16">
+      <c r="O1" s="15"/>
+      <c r="P1" s="15">
         <v>8</v>
       </c>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15">
         <v>9</v>
       </c>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15">
         <v>10</v>
       </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16">
+      <c r="U1" s="15"/>
+      <c r="V1" s="15">
         <v>11</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15">
         <v>12</v>
       </c>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16">
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15">
         <v>13</v>
       </c>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15">
         <v>14</v>
       </c>
-      <c r="AC1" s="16"/>
-      <c r="AD1" s="16">
+      <c r="AC1" s="15"/>
+      <c r="AD1" s="15">
         <v>15</v>
       </c>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16">
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15">
         <v>16</v>
       </c>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16">
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15">
         <v>17</v>
       </c>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16">
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15">
         <v>18</v>
       </c>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15">
         <v>19</v>
       </c>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15">
         <v>20</v>
       </c>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16">
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15">
         <v>21</v>
       </c>
-      <c r="AQ1" s="16"/>
-      <c r="AR1" s="16">
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15">
         <v>22</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16">
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15">
         <v>23</v>
       </c>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16">
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15">
         <v>24</v>
       </c>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16">
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15">
         <v>25</v>
       </c>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15">
         <v>26</v>
       </c>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16">
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15">
         <v>27</v>
       </c>
-      <c r="BC1" s="16"/>
-      <c r="BD1" s="16">
+      <c r="BC1" s="15"/>
+      <c r="BD1" s="15">
         <v>28</v>
       </c>
-      <c r="BE1" s="16"/>
-      <c r="BF1" s="16">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15">
         <v>29</v>
       </c>
-      <c r="BG1" s="16"/>
-      <c r="BH1" s="16">
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15">
         <v>30</v>
       </c>
-      <c r="BI1" s="16"/>
-      <c r="BJ1" s="16">
+      <c r="BI1" s="15"/>
+      <c r="BJ1" s="15">
         <v>31</v>
       </c>
-      <c r="BK1" s="16"/>
-      <c r="BL1" s="16">
+      <c r="BK1" s="15"/>
+      <c r="BL1" s="15">
         <v>32</v>
       </c>
-      <c r="BM1" s="16"/>
-      <c r="BN1" s="16">
+      <c r="BM1" s="15"/>
+      <c r="BN1" s="15">
         <v>33</v>
       </c>
-      <c r="BO1" s="16"/>
-      <c r="BP1" s="16">
+      <c r="BO1" s="15"/>
+      <c r="BP1" s="15">
         <v>34</v>
       </c>
-      <c r="BQ1" s="16"/>
-      <c r="BR1" s="16">
+      <c r="BQ1" s="15"/>
+      <c r="BR1" s="15">
         <v>35</v>
       </c>
-      <c r="BS1" s="16"/>
-      <c r="BT1" s="16">
+      <c r="BS1" s="15"/>
+      <c r="BT1" s="15">
         <v>36</v>
       </c>
-      <c r="BU1" s="16"/>
-      <c r="BV1" s="16">
+      <c r="BU1" s="15"/>
+      <c r="BV1" s="15">
         <v>37</v>
       </c>
-      <c r="BW1" s="16"/>
-      <c r="BX1" s="16">
+      <c r="BW1" s="15"/>
+      <c r="BX1" s="15">
         <v>38</v>
       </c>
-      <c r="BY1" s="16"/>
-      <c r="BZ1" s="16">
+      <c r="BY1" s="15"/>
+      <c r="BZ1" s="15">
         <v>39</v>
       </c>
-      <c r="CA1" s="16"/>
-      <c r="CB1" s="16">
+      <c r="CA1" s="15"/>
+      <c r="CB1" s="15">
         <v>40</v>
       </c>
-      <c r="CC1" s="16"/>
-      <c r="CD1" s="16">
+      <c r="CC1" s="15"/>
+      <c r="CD1" s="15">
         <v>41</v>
       </c>
-      <c r="CE1" s="16"/>
-      <c r="CF1" s="16">
+      <c r="CE1" s="15"/>
+      <c r="CF1" s="15">
         <v>42</v>
       </c>
-      <c r="CG1" s="16"/>
-      <c r="CH1" s="16">
+      <c r="CG1" s="15"/>
+      <c r="CH1" s="15">
         <v>43</v>
       </c>
-      <c r="CI1" s="16"/>
-      <c r="CJ1" s="16">
+      <c r="CI1" s="15"/>
+      <c r="CJ1" s="15">
         <v>44</v>
       </c>
-      <c r="CK1" s="16"/>
+      <c r="CK1" s="15"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="4"/>
@@ -40553,7 +41026,7 @@
       <c r="CK2" s="6"/>
     </row>
     <row r="3" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
       <c r="D3" s="9"/>
@@ -40644,7 +41117,7 @@
       <c r="CK3" s="10"/>
     </row>
     <row r="4" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
       <c r="B4" s="4"/>
@@ -40737,7 +41210,7 @@
       <c r="CK4" s="6"/>
     </row>
     <row r="5" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="11"/>
@@ -40828,7 +41301,7 @@
       <c r="CK5" s="7"/>
     </row>
     <row r="6" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="4"/>
@@ -40921,7 +41394,7 @@
       <c r="CK6" s="6"/>
     </row>
     <row r="7" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="7"/>
       <c r="D7" s="11"/>
@@ -41012,7 +41485,7 @@
       <c r="CK7" s="7"/>
     </row>
     <row r="8" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="17">
         <v>4</v>
       </c>
       <c r="B8" s="4"/>
@@ -41105,7 +41578,7 @@
       <c r="CK8" s="6"/>
     </row>
     <row r="9" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="11"/>
@@ -41196,7 +41669,7 @@
       <c r="CK9" s="7"/>
     </row>
     <row r="10" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="17">
         <v>5</v>
       </c>
       <c r="B10" s="4"/>
@@ -41289,7 +41762,7 @@
       <c r="CK10" s="6"/>
     </row>
     <row r="11" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="7"/>
       <c r="D11" s="11"/>
@@ -41380,7 +41853,7 @@
       <c r="CK11" s="7"/>
     </row>
     <row r="12" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
@@ -41473,7 +41946,7 @@
       <c r="CK12" s="6"/>
     </row>
     <row r="13" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="7"/>
       <c r="D13" s="11"/>
@@ -41564,7 +42037,7 @@
       <c r="CK13" s="7"/>
     </row>
     <row r="14" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>7</v>
       </c>
       <c r="B14" s="4"/>
@@ -41657,7 +42130,7 @@
       <c r="CK14" s="6"/>
     </row>
     <row r="15" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="7"/>
       <c r="D15" s="11"/>
@@ -41748,7 +42221,7 @@
       <c r="CK15" s="7"/>
     </row>
     <row r="16" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="17">
         <v>8</v>
       </c>
       <c r="B16" s="4"/>
@@ -41841,7 +42314,7 @@
       <c r="CK16" s="6"/>
     </row>
     <row r="17" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5"/>
       <c r="C17" s="7"/>
       <c r="D17" s="11"/>
@@ -41932,7 +42405,7 @@
       <c r="CK17" s="7"/>
     </row>
     <row r="18" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="17">
         <v>9</v>
       </c>
       <c r="B18" s="4"/>
@@ -42025,7 +42498,7 @@
       <c r="CK18" s="6"/>
     </row>
     <row r="19" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5"/>
       <c r="C19" s="7"/>
       <c r="D19" s="11"/>
@@ -42116,7 +42589,7 @@
       <c r="CK19" s="7"/>
     </row>
     <row r="20" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="17">
         <v>10</v>
       </c>
       <c r="B20" s="4"/>
@@ -42209,7 +42682,7 @@
       <c r="CK20" s="6"/>
     </row>
     <row r="21" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5"/>
       <c r="C21" s="7"/>
       <c r="D21" s="9"/>
@@ -42300,7 +42773,7 @@
       <c r="CK21" s="7"/>
     </row>
     <row r="22" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15">
+      <c r="A22" s="17">
         <v>11</v>
       </c>
       <c r="B22" s="4"/>
@@ -42393,7 +42866,7 @@
       <c r="CK22" s="6"/>
     </row>
     <row r="23" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="5"/>
       <c r="C23" s="7"/>
       <c r="D23" s="11"/>
@@ -42484,7 +42957,7 @@
       <c r="CK23" s="7"/>
     </row>
     <row r="24" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15">
+      <c r="A24" s="17">
         <v>12</v>
       </c>
       <c r="B24" s="4"/>
@@ -42577,7 +43050,7 @@
       <c r="CK24" s="6"/>
     </row>
     <row r="25" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="5"/>
       <c r="C25" s="7"/>
       <c r="D25" s="11"/>
@@ -42668,7 +43141,7 @@
       <c r="CK25" s="7"/>
     </row>
     <row r="26" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15">
+      <c r="A26" s="17">
         <v>13</v>
       </c>
       <c r="B26" s="4"/>
@@ -42761,7 +43234,7 @@
       <c r="CK26" s="6"/>
     </row>
     <row r="27" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="11"/>
@@ -42852,7 +43325,7 @@
       <c r="CK27" s="7"/>
     </row>
     <row r="28" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15">
+      <c r="A28" s="17">
         <v>14</v>
       </c>
       <c r="B28" s="4"/>
@@ -42945,7 +43418,7 @@
       <c r="CK28" s="6"/>
     </row>
     <row r="29" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="5"/>
       <c r="C29" s="7"/>
       <c r="D29" s="11"/>
@@ -43036,7 +43509,7 @@
       <c r="CK29" s="7"/>
     </row>
     <row r="30" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="17">
         <v>15</v>
       </c>
       <c r="B30" s="4"/>
@@ -43129,7 +43602,7 @@
       <c r="CK30" s="6"/>
     </row>
     <row r="31" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="5"/>
       <c r="C31" s="7"/>
       <c r="D31" s="11"/>
@@ -43220,7 +43693,7 @@
       <c r="CK31" s="7"/>
     </row>
     <row r="32" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="17">
         <v>16</v>
       </c>
       <c r="B32" s="4"/>
@@ -43313,7 +43786,7 @@
       <c r="CK32" s="6"/>
     </row>
     <row r="33" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="5"/>
       <c r="C33" s="7"/>
       <c r="D33" s="11"/>
@@ -43404,7 +43877,7 @@
       <c r="CK33" s="7"/>
     </row>
     <row r="34" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15">
+      <c r="A34" s="17">
         <v>17</v>
       </c>
       <c r="B34" s="4"/>
@@ -43497,7 +43970,7 @@
       <c r="CK34" s="6"/>
     </row>
     <row r="35" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="5"/>
       <c r="C35" s="7"/>
       <c r="D35" s="11"/>
@@ -43588,7 +44061,7 @@
       <c r="CK35" s="7"/>
     </row>
     <row r="36" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15">
+      <c r="A36" s="17">
         <v>18</v>
       </c>
       <c r="B36" s="4"/>
@@ -43681,7 +44154,7 @@
       <c r="CK36" s="6"/>
     </row>
     <row r="37" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="5"/>
       <c r="C37" s="7"/>
       <c r="D37" s="11"/>
@@ -43772,7 +44245,7 @@
       <c r="CK37" s="7"/>
     </row>
     <row r="38" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15">
+      <c r="A38" s="17">
         <v>19</v>
       </c>
       <c r="B38" s="4"/>
@@ -43865,7 +44338,7 @@
       <c r="CK38" s="6"/>
     </row>
     <row r="39" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="15"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="5"/>
       <c r="C39" s="7"/>
       <c r="D39" s="11"/>
@@ -43956,7 +44429,7 @@
       <c r="CK39" s="7"/>
     </row>
     <row r="40" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15">
+      <c r="A40" s="17">
         <v>20</v>
       </c>
       <c r="B40" s="4"/>
@@ -44049,7 +44522,7 @@
       <c r="CK40" s="6"/>
     </row>
     <row r="41" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="5"/>
       <c r="C41" s="7"/>
       <c r="D41" s="11"/>
@@ -44140,7 +44613,7 @@
       <c r="CK41" s="7"/>
     </row>
     <row r="42" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15">
+      <c r="A42" s="17">
         <v>21</v>
       </c>
       <c r="B42" s="4"/>
@@ -44233,7 +44706,7 @@
       <c r="CK42" s="6"/>
     </row>
     <row r="43" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="5"/>
       <c r="C43" s="7"/>
       <c r="D43" s="11"/>
@@ -44324,7 +44797,7 @@
       <c r="CK43" s="7"/>
     </row>
     <row r="44" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15">
+      <c r="A44" s="17">
         <v>22</v>
       </c>
       <c r="B44" s="4"/>
@@ -44417,7 +44890,7 @@
       <c r="CK44" s="6"/>
     </row>
     <row r="45" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="5"/>
       <c r="C45" s="7"/>
       <c r="D45" s="11"/>
@@ -44508,7 +44981,7 @@
       <c r="CK45" s="7"/>
     </row>
     <row r="46" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15">
+      <c r="A46" s="17">
         <v>23</v>
       </c>
       <c r="B46" s="4"/>
@@ -44601,7 +45074,7 @@
       <c r="CK46" s="6"/>
     </row>
     <row r="47" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="5"/>
       <c r="C47" s="7"/>
       <c r="D47" s="11"/>
@@ -44692,7 +45165,7 @@
       <c r="CK47" s="7"/>
     </row>
     <row r="48" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15">
+      <c r="A48" s="17">
         <v>24</v>
       </c>
       <c r="B48" s="4"/>
@@ -44785,7 +45258,7 @@
       <c r="CK48" s="6"/>
     </row>
     <row r="49" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="5"/>
       <c r="C49" s="7"/>
       <c r="D49" s="11"/>
@@ -44876,7 +45349,7 @@
       <c r="CK49" s="7"/>
     </row>
     <row r="50" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15">
+      <c r="A50" s="17">
         <v>25</v>
       </c>
       <c r="B50" s="4"/>
@@ -44969,7 +45442,7 @@
       <c r="CK50" s="6"/>
     </row>
     <row r="51" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="5"/>
       <c r="C51" s="7"/>
       <c r="D51" s="11"/>
@@ -45060,7 +45533,7 @@
       <c r="CK51" s="7"/>
     </row>
     <row r="52" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15">
+      <c r="A52" s="17">
         <v>26</v>
       </c>
       <c r="B52" s="4"/>
@@ -45153,7 +45626,7 @@
       <c r="CK52" s="6"/>
     </row>
     <row r="53" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="5"/>
       <c r="C53" s="7"/>
       <c r="D53" s="11"/>
@@ -45244,7 +45717,7 @@
       <c r="CK53" s="7"/>
     </row>
     <row r="54" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15">
+      <c r="A54" s="17">
         <v>27</v>
       </c>
       <c r="B54" s="4"/>
@@ -45337,7 +45810,7 @@
       <c r="CK54" s="6"/>
     </row>
     <row r="55" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
       <c r="D55" s="11"/>
@@ -45428,7 +45901,7 @@
       <c r="CK55" s="7"/>
     </row>
     <row r="56" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15">
+      <c r="A56" s="17">
         <v>28</v>
       </c>
       <c r="B56" s="4"/>
@@ -45521,7 +45994,7 @@
       <c r="CK56" s="6"/>
     </row>
     <row r="57" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
       <c r="D57" s="11"/>
@@ -45612,7 +46085,7 @@
       <c r="CK57" s="7"/>
     </row>
     <row r="58" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15">
+      <c r="A58" s="17">
         <v>29</v>
       </c>
       <c r="B58" s="4"/>
@@ -45705,7 +46178,7 @@
       <c r="CK58" s="6"/>
     </row>
     <row r="59" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
       <c r="D59" s="11"/>
@@ -45796,7 +46269,7 @@
       <c r="CK59" s="7"/>
     </row>
     <row r="60" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15">
+      <c r="A60" s="17">
         <v>30</v>
       </c>
       <c r="B60" s="4"/>
@@ -45889,7 +46362,7 @@
       <c r="CK60" s="6"/>
     </row>
     <row r="61" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="5"/>
       <c r="C61" s="7"/>
       <c r="D61" s="11"/>
@@ -45980,7 +46453,7 @@
       <c r="CK61" s="7"/>
     </row>
     <row r="62" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15">
+      <c r="A62" s="17">
         <v>31</v>
       </c>
       <c r="B62" s="4"/>
@@ -46073,7 +46546,7 @@
       <c r="CK62" s="6"/>
     </row>
     <row r="63" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="5"/>
       <c r="C63" s="7"/>
       <c r="D63" s="11"/>
@@ -46164,7 +46637,7 @@
       <c r="CK63" s="7"/>
     </row>
     <row r="64" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15">
+      <c r="A64" s="17">
         <v>32</v>
       </c>
       <c r="B64" s="4"/>
@@ -46257,7 +46730,7 @@
       <c r="CK64" s="6"/>
     </row>
     <row r="65" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="5"/>
       <c r="C65" s="7"/>
       <c r="D65" s="11"/>
@@ -46348,7 +46821,7 @@
       <c r="CK65" s="7"/>
     </row>
     <row r="66" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15">
+      <c r="A66" s="17">
         <v>33</v>
       </c>
       <c r="B66" s="4"/>
@@ -46441,7 +46914,7 @@
       <c r="CK66" s="6"/>
     </row>
     <row r="67" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="5"/>
       <c r="C67" s="7"/>
       <c r="D67" s="11"/>
@@ -46532,7 +47005,7 @@
       <c r="CK67" s="7"/>
     </row>
     <row r="68" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15">
+      <c r="A68" s="17">
         <v>34</v>
       </c>
       <c r="B68" s="4"/>
@@ -46625,7 +47098,7 @@
       <c r="CK68" s="6"/>
     </row>
     <row r="69" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="5"/>
       <c r="C69" s="7"/>
       <c r="D69" s="11"/>
@@ -46716,7 +47189,7 @@
       <c r="CK69" s="7"/>
     </row>
     <row r="70" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15">
+      <c r="A70" s="17">
         <v>35</v>
       </c>
       <c r="B70" s="4"/>
@@ -46809,7 +47282,7 @@
       <c r="CK70" s="6"/>
     </row>
     <row r="71" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="5"/>
       <c r="C71" s="7"/>
       <c r="D71" s="11"/>
@@ -46900,7 +47373,7 @@
       <c r="CK71" s="7"/>
     </row>
     <row r="72" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15">
+      <c r="A72" s="17">
         <v>36</v>
       </c>
       <c r="B72" s="4"/>
@@ -46993,7 +47466,7 @@
       <c r="CK72" s="6"/>
     </row>
     <row r="73" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="5"/>
       <c r="C73" s="7"/>
       <c r="D73" s="11"/>
@@ -47084,7 +47557,7 @@
       <c r="CK73" s="7"/>
     </row>
     <row r="74" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15">
+      <c r="A74" s="17">
         <v>37</v>
       </c>
       <c r="B74" s="4"/>
@@ -47177,7 +47650,7 @@
       <c r="CK74" s="6"/>
     </row>
     <row r="75" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="5"/>
       <c r="C75" s="7"/>
       <c r="D75" s="11"/>
@@ -47268,7 +47741,7 @@
       <c r="CK75" s="7"/>
     </row>
     <row r="76" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15">
+      <c r="A76" s="17">
         <v>38</v>
       </c>
       <c r="B76" s="4"/>
@@ -47361,7 +47834,7 @@
       <c r="CK76" s="6"/>
     </row>
     <row r="77" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="5"/>
       <c r="C77" s="7"/>
       <c r="D77" s="11"/>
@@ -47452,7 +47925,7 @@
       <c r="CK77" s="7"/>
     </row>
     <row r="78" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15">
+      <c r="A78" s="17">
         <v>39</v>
       </c>
       <c r="B78" s="4"/>
@@ -47545,7 +48018,7 @@
       <c r="CK78" s="6"/>
     </row>
     <row r="79" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="15"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="5"/>
       <c r="C79" s="7"/>
       <c r="D79" s="11"/>
@@ -47636,7 +48109,7 @@
       <c r="CK79" s="7"/>
     </row>
     <row r="80" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15">
+      <c r="A80" s="17">
         <v>40</v>
       </c>
       <c r="B80" s="4"/>
@@ -47729,7 +48202,7 @@
       <c r="CK80" s="6"/>
     </row>
     <row r="81" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="15"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="5"/>
       <c r="C81" s="7"/>
       <c r="D81" s="11"/>
@@ -47820,7 +48293,7 @@
       <c r="CK81" s="7"/>
     </row>
     <row r="82" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15">
+      <c r="A82" s="17">
         <v>41</v>
       </c>
       <c r="B82" s="4"/>
@@ -47913,7 +48386,7 @@
       <c r="CK82" s="6"/>
     </row>
     <row r="83" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="15"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="5"/>
       <c r="C83" s="7"/>
       <c r="D83" s="11"/>
@@ -48004,7 +48477,7 @@
       <c r="CK83" s="7"/>
     </row>
     <row r="84" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15">
+      <c r="A84" s="17">
         <v>42</v>
       </c>
       <c r="B84" s="4"/>
@@ -48097,7 +48570,7 @@
       <c r="CK84" s="6"/>
     </row>
     <row r="85" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="15"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="5"/>
       <c r="C85" s="7"/>
       <c r="D85" s="11"/>
@@ -48188,7 +48661,7 @@
       <c r="CK85" s="7"/>
     </row>
     <row r="86" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15">
+      <c r="A86" s="17">
         <v>43</v>
       </c>
       <c r="B86" s="4"/>
@@ -48281,7 +48754,7 @@
       <c r="CK86" s="6"/>
     </row>
     <row r="87" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="15"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="5"/>
       <c r="C87" s="7"/>
       <c r="D87" s="11"/>
@@ -48372,7 +48845,7 @@
       <c r="CK87" s="7"/>
     </row>
     <row r="88" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15">
+      <c r="A88" s="17">
         <v>44</v>
       </c>
       <c r="B88" s="4"/>
@@ -48465,7 +48938,7 @@
       <c r="CK88" s="6"/>
     </row>
     <row r="89" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="15"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="5"/>
       <c r="C89" s="7"/>
       <c r="D89" s="11"/>
@@ -48556,7 +49029,7 @@
       <c r="CK89" s="7"/>
     </row>
     <row r="90" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15">
+      <c r="A90" s="17">
         <v>45</v>
       </c>
       <c r="B90" s="4"/>
@@ -48649,7 +49122,7 @@
       <c r="CK90" s="6"/>
     </row>
     <row r="91" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="15"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="5"/>
       <c r="C91" s="7"/>
       <c r="D91" s="11"/>
@@ -48740,7 +49213,7 @@
       <c r="CK91" s="7"/>
     </row>
     <row r="92" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15">
+      <c r="A92" s="17">
         <v>46</v>
       </c>
       <c r="B92" s="4"/>
@@ -48833,7 +49306,7 @@
       <c r="CK92" s="6"/>
     </row>
     <row r="93" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="15"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="5"/>
       <c r="C93" s="7"/>
       <c r="D93" s="11"/>
@@ -48924,7 +49397,7 @@
       <c r="CK93" s="7"/>
     </row>
     <row r="94" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15">
+      <c r="A94" s="17">
         <v>47</v>
       </c>
       <c r="B94" s="4"/>
@@ -49017,7 +49490,7 @@
       <c r="CK94" s="6"/>
     </row>
     <row r="95" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="15"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="5"/>
       <c r="C95" s="7"/>
       <c r="D95" s="11"/>
@@ -49108,7 +49581,7 @@
       <c r="CK95" s="7"/>
     </row>
     <row r="96" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15">
+      <c r="A96" s="17">
         <v>48</v>
       </c>
       <c r="B96" s="4"/>
@@ -49201,7 +49674,7 @@
       <c r="CK96" s="6"/>
     </row>
     <row r="97" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="5"/>
       <c r="C97" s="7"/>
       <c r="D97" s="11"/>
@@ -49292,7 +49765,7 @@
       <c r="CK97" s="7"/>
     </row>
     <row r="98" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15">
+      <c r="A98" s="17">
         <v>49</v>
       </c>
       <c r="B98" s="4"/>
@@ -49385,7 +49858,7 @@
       <c r="CK98" s="6"/>
     </row>
     <row r="99" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="15"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="5"/>
       <c r="C99" s="7"/>
       <c r="D99" s="11"/>
@@ -49476,7 +49949,7 @@
       <c r="CK99" s="7"/>
     </row>
     <row r="100" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15">
+      <c r="A100" s="17">
         <v>50</v>
       </c>
       <c r="B100" s="4"/>
@@ -49569,7 +50042,7 @@
       <c r="CK100" s="6"/>
     </row>
     <row r="101" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="15"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="5"/>
       <c r="C101" s="7"/>
       <c r="D101" s="11"/>
@@ -49660,7 +50133,7 @@
       <c r="CK101" s="7"/>
     </row>
     <row r="102" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15">
+      <c r="A102" s="17">
         <v>51</v>
       </c>
       <c r="B102" s="4"/>
@@ -49753,7 +50226,7 @@
       <c r="CK102" s="6"/>
     </row>
     <row r="103" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="5"/>
       <c r="C103" s="7"/>
       <c r="D103" s="11"/>
@@ -49844,7 +50317,7 @@
       <c r="CK103" s="7"/>
     </row>
     <row r="104" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15">
+      <c r="A104" s="17">
         <v>52</v>
       </c>
       <c r="B104" s="4"/>
@@ -49937,7 +50410,7 @@
       <c r="CK104" s="6"/>
     </row>
     <row r="105" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="15"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="5"/>
       <c r="C105" s="7"/>
       <c r="D105" s="11"/>
@@ -50028,7 +50501,7 @@
       <c r="CK105" s="7"/>
     </row>
     <row r="106" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15">
+      <c r="A106" s="17">
         <v>53</v>
       </c>
       <c r="B106" s="4"/>
@@ -50121,7 +50594,7 @@
       <c r="CK106" s="6"/>
     </row>
     <row r="107" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="5"/>
       <c r="C107" s="7"/>
       <c r="D107" s="11"/>
@@ -50212,7 +50685,7 @@
       <c r="CK107" s="7"/>
     </row>
     <row r="108" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15">
+      <c r="A108" s="17">
         <v>54</v>
       </c>
       <c r="B108" s="4"/>
@@ -50305,7 +50778,7 @@
       <c r="CK108" s="6"/>
     </row>
     <row r="109" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="5"/>
       <c r="C109" s="7"/>
       <c r="D109" s="11"/>
@@ -50396,7 +50869,7 @@
       <c r="CK109" s="7"/>
     </row>
     <row r="110" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15">
+      <c r="A110" s="17">
         <v>55</v>
       </c>
       <c r="B110" s="4"/>
@@ -50489,7 +50962,7 @@
       <c r="CK110" s="6"/>
     </row>
     <row r="111" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="5"/>
       <c r="C111" s="7"/>
       <c r="D111" s="11"/>
@@ -50580,7 +51053,7 @@
       <c r="CK111" s="7"/>
     </row>
     <row r="112" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15">
+      <c r="A112" s="17">
         <v>56</v>
       </c>
       <c r="B112" s="4"/>
@@ -50673,7 +51146,7 @@
       <c r="CK112" s="6"/>
     </row>
     <row r="113" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="5"/>
       <c r="C113" s="7"/>
       <c r="D113" s="11"/>
@@ -50764,7 +51237,7 @@
       <c r="CK113" s="7"/>
     </row>
     <row r="114" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15">
+      <c r="A114" s="17">
         <v>57</v>
       </c>
       <c r="B114" s="4"/>
@@ -50857,7 +51330,7 @@
       <c r="CK114" s="6"/>
     </row>
     <row r="115" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="15"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="5"/>
       <c r="C115" s="7"/>
       <c r="D115" s="11"/>
@@ -50948,7 +51421,7 @@
       <c r="CK115" s="7"/>
     </row>
     <row r="116" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15">
+      <c r="A116" s="17">
         <v>58</v>
       </c>
       <c r="B116" s="4"/>
@@ -51041,7 +51514,7 @@
       <c r="CK116" s="6"/>
     </row>
     <row r="117" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="15"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="5"/>
       <c r="C117" s="7"/>
       <c r="D117" s="11"/>
@@ -51132,7 +51605,7 @@
       <c r="CK117" s="7"/>
     </row>
     <row r="118" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15">
+      <c r="A118" s="17">
         <v>59</v>
       </c>
       <c r="B118" s="4"/>
@@ -51225,7 +51698,7 @@
       <c r="CK118" s="6"/>
     </row>
     <row r="119" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="5"/>
       <c r="C119" s="7"/>
       <c r="D119" s="11"/>
@@ -51316,7 +51789,7 @@
       <c r="CK119" s="7"/>
     </row>
     <row r="120" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15">
+      <c r="A120" s="17">
         <v>60</v>
       </c>
       <c r="B120" s="4"/>
@@ -51409,7 +51882,7 @@
       <c r="CK120" s="6"/>
     </row>
     <row r="121" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="15"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="5"/>
       <c r="C121" s="7"/>
       <c r="D121" s="11"/>
@@ -51500,7 +51973,7 @@
       <c r="CK121" s="7"/>
     </row>
     <row r="122" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15">
+      <c r="A122" s="17">
         <v>61</v>
       </c>
       <c r="B122" s="4"/>
@@ -51593,7 +52066,7 @@
       <c r="CK122" s="6"/>
     </row>
     <row r="123" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="5"/>
       <c r="C123" s="7"/>
       <c r="D123" s="11"/>
@@ -51684,7 +52157,7 @@
       <c r="CK123" s="7"/>
     </row>
     <row r="124" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15">
+      <c r="A124" s="17">
         <v>62</v>
       </c>
       <c r="B124" s="4"/>
@@ -51777,7 +52250,7 @@
       <c r="CK124" s="6"/>
     </row>
     <row r="125" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="15"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="5"/>
       <c r="C125" s="7"/>
       <c r="D125" s="11"/>
@@ -51868,7 +52341,7 @@
       <c r="CK125" s="7"/>
     </row>
     <row r="126" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15">
+      <c r="A126" s="17">
         <v>63</v>
       </c>
       <c r="B126" s="4"/>
@@ -51961,7 +52434,7 @@
       <c r="CK126" s="6"/>
     </row>
     <row r="127" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="5"/>
       <c r="C127" s="7"/>
       <c r="D127" s="11"/>
@@ -52052,7 +52525,7 @@
       <c r="CK127" s="7"/>
     </row>
     <row r="128" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15">
+      <c r="A128" s="17">
         <v>64</v>
       </c>
       <c r="B128" s="4"/>
@@ -52145,7 +52618,7 @@
       <c r="CK128" s="6"/>
     </row>
     <row r="129" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="15"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="5"/>
       <c r="C129" s="7"/>
       <c r="D129" s="11"/>
@@ -52236,7 +52709,7 @@
       <c r="CK129" s="7"/>
     </row>
     <row r="130" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15">
+      <c r="A130" s="17">
         <v>65</v>
       </c>
       <c r="B130" s="4"/>
@@ -52329,7 +52802,7 @@
       <c r="CK130" s="6"/>
     </row>
     <row r="131" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="5"/>
       <c r="C131" s="7"/>
       <c r="D131" s="11"/>
@@ -52420,7 +52893,7 @@
       <c r="CK131" s="7"/>
     </row>
     <row r="132" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15">
+      <c r="A132" s="17">
         <v>66</v>
       </c>
       <c r="B132" s="4"/>
@@ -52513,7 +52986,7 @@
       <c r="CK132" s="6"/>
     </row>
     <row r="133" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="15"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="5"/>
       <c r="C133" s="7"/>
       <c r="D133" s="11"/>
@@ -52604,7 +53077,7 @@
       <c r="CK133" s="7"/>
     </row>
     <row r="134" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15">
+      <c r="A134" s="17">
         <v>67</v>
       </c>
       <c r="B134" s="4"/>
@@ -52697,7 +53170,7 @@
       <c r="CK134" s="6"/>
     </row>
     <row r="135" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="5"/>
       <c r="C135" s="7"/>
       <c r="D135" s="11"/>
@@ -52788,7 +53261,7 @@
       <c r="CK135" s="7"/>
     </row>
     <row r="136" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15">
+      <c r="A136" s="17">
         <v>68</v>
       </c>
       <c r="B136" s="4"/>
@@ -52881,7 +53354,7 @@
       <c r="CK136" s="6"/>
     </row>
     <row r="137" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="5"/>
       <c r="C137" s="7"/>
       <c r="D137" s="11"/>
@@ -52972,7 +53445,7 @@
       <c r="CK137" s="7"/>
     </row>
     <row r="138" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15">
+      <c r="A138" s="17">
         <v>69</v>
       </c>
       <c r="B138" s="4"/>
@@ -53065,7 +53538,7 @@
       <c r="CK138" s="6"/>
     </row>
     <row r="139" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="5"/>
       <c r="C139" s="7"/>
       <c r="D139" s="11"/>
@@ -53156,7 +53629,7 @@
       <c r="CK139" s="7"/>
     </row>
     <row r="140" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15">
+      <c r="A140" s="17">
         <v>70</v>
       </c>
       <c r="B140" s="4"/>
@@ -53249,7 +53722,7 @@
       <c r="CK140" s="6"/>
     </row>
     <row r="141" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="15"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="5"/>
       <c r="C141" s="7"/>
       <c r="D141" s="11"/>
@@ -53340,7 +53813,7 @@
       <c r="CK141" s="7"/>
     </row>
     <row r="142" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15">
+      <c r="A142" s="17">
         <v>71</v>
       </c>
       <c r="B142" s="4"/>
@@ -53433,7 +53906,7 @@
       <c r="CK142" s="6"/>
     </row>
     <row r="143" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="15"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="5"/>
       <c r="C143" s="7"/>
       <c r="D143" s="11"/>
@@ -53524,7 +53997,7 @@
       <c r="CK143" s="7"/>
     </row>
     <row r="144" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15">
+      <c r="A144" s="17">
         <v>72</v>
       </c>
       <c r="B144" s="4"/>
@@ -53617,7 +54090,7 @@
       <c r="CK144" s="6"/>
     </row>
     <row r="145" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="15"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="5"/>
       <c r="C145" s="7"/>
       <c r="D145" s="11"/>
@@ -53708,7 +54181,7 @@
       <c r="CK145" s="7"/>
     </row>
     <row r="146" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15">
+      <c r="A146" s="17">
         <v>73</v>
       </c>
       <c r="B146" s="4"/>
@@ -53801,7 +54274,7 @@
       <c r="CK146" s="6"/>
     </row>
     <row r="147" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="5"/>
       <c r="C147" s="7"/>
       <c r="D147" s="11"/>
@@ -53892,7 +54365,7 @@
       <c r="CK147" s="7"/>
     </row>
     <row r="148" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15">
+      <c r="A148" s="17">
         <v>74</v>
       </c>
       <c r="B148" s="4"/>
@@ -53985,7 +54458,7 @@
       <c r="CK148" s="6"/>
     </row>
     <row r="149" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="15"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="5"/>
       <c r="C149" s="7"/>
       <c r="D149" s="11"/>
@@ -54076,7 +54549,7 @@
       <c r="CK149" s="7"/>
     </row>
     <row r="150" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15">
+      <c r="A150" s="17">
         <v>75</v>
       </c>
       <c r="B150" s="4"/>
@@ -54169,7 +54642,7 @@
       <c r="CK150" s="6"/>
     </row>
     <row r="151" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="15"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="5"/>
       <c r="C151" s="7"/>
       <c r="D151" s="11"/>
@@ -54260,7 +54733,7 @@
       <c r="CK151" s="7"/>
     </row>
     <row r="152" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15">
+      <c r="A152" s="17">
         <v>76</v>
       </c>
       <c r="B152" s="4"/>
@@ -54353,7 +54826,7 @@
       <c r="CK152" s="6"/>
     </row>
     <row r="153" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="15"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="5"/>
       <c r="C153" s="7"/>
       <c r="D153" s="11"/>
@@ -54444,7 +54917,7 @@
       <c r="CK153" s="7"/>
     </row>
     <row r="154" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15">
+      <c r="A154" s="17">
         <v>77</v>
       </c>
       <c r="B154" s="4"/>
@@ -54537,7 +55010,7 @@
       <c r="CK154" s="6"/>
     </row>
     <row r="155" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="15"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="5"/>
       <c r="C155" s="7"/>
       <c r="D155" s="11"/>
@@ -54628,7 +55101,7 @@
       <c r="CK155" s="7"/>
     </row>
     <row r="156" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15">
+      <c r="A156" s="17">
         <v>78</v>
       </c>
       <c r="B156" s="4"/>
@@ -54721,7 +55194,7 @@
       <c r="CK156" s="6"/>
     </row>
     <row r="157" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="15"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="5"/>
       <c r="C157" s="7"/>
       <c r="D157" s="11"/>
@@ -54812,7 +55285,7 @@
       <c r="CK157" s="7"/>
     </row>
     <row r="158" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15">
+      <c r="A158" s="17">
         <v>79</v>
       </c>
       <c r="B158" s="4"/>
@@ -54905,7 +55378,7 @@
       <c r="CK158" s="6"/>
     </row>
     <row r="159" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="15"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="5"/>
       <c r="C159" s="7"/>
       <c r="D159" s="11"/>
@@ -54996,7 +55469,7 @@
       <c r="CK159" s="7"/>
     </row>
     <row r="160" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15">
+      <c r="A160" s="17">
         <v>80</v>
       </c>
       <c r="B160" s="4"/>
@@ -55089,7 +55562,7 @@
       <c r="CK160" s="6"/>
     </row>
     <row r="161" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="15"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="5"/>
       <c r="C161" s="7"/>
       <c r="D161" s="11"/>
@@ -55180,7 +55653,7 @@
       <c r="CK161" s="7"/>
     </row>
     <row r="162" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15">
+      <c r="A162" s="17">
         <v>81</v>
       </c>
       <c r="B162" s="4"/>
@@ -55273,7 +55746,7 @@
       <c r="CK162" s="6"/>
     </row>
     <row r="163" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="15"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="5"/>
       <c r="C163" s="7"/>
       <c r="D163" s="11"/>
@@ -55364,7 +55837,7 @@
       <c r="CK163" s="7"/>
     </row>
     <row r="164" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15">
+      <c r="A164" s="17">
         <v>82</v>
       </c>
       <c r="B164" s="4"/>
@@ -55457,7 +55930,7 @@
       <c r="CK164" s="6"/>
     </row>
     <row r="165" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="15"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="5"/>
       <c r="C165" s="7"/>
       <c r="D165" s="11"/>
@@ -55548,7 +56021,7 @@
       <c r="CK165" s="7"/>
     </row>
     <row r="166" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15">
+      <c r="A166" s="17">
         <v>83</v>
       </c>
       <c r="B166" s="4"/>
@@ -55641,7 +56114,7 @@
       <c r="CK166" s="6"/>
     </row>
     <row r="167" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="5"/>
       <c r="C167" s="7"/>
       <c r="D167" s="11"/>
@@ -55732,7 +56205,7 @@
       <c r="CK167" s="7"/>
     </row>
     <row r="168" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15">
+      <c r="A168" s="17">
         <v>84</v>
       </c>
       <c r="B168" s="4"/>
@@ -55825,7 +56298,7 @@
       <c r="CK168" s="6"/>
     </row>
     <row r="169" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="15"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="5"/>
       <c r="C169" s="7"/>
       <c r="D169" s="11"/>
@@ -55916,7 +56389,7 @@
       <c r="CK169" s="7"/>
     </row>
     <row r="170" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15">
+      <c r="A170" s="17">
         <v>85</v>
       </c>
       <c r="B170" s="4"/>
@@ -56009,7 +56482,7 @@
       <c r="CK170" s="6"/>
     </row>
     <row r="171" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="15"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="5"/>
       <c r="C171" s="7"/>
       <c r="D171" s="11"/>
@@ -56100,7 +56573,7 @@
       <c r="CK171" s="7"/>
     </row>
     <row r="172" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15">
+      <c r="A172" s="17">
         <v>86</v>
       </c>
       <c r="B172" s="4"/>
@@ -56193,7 +56666,7 @@
       <c r="CK172" s="6"/>
     </row>
     <row r="173" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="15"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="5"/>
       <c r="C173" s="7"/>
       <c r="D173" s="11"/>
@@ -56284,7 +56757,7 @@
       <c r="CK173" s="7"/>
     </row>
     <row r="174" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15">
+      <c r="A174" s="17">
         <v>87</v>
       </c>
       <c r="B174" s="4"/>
@@ -56377,7 +56850,7 @@
       <c r="CK174" s="6"/>
     </row>
     <row r="175" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="15"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="5"/>
       <c r="C175" s="7"/>
       <c r="D175" s="11"/>
@@ -56468,7 +56941,7 @@
       <c r="CK175" s="7"/>
     </row>
     <row r="176" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15">
+      <c r="A176" s="17">
         <v>88</v>
       </c>
       <c r="B176" s="4"/>
@@ -56561,7 +57034,7 @@
       <c r="CK176" s="6"/>
     </row>
     <row r="177" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="15"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="5"/>
       <c r="C177" s="7"/>
       <c r="D177" s="11"/>
@@ -56652,7 +57125,7 @@
       <c r="CK177" s="7"/>
     </row>
     <row r="178" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15">
+      <c r="A178" s="17">
         <v>89</v>
       </c>
       <c r="B178" s="4"/>
@@ -56745,7 +57218,7 @@
       <c r="CK178" s="6"/>
     </row>
     <row r="179" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="15"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="5"/>
       <c r="C179" s="7"/>
       <c r="D179" s="11"/>
@@ -56836,7 +57309,7 @@
       <c r="CK179" s="7"/>
     </row>
     <row r="180" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15">
+      <c r="A180" s="17">
         <v>90</v>
       </c>
       <c r="B180" s="4"/>
@@ -56929,7 +57402,7 @@
       <c r="CK180" s="6"/>
     </row>
     <row r="181" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="15"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="5"/>
       <c r="C181" s="7"/>
       <c r="D181" s="11"/>
@@ -57020,7 +57493,7 @@
       <c r="CK181" s="7"/>
     </row>
     <row r="182" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15">
+      <c r="A182" s="17">
         <v>91</v>
       </c>
       <c r="B182" s="4"/>
@@ -57113,7 +57586,7 @@
       <c r="CK182" s="6"/>
     </row>
     <row r="183" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="15"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="5"/>
       <c r="C183" s="7"/>
       <c r="D183" s="11"/>
@@ -57204,7 +57677,7 @@
       <c r="CK183" s="7"/>
     </row>
     <row r="184" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15">
+      <c r="A184" s="17">
         <v>92</v>
       </c>
       <c r="B184" s="4"/>
@@ -57297,7 +57770,7 @@
       <c r="CK184" s="6"/>
     </row>
     <row r="185" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="15"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="5"/>
       <c r="C185" s="7"/>
       <c r="D185" s="11"/>
@@ -57388,7 +57861,7 @@
       <c r="CK185" s="7"/>
     </row>
     <row r="186" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15">
+      <c r="A186" s="17">
         <v>93</v>
       </c>
       <c r="B186" s="4"/>
@@ -57481,7 +57954,7 @@
       <c r="CK186" s="6"/>
     </row>
     <row r="187" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="15"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="5"/>
       <c r="C187" s="7"/>
       <c r="D187" s="11"/>
@@ -57572,7 +58045,7 @@
       <c r="CK187" s="7"/>
     </row>
     <row r="188" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15">
+      <c r="A188" s="17">
         <v>94</v>
       </c>
       <c r="B188" s="4"/>
@@ -57665,7 +58138,7 @@
       <c r="CK188" s="6"/>
     </row>
     <row r="189" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="15"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="5"/>
       <c r="C189" s="7"/>
       <c r="D189" s="11"/>
@@ -57756,7 +58229,7 @@
       <c r="CK189" s="7"/>
     </row>
     <row r="190" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15">
+      <c r="A190" s="17">
         <v>95</v>
       </c>
       <c r="B190" s="4"/>
@@ -57849,7 +58322,7 @@
       <c r="CK190" s="6"/>
     </row>
     <row r="191" spans="1:89" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="15"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="5"/>
       <c r="C191" s="7"/>
       <c r="D191" s="11"/>
@@ -57941,91 +58414,36 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -58050,36 +58468,91 @@
     <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>

--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38534053-E70C-44ED-978C-62DB6129D771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68985" yWindow="3120" windowWidth="43200" windowHeight="23985" activeTab="1" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="68985" yWindow="3120" windowWidth="43200" windowHeight="23985" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -253,10 +253,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5109,182 +5109,182 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="16">
+      <c r="B1" s="15">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="15">
+      <c r="C1" s="15"/>
+      <c r="D1" s="16">
         <v>2</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15">
+      <c r="E1" s="16"/>
+      <c r="F1" s="16">
         <v>3</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16">
         <v>4</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16">
         <v>5</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15">
+      <c r="K1" s="16"/>
+      <c r="L1" s="16">
         <v>6</v>
       </c>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15">
+      <c r="M1" s="16"/>
+      <c r="N1" s="16">
         <v>7</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15">
+      <c r="O1" s="16"/>
+      <c r="P1" s="16">
         <v>8</v>
       </c>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15">
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16">
         <v>9</v>
       </c>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15">
+      <c r="S1" s="16"/>
+      <c r="T1" s="16">
         <v>10</v>
       </c>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16">
         <v>11</v>
       </c>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15">
+      <c r="W1" s="16"/>
+      <c r="X1" s="16">
         <v>12</v>
       </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15">
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16">
         <v>13</v>
       </c>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15">
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16">
         <v>14</v>
       </c>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15">
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16">
         <v>15</v>
       </c>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15">
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16">
         <v>16</v>
       </c>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15">
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16">
         <v>17</v>
       </c>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15">
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16">
         <v>18</v>
       </c>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15">
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16">
         <v>19</v>
       </c>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15">
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16">
         <v>20</v>
       </c>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15">
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16">
         <v>21</v>
       </c>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="15">
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="16">
         <v>22</v>
       </c>
-      <c r="AS1" s="15"/>
-      <c r="AT1" s="15">
+      <c r="AS1" s="16"/>
+      <c r="AT1" s="16">
         <v>23</v>
       </c>
-      <c r="AU1" s="15"/>
-      <c r="AV1" s="15">
+      <c r="AU1" s="16"/>
+      <c r="AV1" s="16">
         <v>24</v>
       </c>
-      <c r="AW1" s="15"/>
-      <c r="AX1" s="15">
+      <c r="AW1" s="16"/>
+      <c r="AX1" s="16">
         <v>25</v>
       </c>
-      <c r="AY1" s="15"/>
-      <c r="AZ1" s="15">
+      <c r="AY1" s="16"/>
+      <c r="AZ1" s="16">
         <v>26</v>
       </c>
-      <c r="BA1" s="15"/>
-      <c r="BB1" s="15">
+      <c r="BA1" s="16"/>
+      <c r="BB1" s="16">
         <v>27</v>
       </c>
-      <c r="BC1" s="15"/>
-      <c r="BD1" s="15">
+      <c r="BC1" s="16"/>
+      <c r="BD1" s="16">
         <v>28</v>
       </c>
-      <c r="BE1" s="15"/>
-      <c r="BF1" s="15">
+      <c r="BE1" s="16"/>
+      <c r="BF1" s="16">
         <v>29</v>
       </c>
-      <c r="BG1" s="15"/>
-      <c r="BH1" s="15">
+      <c r="BG1" s="16"/>
+      <c r="BH1" s="16">
         <v>30</v>
       </c>
-      <c r="BI1" s="15"/>
-      <c r="BJ1" s="15">
+      <c r="BI1" s="16"/>
+      <c r="BJ1" s="16">
         <v>31</v>
       </c>
-      <c r="BK1" s="15"/>
-      <c r="BL1" s="15">
+      <c r="BK1" s="16"/>
+      <c r="BL1" s="16">
         <v>32</v>
       </c>
-      <c r="BM1" s="15"/>
-      <c r="BN1" s="15">
+      <c r="BM1" s="16"/>
+      <c r="BN1" s="16">
         <v>33</v>
       </c>
-      <c r="BO1" s="15"/>
-      <c r="BP1" s="15">
+      <c r="BO1" s="16"/>
+      <c r="BP1" s="16">
         <v>34</v>
       </c>
-      <c r="BQ1" s="15"/>
-      <c r="BR1" s="15">
+      <c r="BQ1" s="16"/>
+      <c r="BR1" s="16">
         <v>35</v>
       </c>
-      <c r="BS1" s="15"/>
-      <c r="BT1" s="15">
+      <c r="BS1" s="16"/>
+      <c r="BT1" s="16">
         <v>36</v>
       </c>
-      <c r="BU1" s="15"/>
-      <c r="BV1" s="15">
+      <c r="BU1" s="16"/>
+      <c r="BV1" s="16">
         <v>37</v>
       </c>
-      <c r="BW1" s="15"/>
-      <c r="BX1" s="15">
+      <c r="BW1" s="16"/>
+      <c r="BX1" s="16">
         <v>38</v>
       </c>
-      <c r="BY1" s="15"/>
-      <c r="BZ1" s="15">
+      <c r="BY1" s="16"/>
+      <c r="BZ1" s="16">
         <v>39</v>
       </c>
-      <c r="CA1" s="15"/>
-      <c r="CB1" s="15">
+      <c r="CA1" s="16"/>
+      <c r="CB1" s="16">
         <v>40</v>
       </c>
-      <c r="CC1" s="15"/>
-      <c r="CD1" s="15">
+      <c r="CC1" s="16"/>
+      <c r="CD1" s="16">
         <v>41</v>
       </c>
-      <c r="CE1" s="15"/>
-      <c r="CF1" s="15">
+      <c r="CE1" s="16"/>
+      <c r="CF1" s="16">
         <v>42</v>
       </c>
-      <c r="CG1" s="15"/>
-      <c r="CH1" s="15">
+      <c r="CG1" s="16"/>
+      <c r="CH1" s="16">
         <v>43</v>
       </c>
-      <c r="CI1" s="15"/>
-      <c r="CJ1" s="15">
+      <c r="CI1" s="16"/>
+      <c r="CJ1" s="16">
         <v>44</v>
       </c>
-      <c r="CK1" s="15"/>
+      <c r="CK1" s="16"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18">
@@ -22770,91 +22770,36 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="BN1:BO1"/>
+    <mergeCell ref="BP1:BQ1"/>
+    <mergeCell ref="BR1:BS1"/>
+    <mergeCell ref="CD1:CE1"/>
+    <mergeCell ref="CF1:CG1"/>
+    <mergeCell ref="CH1:CI1"/>
+    <mergeCell ref="CJ1:CK1"/>
+    <mergeCell ref="BT1:BU1"/>
+    <mergeCell ref="BV1:BW1"/>
+    <mergeCell ref="BX1:BY1"/>
+    <mergeCell ref="BZ1:CA1"/>
+    <mergeCell ref="CB1:CC1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="BJ1:BK1"/>
+    <mergeCell ref="BL1:BM1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -22879,36 +22824,91 @@
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="BJ1:BK1"/>
-    <mergeCell ref="BL1:BM1"/>
-    <mergeCell ref="BN1:BO1"/>
-    <mergeCell ref="BP1:BQ1"/>
-    <mergeCell ref="BR1:BS1"/>
-    <mergeCell ref="CD1:CE1"/>
-    <mergeCell ref="CF1:CG1"/>
-    <mergeCell ref="CH1:CI1"/>
-    <mergeCell ref="CJ1:CK1"/>
-    <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="BV1:BW1"/>
-    <mergeCell ref="BX1:BY1"/>
-    <mergeCell ref="BZ1:CA1"/>
-    <mergeCell ref="CB1:CC1"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:A179"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
@@ -22933,182 +22933,182 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="16">
+      <c r="B1" s="15">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="15">
+      <c r="C1" s="15"/>
+      <c r="D1" s="16">
         <v>2</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15">
+      <c r="E1" s="16"/>
+      <c r="F1" s="16">
         <v>3</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16">
         <v>4</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16">
         <v>5</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15">
+      <c r="K1" s="16"/>
+      <c r="L1" s="16">
         <v>6</v>
       </c>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15">
+      <c r="M1" s="16"/>
+      <c r="N1" s="16">
         <v>7</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15">
+      <c r="O1" s="16"/>
+      <c r="P1" s="16">
         <v>8</v>
       </c>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15">
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16">
         <v>9</v>
       </c>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15">
+      <c r="S1" s="16"/>
+      <c r="T1" s="16">
         <v>10</v>
       </c>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16">
         <v>11</v>
       </c>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15">
+      <c r="W1" s="16"/>
+      <c r="X1" s="16">
         <v>12</v>
       </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15">
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16">
         <v>13</v>
       </c>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15">
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16">
         <v>14</v>
       </c>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15">
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16">
         <v>15</v>
       </c>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15">
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16">
         <v>16</v>
       </c>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15">
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16">
         <v>17</v>
       </c>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15">
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16">
         <v>18</v>
       </c>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15">
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16">
         <v>19</v>
       </c>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15">
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16">
         <v>20</v>
       </c>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15">
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16">
         <v>21</v>
       </c>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="15">
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="16">
         <v>22</v>
       </c>
-      <c r="AS1" s="15"/>
-      <c r="AT1" s="15">
+      <c r="AS1" s="16"/>
+      <c r="AT1" s="16">
         <v>23</v>
       </c>
-      <c r="AU1" s="15"/>
-      <c r="AV1" s="15">
+      <c r="AU1" s="16"/>
+      <c r="AV1" s="16">
         <v>24</v>
       </c>
-      <c r="AW1" s="15"/>
-      <c r="AX1" s="15">
+      <c r="AW1" s="16"/>
+      <c r="AX1" s="16">
         <v>25</v>
       </c>
-      <c r="AY1" s="15"/>
-      <c r="AZ1" s="15">
+      <c r="AY1" s="16"/>
+      <c r="AZ1" s="16">
         <v>26</v>
       </c>
-      <c r="BA1" s="15"/>
-      <c r="BB1" s="15">
+      <c r="BA1" s="16"/>
+      <c r="BB1" s="16">
         <v>27</v>
       </c>
-      <c r="BC1" s="15"/>
-      <c r="BD1" s="15">
+      <c r="BC1" s="16"/>
+      <c r="BD1" s="16">
         <v>28</v>
       </c>
-      <c r="BE1" s="15"/>
-      <c r="BF1" s="15">
+      <c r="BE1" s="16"/>
+      <c r="BF1" s="16">
         <v>29</v>
       </c>
-      <c r="BG1" s="15"/>
-      <c r="BH1" s="15">
+      <c r="BG1" s="16"/>
+      <c r="BH1" s="16">
         <v>30</v>
       </c>
-      <c r="BI1" s="15"/>
-      <c r="BJ1" s="15">
+      <c r="BI1" s="16"/>
+      <c r="BJ1" s="16">
         <v>31</v>
       </c>
-      <c r="BK1" s="15"/>
-      <c r="BL1" s="15">
+      <c r="BK1" s="16"/>
+      <c r="BL1" s="16">
         <v>32</v>
       </c>
-      <c r="BM1" s="15"/>
-      <c r="BN1" s="15">
+      <c r="BM1" s="16"/>
+      <c r="BN1" s="16">
         <v>33</v>
       </c>
-      <c r="BO1" s="15"/>
-      <c r="BP1" s="15">
+      <c r="BO1" s="16"/>
+      <c r="BP1" s="16">
         <v>34</v>
       </c>
-      <c r="BQ1" s="15"/>
-      <c r="BR1" s="15">
+      <c r="BQ1" s="16"/>
+      <c r="BR1" s="16">
         <v>35</v>
       </c>
-      <c r="BS1" s="15"/>
-      <c r="BT1" s="15">
+      <c r="BS1" s="16"/>
+      <c r="BT1" s="16">
         <v>36</v>
       </c>
-      <c r="BU1" s="15"/>
-      <c r="BV1" s="15">
+      <c r="BU1" s="16"/>
+      <c r="BV1" s="16">
         <v>37</v>
       </c>
-      <c r="BW1" s="15"/>
-      <c r="BX1" s="15">
+      <c r="BW1" s="16"/>
+      <c r="BX1" s="16">
         <v>38</v>
       </c>
-      <c r="BY1" s="15"/>
-      <c r="BZ1" s="15">
+      <c r="BY1" s="16"/>
+      <c r="BZ1" s="16">
         <v>39</v>
       </c>
-      <c r="CA1" s="15"/>
-      <c r="CB1" s="15">
+      <c r="CA1" s="16"/>
+      <c r="CB1" s="16">
         <v>40</v>
       </c>
-      <c r="CC1" s="15"/>
-      <c r="CD1" s="15">
+      <c r="CC1" s="16"/>
+      <c r="CD1" s="16">
         <v>41</v>
       </c>
-      <c r="CE1" s="15"/>
-      <c r="CF1" s="15">
+      <c r="CE1" s="16"/>
+      <c r="CF1" s="16">
         <v>42</v>
       </c>
-      <c r="CG1" s="15"/>
-      <c r="CH1" s="15">
+      <c r="CG1" s="16"/>
+      <c r="CH1" s="16">
         <v>43</v>
       </c>
-      <c r="CI1" s="15"/>
-      <c r="CJ1" s="15">
+      <c r="CI1" s="16"/>
+      <c r="CJ1" s="16">
         <v>44</v>
       </c>
-      <c r="CK1" s="15"/>
+      <c r="CK1" s="16"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18">
@@ -40592,36 +40592,91 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -40646,91 +40701,36 @@
     <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
@@ -40755,182 +40755,182 @@
       <c r="A1" s="2">
         <v>0</v>
       </c>
-      <c r="B1" s="16">
+      <c r="B1" s="15">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="15">
+      <c r="C1" s="15"/>
+      <c r="D1" s="16">
         <v>2</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15">
+      <c r="E1" s="16"/>
+      <c r="F1" s="16">
         <v>3</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15">
+      <c r="G1" s="16"/>
+      <c r="H1" s="16">
         <v>4</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16">
         <v>5</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15">
+      <c r="K1" s="16"/>
+      <c r="L1" s="16">
         <v>6</v>
       </c>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15">
+      <c r="M1" s="16"/>
+      <c r="N1" s="16">
         <v>7</v>
       </c>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15">
+      <c r="O1" s="16"/>
+      <c r="P1" s="16">
         <v>8</v>
       </c>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15">
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16">
         <v>9</v>
       </c>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15">
+      <c r="S1" s="16"/>
+      <c r="T1" s="16">
         <v>10</v>
       </c>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16">
         <v>11</v>
       </c>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15">
+      <c r="W1" s="16"/>
+      <c r="X1" s="16">
         <v>12</v>
       </c>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15">
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16">
         <v>13</v>
       </c>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15">
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16">
         <v>14</v>
       </c>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15">
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16">
         <v>15</v>
       </c>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15">
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16">
         <v>16</v>
       </c>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15">
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16">
         <v>17</v>
       </c>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15">
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16">
         <v>18</v>
       </c>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15">
+      <c r="AK1" s="16"/>
+      <c r="AL1" s="16">
         <v>19</v>
       </c>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15">
+      <c r="AM1" s="16"/>
+      <c r="AN1" s="16">
         <v>20</v>
       </c>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15">
+      <c r="AO1" s="16"/>
+      <c r="AP1" s="16">
         <v>21</v>
       </c>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="15">
+      <c r="AQ1" s="16"/>
+      <c r="AR1" s="16">
         <v>22</v>
       </c>
-      <c r="AS1" s="15"/>
-      <c r="AT1" s="15">
+      <c r="AS1" s="16"/>
+      <c r="AT1" s="16">
         <v>23</v>
       </c>
-      <c r="AU1" s="15"/>
-      <c r="AV1" s="15">
+      <c r="AU1" s="16"/>
+      <c r="AV1" s="16">
         <v>24</v>
       </c>
-      <c r="AW1" s="15"/>
-      <c r="AX1" s="15">
+      <c r="AW1" s="16"/>
+      <c r="AX1" s="16">
         <v>25</v>
       </c>
-      <c r="AY1" s="15"/>
-      <c r="AZ1" s="15">
+      <c r="AY1" s="16"/>
+      <c r="AZ1" s="16">
         <v>26</v>
       </c>
-      <c r="BA1" s="15"/>
-      <c r="BB1" s="15">
+      <c r="BA1" s="16"/>
+      <c r="BB1" s="16">
         <v>27</v>
       </c>
-      <c r="BC1" s="15"/>
-      <c r="BD1" s="15">
+      <c r="BC1" s="16"/>
+      <c r="BD1" s="16">
         <v>28</v>
       </c>
-      <c r="BE1" s="15"/>
-      <c r="BF1" s="15">
+      <c r="BE1" s="16"/>
+      <c r="BF1" s="16">
         <v>29</v>
       </c>
-      <c r="BG1" s="15"/>
-      <c r="BH1" s="15">
+      <c r="BG1" s="16"/>
+      <c r="BH1" s="16">
         <v>30</v>
       </c>
-      <c r="BI1" s="15"/>
-      <c r="BJ1" s="15">
+      <c r="BI1" s="16"/>
+      <c r="BJ1" s="16">
         <v>31</v>
       </c>
-      <c r="BK1" s="15"/>
-      <c r="BL1" s="15">
+      <c r="BK1" s="16"/>
+      <c r="BL1" s="16">
         <v>32</v>
       </c>
-      <c r="BM1" s="15"/>
-      <c r="BN1" s="15">
+      <c r="BM1" s="16"/>
+      <c r="BN1" s="16">
         <v>33</v>
       </c>
-      <c r="BO1" s="15"/>
-      <c r="BP1" s="15">
+      <c r="BO1" s="16"/>
+      <c r="BP1" s="16">
         <v>34</v>
       </c>
-      <c r="BQ1" s="15"/>
-      <c r="BR1" s="15">
+      <c r="BQ1" s="16"/>
+      <c r="BR1" s="16">
         <v>35</v>
       </c>
-      <c r="BS1" s="15"/>
-      <c r="BT1" s="15">
+      <c r="BS1" s="16"/>
+      <c r="BT1" s="16">
         <v>36</v>
       </c>
-      <c r="BU1" s="15"/>
-      <c r="BV1" s="15">
+      <c r="BU1" s="16"/>
+      <c r="BV1" s="16">
         <v>37</v>
       </c>
-      <c r="BW1" s="15"/>
-      <c r="BX1" s="15">
+      <c r="BW1" s="16"/>
+      <c r="BX1" s="16">
         <v>38</v>
       </c>
-      <c r="BY1" s="15"/>
-      <c r="BZ1" s="15">
+      <c r="BY1" s="16"/>
+      <c r="BZ1" s="16">
         <v>39</v>
       </c>
-      <c r="CA1" s="15"/>
-      <c r="CB1" s="15">
+      <c r="CA1" s="16"/>
+      <c r="CB1" s="16">
         <v>40</v>
       </c>
-      <c r="CC1" s="15"/>
-      <c r="CD1" s="15">
+      <c r="CC1" s="16"/>
+      <c r="CD1" s="16">
         <v>41</v>
       </c>
-      <c r="CE1" s="15"/>
-      <c r="CF1" s="15">
+      <c r="CE1" s="16"/>
+      <c r="CF1" s="16">
         <v>42</v>
       </c>
-      <c r="CG1" s="15"/>
-      <c r="CH1" s="15">
+      <c r="CG1" s="16"/>
+      <c r="CH1" s="16">
         <v>43</v>
       </c>
-      <c r="CI1" s="15"/>
-      <c r="CJ1" s="15">
+      <c r="CI1" s="16"/>
+      <c r="CJ1" s="16">
         <v>44</v>
       </c>
-      <c r="CK1" s="15"/>
+      <c r="CK1" s="16"/>
     </row>
     <row r="2" spans="1:89" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18">
@@ -58414,36 +58414,91 @@
     </row>
   </sheetData>
   <mergeCells count="139">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AX1:AY1"/>
-    <mergeCell ref="AZ1:BA1"/>
-    <mergeCell ref="BB1:BC1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="BF1:BG1"/>
-    <mergeCell ref="BH1:BI1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="A190:A191"/>
+    <mergeCell ref="A178:A179"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A186:A187"/>
+    <mergeCell ref="A188:A189"/>
+    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A154:A155"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A158:A159"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A164:A165"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="A144:A145"/>
+    <mergeCell ref="A146:A147"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
@@ -58468,91 +58523,36 @@
     <mergeCell ref="BP1:BQ1"/>
     <mergeCell ref="BR1:BS1"/>
     <mergeCell ref="BT1:BU1"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A154:A155"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A158:A159"/>
-    <mergeCell ref="A160:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A164:A165"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="A144:A145"/>
-    <mergeCell ref="A146:A147"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="A190:A191"/>
-    <mergeCell ref="A178:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A182:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A189"/>
-    <mergeCell ref="A166:A167"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A175"/>
-    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="AX1:AY1"/>
+    <mergeCell ref="AZ1:BA1"/>
+    <mergeCell ref="BB1:BC1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="BF1:BG1"/>
+    <mergeCell ref="BH1:BI1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AV1:AW1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>

--- a/src/index.xlsx
+++ b/src/index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\0_forge\ro\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73362EBD-E25E-477C-BEF1-BB6E64F8B07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DBE304-6EDF-47A7-BD4C-EA826E3A7710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="56715" yWindow="5775" windowWidth="40545" windowHeight="26820" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
+    <workbookView xWindow="60675" yWindow="2970" windowWidth="40545" windowHeight="26820" activeTab="2" xr2:uid="{D0EE71BD-B30E-4D43-B36C-EBD3A221A804}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="6" r:id="rId1"/>
@@ -4258,14 +4258,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>153864</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>70</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>72</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -4282,8 +4282,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4154365" y="1846385"/>
-          <a:ext cx="6616212" cy="307730"/>
+          <a:off x="4154364" y="1846385"/>
+          <a:ext cx="7019193" cy="307730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4346,7 +4346,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>さん。物々交換も。</a:t>
+            <a:t>さん。部屋がサーバールームのようになってます。</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100" b="1" i="0">
             <a:solidFill>
